--- a/apps/api/data/excel_templates/skills.xlsx
+++ b/apps/api/data/excel_templates/skills.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Bildix/Website/Bildyx/apps/api/data/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2073473-DAFD-024A-B22A-94B36073C9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB0F159-E571-0244-84F9-0C6CCF9D0D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="20740" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="skills" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="855">
   <si>
     <t>name</t>
   </si>
@@ -74,13 +74,2528 @@
   </si>
   <si>
     <t>metadata</t>
+  </si>
+  <si>
+    <t>2-3 years (advanced expertise)</t>
+  </si>
+  <si>
+    <t>Object-Oriented Programming, Full-stack Development, Machine Learning</t>
+  </si>
+  <si>
+    <t>Computer Science, Software Engineering, Data Science</t>
+  </si>
+  <si>
+    <t>Applications, Data Analysis, AI Development</t>
+  </si>
+  <si>
+    <t>Technology, Software, Data Science</t>
+  </si>
+  <si>
+    <t>Software Developer, Data Scientist, AI Engineer</t>
+  </si>
+  <si>
+    <t>Software Development, Data Science, AI</t>
+  </si>
+  <si>
+    <t>Software Development, Programming</t>
+  </si>
+  <si>
+    <t>Technical Skill</t>
+  </si>
+  <si>
+    <t>C++/Python/Java Programming</t>
+  </si>
+  <si>
+    <t>1-2 years (intermediate to advanced expertise)</t>
+  </si>
+  <si>
+    <t>Data Structures, Algorithm Optimization, Embedded Programming</t>
+  </si>
+  <si>
+    <t>Applications, Machine Learning, Embedded Systems</t>
+  </si>
+  <si>
+    <t>Software Developer, Data Scientist, Embedded Systems Engineer</t>
+  </si>
+  <si>
+    <t>Software Development, Data Science, Embedded Systems</t>
+  </si>
+  <si>
+    <t>C++/Python Programming</t>
+  </si>
+  <si>
+    <t>Object-Oriented Programming, Full-stack Development, Data Structures</t>
+  </si>
+  <si>
+    <t>Applications, Data Analysis, Web Development</t>
+  </si>
+  <si>
+    <t>Technology, Data Science, Software Development</t>
+  </si>
+  <si>
+    <t>Software Developer, Data Scientist, Web Developer</t>
+  </si>
+  <si>
+    <t>Software Development, Data Science, Web Development</t>
+  </si>
+  <si>
+    <t>C++/Java/Python Programming</t>
+  </si>
+  <si>
+    <t>1-2 years (intermediate expertise)</t>
+  </si>
+  <si>
+    <t>Object-Oriented Programming, Cross-platform Development, Web Development</t>
+  </si>
+  <si>
+    <t>Computer Science, Software Engineering</t>
+  </si>
+  <si>
+    <t>Applications, Web Apps, Mobile Apps</t>
+  </si>
+  <si>
+    <t>Technology, Software, Mobile Development</t>
+  </si>
+  <si>
+    <t>Software Developer, Mobile App Developer, Web Developer</t>
+  </si>
+  <si>
+    <t>Software Development, Web Development, Mobile Apps</t>
+  </si>
+  <si>
+    <t>C++/Java Programming</t>
+  </si>
+  <si>
+    <t>Object-Oriented Programming, Algorithm Design, Data Structures</t>
+  </si>
+  <si>
+    <t>Applications, Data Analysis, Game Development</t>
+  </si>
+  <si>
+    <t>Technology, Data Science, Gaming, Software</t>
+  </si>
+  <si>
+    <t>Software Developer, Data Scientist, Game Programmer</t>
+  </si>
+  <si>
+    <t>Software Development, Data Science, Game Development</t>
+  </si>
+  <si>
+    <t>C/C++/Python Programming</t>
+  </si>
+  <si>
+    <t>Numerical Methods, Performance Optimization, Parallel Programming</t>
+  </si>
+  <si>
+    <t>Computer Science, Engineering, Computational Science</t>
+  </si>
+  <si>
+    <t>Simulation Software, Scientific Applications</t>
+  </si>
+  <si>
+    <t>Technology, Science, Research</t>
+  </si>
+  <si>
+    <t>HPC Developer, Embedded Systems Engineer, Programmer</t>
+  </si>
+  <si>
+    <t>High-Performance Computing, Embedded Systems</t>
+  </si>
+  <si>
+    <t>C/C++/Fortran Programming</t>
+  </si>
+  <si>
+    <t>1 year (intermediate expertise)</t>
+  </si>
+  <si>
+    <t>Memory Management, Object-Oriented Programming, Multi-threading</t>
+  </si>
+  <si>
+    <t>Applications, Game Engines, Systems Software</t>
+  </si>
+  <si>
+    <t>Technology, Gaming, Electronics, Software</t>
+  </si>
+  <si>
+    <t>Software Developer, Game Developer, Systems Programmer</t>
+  </si>
+  <si>
+    <t>Software Development, Embedded Systems, Game Development</t>
+  </si>
+  <si>
+    <t>C/C++ Programming</t>
+  </si>
+  <si>
+    <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
+  </si>
+  <si>
+    <t>Algorithm Development, Memory Management, System-Level Programming</t>
+  </si>
+  <si>
+    <t>Applications, Firmware, Systems Software</t>
+  </si>
+  <si>
+    <t>Technology, Electronics, Software Development</t>
+  </si>
+  <si>
+    <t>Software Developer, Embedded Systems Engineer, Programmer</t>
+  </si>
+  <si>
+    <t>Software Development, Embedded Systems</t>
+  </si>
+  <si>
+    <t>C Programming</t>
+  </si>
+  <si>
+    <t>Crisis Management, Risk Analysis, Strategic Planning</t>
+  </si>
+  <si>
+    <t>Business Administration, Risk Management, IT Management</t>
+  </si>
+  <si>
+    <t>Continuity Plans, Disaster Recovery</t>
+  </si>
+  <si>
+    <t>IT, Healthcare, Government, Corporate</t>
+  </si>
+  <si>
+    <t>Business Continuity Planner, Risk Manager, Operations Manager</t>
+  </si>
+  <si>
+    <t>IT, Healthcare, Corporate, Government</t>
+  </si>
+  <si>
+    <t>Risk Management, Business Strategy</t>
+  </si>
+  <si>
+    <t>Business &amp; Organizational Skill</t>
+  </si>
+  <si>
+    <t>Business Continuity Planning</t>
+  </si>
+  <si>
+    <t>Data Transfer Optimization, Hardware Design, System Architecture</t>
+  </si>
+  <si>
+    <t>Computer Engineering, Electrical Engineering</t>
+  </si>
+  <si>
+    <t>Computer Systems, Microprocessor Design</t>
+  </si>
+  <si>
+    <t>Electronics, Technology, Embedded Systems</t>
+  </si>
+  <si>
+    <t>Systems Architect, Hardware Engineer, Embedded Systems Designer</t>
+  </si>
+  <si>
+    <t>Electronics, Computer Science, Embedded Systems</t>
+  </si>
+  <si>
+    <t>Computer Architecture, Hardware Design</t>
+  </si>
+  <si>
+    <t>Bus Architectures</t>
+  </si>
+  <si>
+    <t>Stress Testing, System Testing, Failure Prediction</t>
+  </si>
+  <si>
+    <t>Electrical Engineering, Mechanical Engineering</t>
+  </si>
+  <si>
+    <t>Product Testing, Reliability Evaluation</t>
+  </si>
+  <si>
+    <t>Electronics, Automotive, Manufacturing</t>
+  </si>
+  <si>
+    <t>Test Engineer, QA Engineer, Manufacturing Specialist</t>
+  </si>
+  <si>
+    <t>Electronics, Manufacturing, Automotive</t>
+  </si>
+  <si>
+    <t>Quality Assurance, Testing</t>
+  </si>
+  <si>
+    <t>Burn-In Testing</t>
+  </si>
+  <si>
+    <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+  </si>
+  <si>
+    <t>Brand Strategy, Customer Insights, Competitive Analysis</t>
+  </si>
+  <si>
+    <t>Marketing, Business Administration, Communications</t>
+  </si>
+  <si>
+    <t>Brand Positioning, Product Identity</t>
+  </si>
+  <si>
+    <t>Retail, Advertising, Consumer Goods</t>
+  </si>
+  <si>
+    <t>Brand Strategist, Marketing Manager, Product Manager</t>
+  </si>
+  <si>
+    <t>Advertising, Retail, Consumer Goods</t>
+  </si>
+  <si>
+    <t>Marketing, Branding, Strategy</t>
+  </si>
+  <si>
+    <t>Business &amp; Marketing Skill</t>
+  </si>
+  <si>
+    <t>Brand Development</t>
+  </si>
+  <si>
+    <t>Market Research, Content Creation, Audience Engagement</t>
+  </si>
+  <si>
+    <t>Brand Strategy, Marketing Campaigns</t>
+  </si>
+  <si>
+    <t>Retail, Consumer Goods, Marketing</t>
+  </si>
+  <si>
+    <t>Brand Manager, Marketing Director, Digital Marketing Specialist</t>
+  </si>
+  <si>
+    <t>Consumer Goods, Digital Marketing, Retail</t>
+  </si>
+  <si>
+    <t>Marketing, Branding</t>
+  </si>
+  <si>
+    <t>Brand Building</t>
+  </si>
+  <si>
+    <t>Neural Simulation, Cognitive Modeling, Brain Network Analysis</t>
+  </si>
+  <si>
+    <t>Neuroscience, AI, Computer Science</t>
+  </si>
+  <si>
+    <t>Brain Models, Cognitive Simulations</t>
+  </si>
+  <si>
+    <t>Healthcare, Research, AI</t>
+  </si>
+  <si>
+    <t>Neuroscientist, Simulation Scientist, Computational Neuroscientist</t>
+  </si>
+  <si>
+    <t>Healthcare, Cognitive Science, AI Research</t>
+  </si>
+  <si>
+    <t>Neuroscience, AI, Simulation</t>
+  </si>
+  <si>
+    <t>Scientific &amp; Technical Skill</t>
+  </si>
+  <si>
+    <t>Brain Simulation</t>
+  </si>
+  <si>
+    <t>Neural Connectivity, Computational Neuroscience, Brain Mapping</t>
+  </si>
+  <si>
+    <t>Neural Networks, Brain Simulation</t>
+  </si>
+  <si>
+    <t>Healthcare, AI, Research</t>
+  </si>
+  <si>
+    <t>Neuroscientist, AI Researcher, Cognitive Systems Engineer</t>
+  </si>
+  <si>
+    <t>Healthcare, AI Research, Cognitive Science</t>
+  </si>
+  <si>
+    <t>Neuroscience, Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>Brain Networks</t>
+  </si>
+  <si>
+    <t>Firmware Programming, System Initialization, Low-Level Debugging</t>
+  </si>
+  <si>
+    <t>Computer Science, Electrical Engineering</t>
+  </si>
+  <si>
+    <t>Bootloading Software, Embedded Systems</t>
+  </si>
+  <si>
+    <t>Electronics, Automotive, Software Development</t>
+  </si>
+  <si>
+    <t>Firmware Engineer, Embedded Systems Developer, Bootloader Engineer</t>
+  </si>
+  <si>
+    <t>Firmware Development, Electronics, Automotive</t>
+  </si>
+  <si>
+    <t>Embedded Systems, Software Engineering</t>
+  </si>
+  <si>
+    <t>Bootloaders</t>
+  </si>
+  <si>
+    <t>Bonding Techniques, Adhesive Application, Surface Interaction</t>
+  </si>
+  <si>
+    <t>Materials Science, Electrical Engineering</t>
+  </si>
+  <si>
+    <t>Semiconductor Devices, Microelectronics</t>
+  </si>
+  <si>
+    <t>Electronics, Manufacturing</t>
+  </si>
+  <si>
+    <t>Process Engineer, Materials Scientist, Electronics Engineer</t>
+  </si>
+  <si>
+    <t>Semiconductor Manufacturing, Electronics Assembly</t>
+  </si>
+  <si>
+    <t>Materials Science, Electronics</t>
+  </si>
+  <si>
+    <t>Bonding Technology</t>
+  </si>
+  <si>
+    <t>Schematic Design, Signal Integrity, PCB Layout</t>
+  </si>
+  <si>
+    <t>Electrical Engineering, Computer Engineering</t>
+  </si>
+  <si>
+    <t>PCB Design, Embedded Systems</t>
+  </si>
+  <si>
+    <t>Electronics, Automotive, Telecommunications</t>
+  </si>
+  <si>
+    <t>Hardware Engineer, PCB Designer, Electronics Designer</t>
+  </si>
+  <si>
+    <t>Consumer Electronics, Telecommunications, Automotive</t>
+  </si>
+  <si>
+    <t>Electronics, Hardware Engineering</t>
+  </si>
+  <si>
+    <t>Board-Level Design</t>
+  </si>
+  <si>
+    <t>Signal Testing, Circuit Troubleshooting, Debugging Techniques</t>
+  </si>
+  <si>
+    <t>Electrical Engineering, Computer Science</t>
+  </si>
+  <si>
+    <t>Circuit Debugging, Microcontrollers</t>
+  </si>
+  <si>
+    <t>Electronics, Telecommunications, Technology</t>
+  </si>
+  <si>
+    <t>Hardware Engineer, Embedded Systems Engineer, Debugging Specialist</t>
+  </si>
+  <si>
+    <t>Electronics Manufacturing, Hardware Development</t>
+  </si>
+  <si>
+    <t>Electronics, Embedded Systems, Debugging</t>
+  </si>
+  <si>
+    <t>Board-Level Debugging</t>
+  </si>
+  <si>
+    <t>Encryption, Threat Detection, Security Auditing, Penetration Testing</t>
+  </si>
+  <si>
+    <t>Computer Science, Cryptography, Cybersecurity</t>
+  </si>
+  <si>
+    <t>Secure Transactions, Smart Contracts</t>
+  </si>
+  <si>
+    <t>Technology, Finance, Cybersecurity</t>
+  </si>
+  <si>
+    <t>Blockchain Security Engineer, Security Analyst, Cryptography Expert</t>
+  </si>
+  <si>
+    <t>Finance, Technology, Cryptocurrency</t>
+  </si>
+  <si>
+    <t>Cybersecurity, Blockchain</t>
+  </si>
+  <si>
+    <t>Blockchain Security</t>
+  </si>
+  <si>
+    <t>Network Optimization, Consensus Algorithms, Scaling Solutions</t>
+  </si>
+  <si>
+    <t>Computer Science, Cryptography, Mathematics</t>
+  </si>
+  <si>
+    <t>Blockchain Networks, Cryptocurrencies</t>
+  </si>
+  <si>
+    <t>Technology, Finance, Cryptocurrency</t>
+  </si>
+  <si>
+    <t>Blockchain Engineer, Distributed Systems Architect, Solutions Architect</t>
+  </si>
+  <si>
+    <t>Blockchain, Distributed Systems</t>
+  </si>
+  <si>
+    <t>Blockchain Scaling</t>
+  </si>
+  <si>
+    <t>Blockchain Development, Network Design, Platform Architecture</t>
+  </si>
+  <si>
+    <t>Computer Science, Engineering, Mathematics</t>
+  </si>
+  <si>
+    <t>Blockchain Networks, Decentralized Apps</t>
+  </si>
+  <si>
+    <t>Technology, Finance, Decentralized Apps</t>
+  </si>
+  <si>
+    <t>Blockchain Developer, Platform Engineer, Technical Architect</t>
+  </si>
+  <si>
+    <t>Finance, Technology, Decentralized Applications</t>
+  </si>
+  <si>
+    <t>Blockchain, Software Engineering</t>
+  </si>
+  <si>
+    <t>Blockchain Platforms</t>
+  </si>
+  <si>
+    <t>System Integration, Blockchain APIs, Software Development</t>
+  </si>
+  <si>
+    <t>Computer Science, Engineering, Business Administration</t>
+  </si>
+  <si>
+    <t>Blockchain Solutions, Legacy System Integration</t>
+  </si>
+  <si>
+    <t>Technology, Finance, Supply Chain</t>
+  </si>
+  <si>
+    <t>Blockchain Integration Specialist, Software Engineer</t>
+  </si>
+  <si>
+    <t>Finance, Technology, Supply Chain</t>
+  </si>
+  <si>
+    <t>Blockchain Integration</t>
+  </si>
+  <si>
+    <t>Transaction Analysis, Fraud Prevention, Blockchain Security</t>
+  </si>
+  <si>
+    <t>Computer Science, Cybersecurity, Finance</t>
+  </si>
+  <si>
+    <t>Fraud Prevention, Transaction Monitoring</t>
+  </si>
+  <si>
+    <t>Finance, Cybersecurity, Technology</t>
+  </si>
+  <si>
+    <t>Blockchain Developer, Fraud Analyst, Security Specialist</t>
+  </si>
+  <si>
+    <t>Finance, Cybersecurity, Banking</t>
+  </si>
+  <si>
+    <t>Blockchain, Security, Fraud Prevention</t>
+  </si>
+  <si>
+    <t>Blockchain for Fraud Detection</t>
+  </si>
+  <si>
+    <t>Regulatory Frameworks, Smart Contract Development, Auditing</t>
+  </si>
+  <si>
+    <t>Computer Science, Law, Business Administration</t>
+  </si>
+  <si>
+    <t>Regulatory Compliance, Smart Contracts</t>
+  </si>
+  <si>
+    <t>Finance, Technology, Legal, Compliance</t>
+  </si>
+  <si>
+    <t>Compliance Engineer, Blockchain Consultant, Regulatory Analyst</t>
+  </si>
+  <si>
+    <t>Finance, Compliance, Legal, Technology</t>
+  </si>
+  <si>
+    <t>Blockchain, Regulatory Technology</t>
+  </si>
+  <si>
+    <t>Blockchain for Compliance</t>
+  </si>
+  <si>
+    <t>Blockchain Development, Smart Contracts, Security Protocols</t>
+  </si>
+  <si>
+    <t>Cryptocurrencies, Distributed Ledgers</t>
+  </si>
+  <si>
+    <t>Blockchain Developer, Cryptography Engineer, Software Engineer</t>
+  </si>
+  <si>
+    <t>Cryptography, Distributed Systems</t>
+  </si>
+  <si>
+    <t>Blockchain</t>
+  </si>
+  <si>
+    <t>Network Analysis, Systems Biology, Data Modeling</t>
+  </si>
+  <si>
+    <t>Biology, Computer Science, Data Science</t>
+  </si>
+  <si>
+    <t>Protein Interaction Networks, Biological Models</t>
+  </si>
+  <si>
+    <t>Healthcare, Research, Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>Bioinformatics Network Analyst, Systems Biologist, Researcher</t>
+  </si>
+  <si>
+    <t>Bioinformatics, Network Analysis</t>
+  </si>
+  <si>
+    <t>Analytical &amp; Technical Skill</t>
+  </si>
+  <si>
+    <t>Biological Networks</t>
+  </si>
+  <si>
+    <t>Data Organization, Data Mining, Bioinformatics Analysis</t>
+  </si>
+  <si>
+    <t>Computer Science, Biology, Data Science</t>
+  </si>
+  <si>
+    <t>Genomic Databases, Medical Data Repositories</t>
+  </si>
+  <si>
+    <t>Healthcare, Biotechnology, Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>Bioinformatics Specialist, Database Administrator, Researcher</t>
+  </si>
+  <si>
+    <t>Healthcare, Pharmaceuticals, Research</t>
+  </si>
+  <si>
+    <t>Bioinformatics, Data Management, Software</t>
+  </si>
+  <si>
+    <t>Biological Databases</t>
+  </si>
+  <si>
+    <t>Database Design, Data Storage, Genomic Data Management</t>
+  </si>
+  <si>
+    <t>Computer Science, Biology, Data Management</t>
+  </si>
+  <si>
+    <t>Medical Data Repositories, Genomic Databases</t>
+  </si>
+  <si>
+    <t>Healthcare, Research, Biotechnology</t>
+  </si>
+  <si>
+    <t>Database Administrator, Bioinformatics Data Manager, Research Scientist</t>
+  </si>
+  <si>
+    <t>Bioinformatics, Data Management</t>
+  </si>
+  <si>
+    <t>Biological Database Management</t>
+  </si>
+  <si>
+    <t>Data Merging, Multi-Source Integration, Biological Data Analysis</t>
+  </si>
+  <si>
+    <t>Genomic Data Integration, Medical Records</t>
+  </si>
+  <si>
+    <t>Data Integration Specialist, Bioinformatics Analyst, Researcher</t>
+  </si>
+  <si>
+    <t>Healthcare, Biotechnology, Research</t>
+  </si>
+  <si>
+    <t>Bioinformatics, Data Science</t>
+  </si>
+  <si>
+    <t>Biological Data Integration</t>
+  </si>
+  <si>
+    <t>Tool Development, Data Analysis, Genomic Data Processing</t>
+  </si>
+  <si>
+    <t>Genomic Research, Medical Data Analysis</t>
+  </si>
+  <si>
+    <t>Bioinformatics Specialist, Data Scientist, Computational Biologist</t>
+  </si>
+  <si>
+    <t>Bioinformatics, Data Science, Software</t>
+  </si>
+  <si>
+    <t>Bioinformatics Tools</t>
+  </si>
+  <si>
+    <t>Database Design, Data Mining, Genomic Data Management</t>
+  </si>
+  <si>
+    <t>Bioinformatics Database Administrator, Data Scientist, Researcher</t>
+  </si>
+  <si>
+    <t>Bioinformatics Databases</t>
+  </si>
+  <si>
+    <t>Algorithm Development, Machine Learning, Data Analysis</t>
+  </si>
+  <si>
+    <t>Computer Science, Biology, Mathematics</t>
+  </si>
+  <si>
+    <t>Genomic Research, Drug Discovery Tools</t>
+  </si>
+  <si>
+    <t>Computational Biologist, Bioinformatics Researcher, Data Scientist</t>
+  </si>
+  <si>
+    <t>Healthcare, Pharmaceuticals, Biotechnology</t>
+  </si>
+  <si>
+    <t>Bioinformatics, Computational Biology</t>
+  </si>
+  <si>
+    <t>Bioinformatics Algorithms</t>
+  </si>
+  <si>
+    <t>Genomic Data Analysis, Statistical Methods, Molecular Biology</t>
+  </si>
+  <si>
+    <t>Genomic Data Analysis, Healthcare Research</t>
+  </si>
+  <si>
+    <t>Bioinformatician, Computational Biologist, Research Scientist</t>
+  </si>
+  <si>
+    <t>Bioinformatics</t>
+  </si>
+  <si>
+    <t>Pattern Recognition, Customer Segmentation, Predictive Modeling</t>
+  </si>
+  <si>
+    <t>Data Science, Psychology, Marketing</t>
+  </si>
+  <si>
+    <t>Customer Insights, Behavioral Data Models</t>
+  </si>
+  <si>
+    <t>Marketing, E-commerce, Technology</t>
+  </si>
+  <si>
+    <t>Data Scientist, Behavioral Analyst, Marketing Specialist</t>
+  </si>
+  <si>
+    <t>E-commerce, Marketing, Consumer Behavior Research</t>
+  </si>
+  <si>
+    <t>Data Science, Marketing, Psychology</t>
+  </si>
+  <si>
+    <t>Analytical Skill</t>
+  </si>
+  <si>
+    <t>Behavioral Analytics</t>
+  </si>
+  <si>
+    <t>Battery Charging, Energy Storage, Power Management</t>
+  </si>
+  <si>
+    <t>Electrical Engineering, Energy Systems, Computer Science</t>
+  </si>
+  <si>
+    <t>Electric Vehicle Batteries, Solar Power Systems</t>
+  </si>
+  <si>
+    <t>Automotive, Energy, Electronics</t>
+  </si>
+  <si>
+    <t>Battery Systems Engineer, Electrical Engineer, Energy Consultant</t>
+  </si>
+  <si>
+    <t>Electric Vehicles, Renewable Energy, Consumer Electronics</t>
+  </si>
+  <si>
+    <t>Engineering, Electronics, Software</t>
+  </si>
+  <si>
+    <t>Battery Management Systems</t>
+  </si>
+  <si>
+    <t>Cloud Solutions, API Development, Regulatory Compliance</t>
+  </si>
+  <si>
+    <t>Business Administration, Software Engineering, Finance</t>
+  </si>
+  <si>
+    <t>Digital Banking Platforms, Financial Services</t>
+  </si>
+  <si>
+    <t>Banking, Fintech, Technology</t>
+  </si>
+  <si>
+    <t>SaaS Architect, Fintech Developer, Business Development Manager</t>
+  </si>
+  <si>
+    <t>Fintech, Digital Banking</t>
+  </si>
+  <si>
+    <t>Finance, SaaS, Software Engineering</t>
+  </si>
+  <si>
+    <t>Business &amp; Technical Skill</t>
+  </si>
+  <si>
+    <t>Banking-as-a-Service</t>
+  </si>
+  <si>
+    <t>Financial Software Development, Security, UX/UI Design</t>
+  </si>
+  <si>
+    <t>Computer Science, Finance, Software Engineering</t>
+  </si>
+  <si>
+    <t>Banking Applications, Payment Systems</t>
+  </si>
+  <si>
+    <t>Software Engineer, Banking Systems Architect, Fintech Developer</t>
+  </si>
+  <si>
+    <t>Banking, Fintech, Payment Systems</t>
+  </si>
+  <si>
+    <t>Software Engineering, Finance</t>
+  </si>
+  <si>
+    <t>Banking Software</t>
+  </si>
+  <si>
+    <t>API Integration, Security, System Interoperability</t>
+  </si>
+  <si>
+    <t>Core Banking Systems, Payment Gateways</t>
+  </si>
+  <si>
+    <t>Integration Specialist, Banking Software Engineer, IT Specialist</t>
+  </si>
+  <si>
+    <t>Finance, Software Engineering</t>
+  </si>
+  <si>
+    <t>Banking Platforms Integration</t>
+  </si>
+  <si>
+    <t>Statistical Modeling, Risk Management, Performance Evaluation</t>
+  </si>
+  <si>
+    <t>Finance, Economics, Data Science</t>
+  </si>
+  <si>
+    <t>Financial Models, Trading Strategies</t>
+  </si>
+  <si>
+    <t>Finance, Investment, Trading</t>
+  </si>
+  <si>
+    <t>Quantitative Analyst, Algorithmic Trader, Data Scientist</t>
+  </si>
+  <si>
+    <t>Trading, Investment, Financial Planning</t>
+  </si>
+  <si>
+    <t>Finance, Data Science, Algorithms</t>
+  </si>
+  <si>
+    <t>Backtesting</t>
+  </si>
+  <si>
+    <t>Machine Learning, Sensor Integration, System Design, Path Planning</t>
+  </si>
+  <si>
+    <t>Robotics, Computer Science, Electrical Engineering</t>
+  </si>
+  <si>
+    <t>Self-Driving Cars, Drones, Robotic Systems</t>
+  </si>
+  <si>
+    <t>Robotics, Automotive, Aerospace, Technology</t>
+  </si>
+  <si>
+    <t>Robotics Engineer, Autonomous Vehicle Engineer, AI Specialist</t>
+  </si>
+  <si>
+    <t>Robotics, Autonomous Vehicles, Aerospace</t>
+  </si>
+  <si>
+    <t>Robotics, AI, Engineering</t>
+  </si>
+  <si>
+    <t>Autonomous Systems</t>
+  </si>
+  <si>
+    <t>Vehicle Diagnostics, Performance Testing, Safety Standards</t>
+  </si>
+  <si>
+    <t>Mechanical Engineering, Automotive Engineering, Testing Methods</t>
+  </si>
+  <si>
+    <t>Vehicle Testing, Crash Simulation, Performance Evaluation</t>
+  </si>
+  <si>
+    <t>Automotive, Engineering</t>
+  </si>
+  <si>
+    <t>Test Engineer, Automotive Engineer, Quality Assurance Specialist</t>
+  </si>
+  <si>
+    <t>Automotive Manufacturing, Research, Development</t>
+  </si>
+  <si>
+    <t>Automotive Engineering, Testing</t>
+  </si>
+  <si>
+    <t>Automotive Testing</t>
+  </si>
+  <si>
+    <t>Systems Design, Integration, Embedded Systems, Diagnostics</t>
+  </si>
+  <si>
+    <t>Mechanical Engineering, Electrical Engineering, Automotive Technology</t>
+  </si>
+  <si>
+    <t>Automotive Components, Infotainment Systems</t>
+  </si>
+  <si>
+    <t>Automotive, Electronics</t>
+  </si>
+  <si>
+    <t>Automotive Engineer, Systems Engineer, Electronics Engineer</t>
+  </si>
+  <si>
+    <t>Automotive Design, Automotive Manufacturing</t>
+  </si>
+  <si>
+    <t>Automotive Engineering, Electronics</t>
+  </si>
+  <si>
+    <t>Automotive Systems</t>
+  </si>
+  <si>
+    <t>Safety Protocols, Regulatory Standards, Vehicle Testing</t>
+  </si>
+  <si>
+    <t>Mechanical Engineering, Automotive Engineering, Law</t>
+  </si>
+  <si>
+    <t>Vehicle Safety Systems, Compliance Testing</t>
+  </si>
+  <si>
+    <t>Automotive, Engineering, Compliance</t>
+  </si>
+  <si>
+    <t>Safety Engineer, Regulatory Compliance Officer, Automotive Engineer</t>
+  </si>
+  <si>
+    <t>Automotive Manufacturing, Automotive Design</t>
+  </si>
+  <si>
+    <t>Automotive, Safety, Compliance</t>
+  </si>
+  <si>
+    <t>Regulatory &amp; Technical Skill</t>
+  </si>
+  <si>
+    <t>Automotive Safety Standards</t>
+  </si>
+  <si>
+    <t>Scripting, Process Automation, Tool Development, Integration</t>
+  </si>
+  <si>
+    <t>Testing Tools, Automation Frameworks</t>
+  </si>
+  <si>
+    <t>IT, Software, Manufacturing</t>
+  </si>
+  <si>
+    <t>Automation Developer, Software Engineer, Tools Specialist</t>
+  </si>
+  <si>
+    <t>IT, Software Development, Manufacturing</t>
+  </si>
+  <si>
+    <t>Software Engineering, Automation, Tools</t>
+  </si>
+  <si>
+    <t>Automation Tools</t>
+  </si>
+  <si>
+    <t>Robotics, Control Theory, System Design, Automation Technology</t>
+  </si>
+  <si>
+    <t>Mechanical Engineering, Electrical Engineering</t>
+  </si>
+  <si>
+    <t>Automated Production Lines, Robotics, Control Systems</t>
+  </si>
+  <si>
+    <t>Manufacturing, Aerospace, Energy, Robotics</t>
+  </si>
+  <si>
+    <t>Automation Engineer, Robotics Engineer, System Integrator</t>
+  </si>
+  <si>
+    <t>Manufacturing, Automotive, Energy, Aerospace</t>
+  </si>
+  <si>
+    <t>Engineering, Robotics, Control Systems</t>
+  </si>
+  <si>
+    <t>Automation Systems</t>
+  </si>
+  <si>
+    <t>Test Automation, Hardware Testing, Software Integration</t>
+  </si>
+  <si>
+    <t>Electrical Engineering, Computer Science, Physics</t>
+  </si>
+  <si>
+    <t>Testing Systems, Circuit Boards, Validation</t>
+  </si>
+  <si>
+    <t>Electronics, Aerospace, Automotive</t>
+  </si>
+  <si>
+    <t>Test Engineer, ATE Engineer, Electronics Engineer</t>
+  </si>
+  <si>
+    <t>Electronics Manufacturing, Aerospace, Automotive</t>
+  </si>
+  <si>
+    <t>Electronics, Testing, Engineering</t>
+  </si>
+  <si>
+    <t>Automated Test Equipment</t>
+  </si>
+  <si>
+    <t>Robotics, Process Optimization, Mechatronics, System Integration</t>
+  </si>
+  <si>
+    <t>Production Lines, Robotics Systems</t>
+  </si>
+  <si>
+    <t>Manufacturing, Automotive, Electronics</t>
+  </si>
+  <si>
+    <t>Automation Engineer, Robotics Engineer, Manufacturing Engineer</t>
+  </si>
+  <si>
+    <t>Manufacturing, Automotive, Consumer Electronics</t>
+  </si>
+  <si>
+    <t>Manufacturing, Robotics</t>
+  </si>
+  <si>
+    <t>Automated Assembly</t>
+  </si>
+  <si>
+    <t>Encryption, Access Control, Protocol Analysis, Identity Management</t>
+  </si>
+  <si>
+    <t>Computer Science, Network Engineering, Cybersecurity</t>
+  </si>
+  <si>
+    <t>Security Systems, Cloud Authentication</t>
+  </si>
+  <si>
+    <t>Technology, Cybersecurity, IT</t>
+  </si>
+  <si>
+    <t>Security Engineer, Network Engineer, Cybersecurity Analyst</t>
+  </si>
+  <si>
+    <t>Web Development, Cloud Computing, IT Security</t>
+  </si>
+  <si>
+    <t>Cybersecurity, Networking</t>
+  </si>
+  <si>
+    <t>Authentication Protocols</t>
+  </si>
+  <si>
+    <t>Internal Control Frameworks, Risk Assessment, Regulatory Knowledge</t>
+  </si>
+  <si>
+    <t>Accounting, Finance, Business Administration</t>
+  </si>
+  <si>
+    <t>Audit Processes, Compliance Testing</t>
+  </si>
+  <si>
+    <t>Finance, Healthcare, Government, Corporate</t>
+  </si>
+  <si>
+    <t>Auditor, Risk Analyst, Compliance Specialist</t>
+  </si>
+  <si>
+    <t>Finance, Government, Healthcare, Corporate</t>
+  </si>
+  <si>
+    <t>Audit, Risk Management, Compliance</t>
+  </si>
+  <si>
+    <t>Audit Methodologies</t>
+  </si>
+  <si>
+    <t>Coordination, Risk Assessment, Documentation, Regulatory Knowledge</t>
+  </si>
+  <si>
+    <t>Business Administration, Finance, Accounting</t>
+  </si>
+  <si>
+    <t>Audit Processes, Risk Management</t>
+  </si>
+  <si>
+    <t>Audit Manager, Audit Coordinator, Compliance Officer</t>
+  </si>
+  <si>
+    <t>Audit Coordination</t>
+  </si>
+  <si>
+    <t>Numerical Weather Prediction, Data Assimilation, Climate Modeling</t>
+  </si>
+  <si>
+    <t>Environmental Science, Atmospheric Science, Physics</t>
+  </si>
+  <si>
+    <t>Weather Forecasting, Climate Simulations</t>
+  </si>
+  <si>
+    <t>Environmental Science, Aerospace, Research</t>
+  </si>
+  <si>
+    <t>Atmospheric Scientist, Meteorologist, Climate Modeler</t>
+  </si>
+  <si>
+    <t>Meteorology, Climate Science, Aerospace</t>
+  </si>
+  <si>
+    <t>Atmospheric Science, Environmental Science</t>
+  </si>
+  <si>
+    <t>Atmospheric Modeling</t>
+  </si>
+  <si>
+    <t>Troubleshooting, Maintenance Protocols, Diagnostics</t>
+  </si>
+  <si>
+    <t>Test Equipment, Circuit Boards, Diagnostic Systems</t>
+  </si>
+  <si>
+    <t>Electronics, Aerospace, Manufacturing</t>
+  </si>
+  <si>
+    <t>Maintenance Technician, ATE Engineer, Repair Specialist</t>
+  </si>
+  <si>
+    <t>Manufacturing, Aerospace, Electronics Repair</t>
+  </si>
+  <si>
+    <t>Electronics, Maintenance, Engineering</t>
+  </si>
+  <si>
+    <t>ATE Equipment Maintenance</t>
+  </si>
+  <si>
+    <t>Testing Systems, Electronics Validation</t>
+  </si>
+  <si>
+    <t>ATE</t>
+  </si>
+  <si>
+    <t>2-3 years (intermediate to advanced expertise)</t>
+  </si>
+  <si>
+    <t>Theoretical Physics, Research, Data Analysis, Observation Methods</t>
+  </si>
+  <si>
+    <t>Physics, Mathematics, Astronomy</t>
+  </si>
+  <si>
+    <t>Space Research, Scientific Discoveries</t>
+  </si>
+  <si>
+    <t>Research, Space Science, Education</t>
+  </si>
+  <si>
+    <t>Astrophysicist, Research Scientist, Educator</t>
+  </si>
+  <si>
+    <t>Research, Education, Space Exploration</t>
+  </si>
+  <si>
+    <t>Physics, Space Science</t>
+  </si>
+  <si>
+    <t>Scientific Skill</t>
+  </si>
+  <si>
+    <t>Astrophysics</t>
+  </si>
+  <si>
+    <t>Simulation Software, Numerical Methods, High-Performance Computing</t>
+  </si>
+  <si>
+    <t>Physics, Computer Science, Mathematics</t>
+  </si>
+  <si>
+    <t>Computational Models, Simulation Software</t>
+  </si>
+  <si>
+    <t>Astrophysicist, Simulation Specialist, Research Scientist</t>
+  </si>
+  <si>
+    <t>Research, Space Science, Simulations</t>
+  </si>
+  <si>
+    <t>Astrophysics, Computational Science</t>
+  </si>
+  <si>
+    <t>Astrophysical Simulations</t>
+  </si>
+  <si>
+    <t>Numerical Simulation, Mathematical Modeling, Computational Physics</t>
+  </si>
+  <si>
+    <t>Physics, Mathematics, Computer Science</t>
+  </si>
+  <si>
+    <t>Space Simulations, Astrophysical Models</t>
+  </si>
+  <si>
+    <t>Astrophysicist, Computational Scientist, Researcher</t>
+  </si>
+  <si>
+    <t>Space Research, Simulation, Education</t>
+  </si>
+  <si>
+    <t>Astrophysics, Computational Modeling</t>
+  </si>
+  <si>
+    <t>Astrophysical Modeling</t>
+  </si>
+  <si>
+    <t>Data Parsing, Format Conversion, Data Storage Systems</t>
+  </si>
+  <si>
+    <t>Computer Science, Astronomy, Data Science</t>
+  </si>
+  <si>
+    <t>Space Observations, Data Analysis</t>
+  </si>
+  <si>
+    <t>Research, Space Science, Astronomy</t>
+  </si>
+  <si>
+    <t>Data Scientist, Researcher, Software Developer</t>
+  </si>
+  <si>
+    <t>Space Research, Data Science, Astrophysics</t>
+  </si>
+  <si>
+    <t>Data Science, Astronomy, Software Engineering</t>
+  </si>
+  <si>
+    <t>Astronomy Data Formats</t>
+  </si>
+  <si>
+    <t>Celestial Observation, Telescope Operation, Research Methods</t>
+  </si>
+  <si>
+    <t>Physics, Astronomy, Mathematics</t>
+  </si>
+  <si>
+    <t>Space Research, Telescopes, Space Missions</t>
+  </si>
+  <si>
+    <t>Astronomer, Astrophysicist, Research Scientist</t>
+  </si>
+  <si>
+    <t>Space Science, Physics</t>
+  </si>
+  <si>
+    <t>Astronomy</t>
+  </si>
+  <si>
+    <t>Market Analysis, Discounted Cash Flow, Comparable Analysis</t>
+  </si>
+  <si>
+    <t>Finance, Economics, Real Estate</t>
+  </si>
+  <si>
+    <t>Investment Valuation, Property Valuation</t>
+  </si>
+  <si>
+    <t>Finance, Real Estate, Private Equity</t>
+  </si>
+  <si>
+    <t>Valuation Analyst, Financial Analyst, Real Estate Appraiser</t>
+  </si>
+  <si>
+    <t>Real Estate, Private Equity, Public Markets</t>
+  </si>
+  <si>
+    <t>Finance, Real Estate, Investment</t>
+  </si>
+  <si>
+    <t>Financial Skill</t>
+  </si>
+  <si>
+    <t>Asset Valuation</t>
+  </si>
+  <si>
+    <t>Risk Management, Portfolio Diversification, Statistical Analysis</t>
+  </si>
+  <si>
+    <t>Finance, Economics, Mathematics</t>
+  </si>
+  <si>
+    <t>Investment Portfolios, Risk Management</t>
+  </si>
+  <si>
+    <t>Finance, Investment, Wealth Management</t>
+  </si>
+  <si>
+    <t>Portfolio Manager, Financial Analyst, Investment Advisor</t>
+  </si>
+  <si>
+    <t>Hedge Funds, Wealth Management, Financial Planning</t>
+  </si>
+  <si>
+    <t>Finance, Investment Management</t>
+  </si>
+  <si>
+    <t>Asset Allocation</t>
+  </si>
+  <si>
+    <t>Formal Verification, Test Automation, Debugging, Model Checking</t>
+  </si>
+  <si>
+    <t>Electrical Engineering, Computer Science, Software Engineering</t>
+  </si>
+  <si>
+    <t>Verification Tools, Testbenches, Simulation Models</t>
+  </si>
+  <si>
+    <t>Electronics, Software Engineering</t>
+  </si>
+  <si>
+    <t>Verification Engineer, Embedded Systems Engineer, Hardware Engineer</t>
+  </si>
+  <si>
+    <t>Semiconductor Design, Embedded Systems, Software Development</t>
+  </si>
+  <si>
+    <t>Software Verification, Hardware Design</t>
+  </si>
+  <si>
+    <t>Assertion-Based Verification</t>
+  </si>
+  <si>
+    <t>Formal Methods, Hardware Verification, Test Automation</t>
+  </si>
+  <si>
+    <t>Design Verification, Testbenches</t>
+  </si>
+  <si>
+    <t>Verification Engineer, Hardware Engineer, Software Tester</t>
+  </si>
+  <si>
+    <t>Embedded Systems, Semiconductor Design, Formal Verification</t>
+  </si>
+  <si>
+    <t>Software Engineering, Verification</t>
+  </si>
+  <si>
+    <t>Assertion Languages</t>
+  </si>
+  <si>
+    <t>Circuit Design, Hardware Description Languages, Optimization Techniques</t>
+  </si>
+  <si>
+    <t>Integrated Circuits, Consumer Electronics</t>
+  </si>
+  <si>
+    <t>Electronics, Telecommunications, Computing</t>
+  </si>
+  <si>
+    <t>ASIC Engineer, Hardware Engineer, System-on-Chip (SoC) Designer</t>
+  </si>
+  <si>
+    <t>Telecommunications, Consumer Electronics, Computing</t>
+  </si>
+  <si>
+    <t>Electronics, Hardware Design</t>
+  </si>
+  <si>
+    <t>ASIC Design</t>
+  </si>
+  <si>
+    <t>ARM Assembly, Processor Design, Low-Level Programming</t>
+  </si>
+  <si>
+    <t>Mobile Devices, Embedded Systems</t>
+  </si>
+  <si>
+    <t>Electronics, Consumer Electronics, Mobile</t>
+  </si>
+  <si>
+    <t>Embedded Systems Engineer, Hardware Engineer, Firmware Developer</t>
+  </si>
+  <si>
+    <t>Mobile Devices, Embedded Systems, Consumer Electronics</t>
+  </si>
+  <si>
+    <t>ARM Architecture</t>
+  </si>
+  <si>
+    <t>Theoretical Analysis, Approximation Methods, Proofs of Bounds</t>
+  </si>
+  <si>
+    <t>Mathematics, Computer Science, Operations Research</t>
+  </si>
+  <si>
+    <t>Computational Models, Optimization Algorithms</t>
+  </si>
+  <si>
+    <t>Mathematics, Technology, Research</t>
+  </si>
+  <si>
+    <t>Researcher, Algorithm Developer, Data Scientist</t>
+  </si>
+  <si>
+    <t>AI, Operations Research, Data Science</t>
+  </si>
+  <si>
+    <t>Mathematics, Algorithms</t>
+  </si>
+  <si>
+    <t>Approximation Theory</t>
+  </si>
+  <si>
+    <t>Algorithm Design, Approximation Techniques, Computational Complexity</t>
+  </si>
+  <si>
+    <t>Computer Science, Mathematics, Operations Research</t>
+  </si>
+  <si>
+    <t>Optimization Problems, Computational Models</t>
+  </si>
+  <si>
+    <t>Technology, Research, AI, Operations Research</t>
+  </si>
+  <si>
+    <t>Algorithm Engineer, Data Scientist, Researcher</t>
+  </si>
+  <si>
+    <t>Machine Learning, Data Science, Operations Research</t>
+  </si>
+  <si>
+    <t>Algorithms, Computer Science, Optimization</t>
+  </si>
+  <si>
+    <t>Approximation Algorithms</t>
+  </si>
+  <si>
+    <t>Time Management, Database Design, User Interface Design</t>
+  </si>
+  <si>
+    <t>Computer Science, Business Administration</t>
+  </si>
+  <si>
+    <t>Appointment Scheduling Systems, Calendar Apps</t>
+  </si>
+  <si>
+    <t>Healthcare, Education, Business Services</t>
+  </si>
+  <si>
+    <t>Scheduling Software Developer, Operations Coordinator, IT Specialist</t>
+  </si>
+  <si>
+    <t>Healthcare, Business Services, Education</t>
+  </si>
+  <si>
+    <t>Software Development, Business Operations</t>
+  </si>
+  <si>
+    <t>Appointment Scheduling</t>
+  </si>
+  <si>
+    <t>Software Design, Debugging, System Integration, User Experience</t>
+  </si>
+  <si>
+    <t>Computer Science, Engineering, Product Design</t>
+  </si>
+  <si>
+    <t>Software Applications, Embedded Systems</t>
+  </si>
+  <si>
+    <t>Technology, Electronics, Consumer Goods</t>
+  </si>
+  <si>
+    <t>Application Engineer, Software Engineer, Systems Engineer</t>
+  </si>
+  <si>
+    <t>SaaS, Embedded Systems, Consumer Electronics</t>
+  </si>
+  <si>
+    <t>Software Engineering, Product Design</t>
+  </si>
+  <si>
+    <t>Application Engineering</t>
+  </si>
+  <si>
+    <t>Programming, UI/UX Design, Databases, Problem Solving</t>
+  </si>
+  <si>
+    <t>Mobile Applications, Web Platforms</t>
+  </si>
+  <si>
+    <t>Technology, Mobile, Web Development</t>
+  </si>
+  <si>
+    <t>Software Developer, Mobile Developer, Full Stack Developer</t>
+  </si>
+  <si>
+    <t>Mobile Apps, Web Apps, Enterprise Software</t>
+  </si>
+  <si>
+    <t>Software Engineering, Web Development</t>
+  </si>
+  <si>
+    <t>Application Development</t>
+  </si>
+  <si>
+    <t>Encryption, Authentication, Access Control, Security Protocols</t>
+  </si>
+  <si>
+    <t>Computer Science, Cybersecurity</t>
+  </si>
+  <si>
+    <t>Web Applications, API Security Systems</t>
+  </si>
+  <si>
+    <t>Technology, Cybersecurity, Cloud Computing</t>
+  </si>
+  <si>
+    <t>Security Engineer, API Security Specialist, Backend Developer</t>
+  </si>
+  <si>
+    <t>Web Development, Cloud Computing, SaaS</t>
+  </si>
+  <si>
+    <t>Cybersecurity, Software Engineering</t>
+  </si>
+  <si>
+    <t>API Security</t>
+  </si>
+  <si>
+    <t>API Design, Authentication, Load Balancing, Service Integration</t>
+  </si>
+  <si>
+    <t>Computer Science, Software Engineering, Networking</t>
+  </si>
+  <si>
+    <t>Web Applications, Cloud Services, Microservices</t>
+  </si>
+  <si>
+    <t>Technology, Cloud Computing, SaaS</t>
+  </si>
+  <si>
+    <t>API Engineer, Backend Developer, Cloud Solutions Architect</t>
+  </si>
+  <si>
+    <t>Web Development, Cloud Applications, SaaS</t>
+  </si>
+  <si>
+    <t>Software Engineering, Cloud Computing, Networking</t>
+  </si>
+  <si>
+    <t>API Gateways</t>
+  </si>
+  <si>
+    <t>RF Design, Antenna Modeling, Wireless Communication</t>
+  </si>
+  <si>
+    <t>Electrical Engineering, Physics, Telecommunications</t>
+  </si>
+  <si>
+    <t>Communication Systems, Wireless Networks</t>
+  </si>
+  <si>
+    <t>Telecommunications, Aerospace, Electronics</t>
+  </si>
+  <si>
+    <t>RF Engineer, Antenna Engineer, Communications Systems Engineer</t>
+  </si>
+  <si>
+    <t>Telecommunications, Aerospace, Consumer Electronics</t>
+  </si>
+  <si>
+    <t>Electronics, Communication Systems, Engineering</t>
+  </si>
+  <si>
+    <t>Antenna Design</t>
+  </si>
+  <si>
+    <t>Analog-to-Digital Conversion, Signal Processing, Data Acquisition</t>
+  </si>
+  <si>
+    <t>Electrical Engineering, Physics, Computer Engineering</t>
+  </si>
+  <si>
+    <t>ADCs, Communication Systems, Consumer Electronics</t>
+  </si>
+  <si>
+    <t>Electronics, Telecommunications, Audio</t>
+  </si>
+  <si>
+    <t>Electronics Engineer, Signal Processing Engineer, Embedded Systems Developer</t>
+  </si>
+  <si>
+    <t>Audio Systems, Communication Systems, Consumer Electronics</t>
+  </si>
+  <si>
+    <t>Electronics, Signal Processing, Data Acquisition</t>
+  </si>
+  <si>
+    <t>Analog-to-Digital Conversion</t>
+  </si>
+  <si>
+    <t>Circuit Design, Signal Integrity, Frequency Response</t>
+  </si>
+  <si>
+    <t>Audio Devices, Communication Systems, Consumer Electronics</t>
+  </si>
+  <si>
+    <t>Circuit Designer, Electronics Engineer, Embedded Systems Engineer</t>
+  </si>
+  <si>
+    <t>Electronics, Circuit Design</t>
+  </si>
+  <si>
+    <t>Analog Circuit Design</t>
+  </si>
+  <si>
+    <t>Circuit Design, Signal Processing, Mixed-Signal Systems</t>
+  </si>
+  <si>
+    <t>Consumer Electronics, Communication Devices</t>
+  </si>
+  <si>
+    <t>Consumer Electronics, Automotive, Telecommunications</t>
+  </si>
+  <si>
+    <t>Electronics, Circuit Design, Engineering</t>
+  </si>
+  <si>
+    <t>Analog and Digital Design</t>
+  </si>
+  <si>
+    <t>Signal Amplification, Circuit Design, Frequency Response</t>
+  </si>
+  <si>
+    <t>Electrical Engineering, Audio Engineering</t>
+  </si>
+  <si>
+    <t>Audio Amplifiers, Communication Systems</t>
+  </si>
+  <si>
+    <t>Electronics Engineer, Audio Engineer, Signal Processing Engineer</t>
+  </si>
+  <si>
+    <t>Audio Systems, Telecommunications, Consumer Electronics</t>
+  </si>
+  <si>
+    <t>Electronics, Signal Processing</t>
+  </si>
+  <si>
+    <t>Amplifiers</t>
+  </si>
+  <si>
+    <t>Regulatory Knowledge, Risk Assessment, Investigation Techniques</t>
+  </si>
+  <si>
+    <t>Finance, Law, Risk Management</t>
+  </si>
+  <si>
+    <t>Anti-Money Laundering Systems, Risk Management</t>
+  </si>
+  <si>
+    <t>Finance, Banking, Regulatory Compliance</t>
+  </si>
+  <si>
+    <t>Compliance Officer, Risk Analyst, AML Specialist</t>
+  </si>
+  <si>
+    <t>Banking, Finance, Compliance, Security</t>
+  </si>
+  <si>
+    <t>Finance, Compliance, Risk Management</t>
+  </si>
+  <si>
+    <t>Regulatory &amp; Analytical Skill</t>
+  </si>
+  <si>
+    <t>AML</t>
+  </si>
+  <si>
+    <t>FPGA Programming, Hardware Design, Circuit Design</t>
+  </si>
+  <si>
+    <t>Electrical Engineering, Computer Engineering, Physics</t>
+  </si>
+  <si>
+    <t>Embedded Systems, Hardware Acceleration</t>
+  </si>
+  <si>
+    <t>Technology, Telecommunications, Electronics</t>
+  </si>
+  <si>
+    <t>FPGA Engineer, Hardware Engineer, Embedded Systems Developer</t>
+  </si>
+  <si>
+    <t>Electronics, Hardware Engineering, Programming</t>
+  </si>
+  <si>
+    <t>Altera/Intel FPGA</t>
+  </si>
+  <si>
+    <t>Chemoinformatics, Pattern Recognition, Statistical Analysis</t>
+  </si>
+  <si>
+    <t>Chemistry, Computer Science, Biostatistics</t>
+  </si>
+  <si>
+    <t>Chemical Data Models, Drug Discovery Tools</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals, Biotech, Chemistry</t>
+  </si>
+  <si>
+    <t>Data Scientist, Chemoinformatics Specialist, Research Scientist</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals, Biotechnology, Chemical Engineering</t>
+  </si>
+  <si>
+    <t>Data Science, Chemistry, Machine Learning</t>
+  </si>
+  <si>
+    <t>Algorithms for Chemical Data</t>
+  </si>
+  <si>
+    <t>Data Analysis, Statistical Modeling, Market Knowledge</t>
+  </si>
+  <si>
+    <t>Finance, Computer Science, Mathematics</t>
+  </si>
+  <si>
+    <t>Trading Algorithms, Financial Models, Market Analytics</t>
+  </si>
+  <si>
+    <t>Finance, Technology, Trading</t>
+  </si>
+  <si>
+    <t>Financial Markets, Hedge Funds, Trading Platforms</t>
+  </si>
+  <si>
+    <t>Finance, Data Science, Software Engineering</t>
+  </si>
+  <si>
+    <t>Algorithmic Trading</t>
+  </si>
+  <si>
+    <t>Critical Thinking, Logical Reasoning, Programming Skills</t>
+  </si>
+  <si>
+    <t>Computer Science, Mathematics, Engineering</t>
+  </si>
+  <si>
+    <t>Coding Competitions, AI Models, Optimization</t>
+  </si>
+  <si>
+    <t>Technology, Finance, Research, AI</t>
+  </si>
+  <si>
+    <t>Software Engineer, Data Scientist, Algorithm Developer</t>
+  </si>
+  <si>
+    <t>Software Development, Competitive Programming, AI</t>
+  </si>
+  <si>
+    <t>Problem Solving, Computer Science</t>
+  </si>
+  <si>
+    <t>Algorithmic Problem Solving</t>
+  </si>
+  <si>
+    <t>Complexity Theory, Algorithmic Design, Data Structures</t>
+  </si>
+  <si>
+    <t>Computer Science, Mathematics</t>
+  </si>
+  <si>
+    <t>Algorithm Optimization, Complexity Analysis</t>
+  </si>
+  <si>
+    <t>Technology, Research, AI, Academia</t>
+  </si>
+  <si>
+    <t>Algorithm Engineer, Data Scientist, Software Engineer</t>
+  </si>
+  <si>
+    <t>Software Development, Research, AI</t>
+  </si>
+  <si>
+    <t>Algorithmic Complexity</t>
+  </si>
+  <si>
+    <t>Fairness Audits, Algorithmic Evaluation, Bias Metrics</t>
+  </si>
+  <si>
+    <t>Computer Science, Ethics, Social Science</t>
+  </si>
+  <si>
+    <t>AI Models, Bias Detection Systems</t>
+  </si>
+  <si>
+    <t>Technology, Ethics, Data Science</t>
+  </si>
+  <si>
+    <t>AI Researcher, Data Scientist, Ethicist, Policy Analyst</t>
+  </si>
+  <si>
+    <t>AI, Machine Learning, Social Sciences</t>
+  </si>
+  <si>
+    <t>Data Science, Ethics, AI</t>
+  </si>
+  <si>
+    <t>Algorithmic Bias Analysis</t>
+  </si>
+  <si>
+    <t>Bias Detection, Fairness in AI, Ethical Decision Making</t>
+  </si>
+  <si>
+    <t>AI Models, Machine Learning Systems</t>
+  </si>
+  <si>
+    <t>AI Researcher, Data Scientist, Ethicist</t>
+  </si>
+  <si>
+    <t>Algorithmic Bias</t>
+  </si>
+  <si>
+    <t>Problem Solving, Optimization, Data Structures, Programming</t>
+  </si>
+  <si>
+    <t>Software Algorithms, Data Processing, AI Models</t>
+  </si>
+  <si>
+    <t>Technology, Finance, AI, Data Science</t>
+  </si>
+  <si>
+    <t>Software Engineer, Data Scientist, Algorithm Engineer</t>
+  </si>
+  <si>
+    <t>Software Development, Machine Learning, Data Science</t>
+  </si>
+  <si>
+    <t>Algorithm Development</t>
+  </si>
+  <si>
+    <t>Machine Learning, Pattern Recognition, Data Analytics</t>
+  </si>
+  <si>
+    <t>Computer Science, Data Science, Engineering</t>
+  </si>
+  <si>
+    <t>Fraud Detection Systems, Security Software</t>
+  </si>
+  <si>
+    <t>Finance, Cybersecurity, E-commerce</t>
+  </si>
+  <si>
+    <t>Data Scientist, AI Engineer, Fraud Analyst</t>
+  </si>
+  <si>
+    <t>Finance, E-commerce, Banking, Cybersecurity</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Data Science</t>
+  </si>
+  <si>
+    <t>AI for Fraud Detection</t>
+  </si>
+  <si>
+    <t>3D Modeling, Thermal Management, Structural Integrity</t>
+  </si>
+  <si>
+    <t>Mechanical Engineering, Materials Science</t>
+  </si>
+  <si>
+    <t>Microelectronics, Consumer Electronics</t>
+  </si>
+  <si>
+    <t>Manufacturing, Electronics, Consumer Goods</t>
+  </si>
+  <si>
+    <t>Packaging Engineer, Process Engineer, Materials Scientist</t>
+  </si>
+  <si>
+    <t>Electronics, Semiconductor, Consumer Goods</t>
+  </si>
+  <si>
+    <t>Engineering, Manufacturing</t>
+  </si>
+  <si>
+    <t>Advanced Packaging</t>
+  </si>
+  <si>
+    <t>Analog to Digital Conversion, Signal Processing, Circuit Design</t>
+  </si>
+  <si>
+    <t>Electrical Engineering, Signal Processing</t>
+  </si>
+  <si>
+    <t>Audio Devices, Communication Systems</t>
+  </si>
+  <si>
+    <t>Telecommunications, Consumer Electronics</t>
+  </si>
+  <si>
+    <t>Electronics Engineer, Signal Processing Engineer</t>
+  </si>
+  <si>
+    <t>Telecommunications, Audio/Video, Consumer Electronics</t>
+  </si>
+  <si>
+    <t>ADC/DAC</t>
+  </si>
+  <si>
+    <t>Data Management, Security Protocols, Database Design</t>
+  </si>
+  <si>
+    <t>Information Technology, Computer Science</t>
+  </si>
+  <si>
+    <t>Data Security, Information Management</t>
+  </si>
+  <si>
+    <t>Finance, Healthcare, Telecommunications</t>
+  </si>
+  <si>
+    <t>IT Specialist, Account Information Manager, Data Analyst</t>
+  </si>
+  <si>
+    <t>Banking, Healthcare, Telecom, Finance</t>
+  </si>
+  <si>
+    <t>IT Services, Data Management, Security</t>
+  </si>
+  <si>
+    <t>Technical &amp; Support Skill</t>
+  </si>
+  <si>
+    <t>Account Information Services</t>
+  </si>
+  <si>
+    <t>Relationship Management, Negotiation, Communication, Data Analysis</t>
+  </si>
+  <si>
+    <t>Business, Marketing, Sales</t>
+  </si>
+  <si>
+    <t>Enterprise Solutions, CRM Systems</t>
+  </si>
+  <si>
+    <t>Technology, Sales, Marketing, Finance</t>
+  </si>
+  <si>
+    <t>Account Manager, Sales Representative, Business Development Manager</t>
+  </si>
+  <si>
+    <t>SaaS, B2B Sales, Marketing, Business Development</t>
+  </si>
+  <si>
+    <t>Sales, Customer Relations, Marketing</t>
+  </si>
+  <si>
+    <t>Account Development</t>
+  </si>
+  <si>
+    <t>Sensor Design, Signal Processing, MEMS Technology</t>
+  </si>
+  <si>
+    <t>Electrical Engineering, Mechanical Engineering, Physics</t>
+  </si>
+  <si>
+    <t>Wearables, Automotive Systems, Drones</t>
+  </si>
+  <si>
+    <t>Electronics, Automotive, Aerospace</t>
+  </si>
+  <si>
+    <t>Sensor Design Engineer, Electronics Engineer, Mechatronics Engineer</t>
+  </si>
+  <si>
+    <t>Consumer Electronics, Automotive, Aerospace</t>
+  </si>
+  <si>
+    <t>Electronics, Mechanical Engineering</t>
+  </si>
+  <si>
+    <t>Accelerometer Design</t>
+  </si>
+  <si>
+    <t>Failure Analysis, Statistical Modeling, Stress Testing</t>
+  </si>
+  <si>
+    <t>Product Testing, Quality Assurance</t>
+  </si>
+  <si>
+    <t>Manufacturing, Aerospace, Electronics</t>
+  </si>
+  <si>
+    <t>Reliability Engineer, Test Engineer, QA Engineer</t>
+  </si>
+  <si>
+    <t>Manufacturing, Electronics, Aerospace</t>
+  </si>
+  <si>
+    <t>Testing, Reliability Engineering</t>
+  </si>
+  <si>
+    <t>Accelerated Life Testing</t>
+  </si>
+  <si>
+    <t>3D Printing, CAD Tools, Structural Design, Materials Selection</t>
+  </si>
+  <si>
+    <t>Engineering, Industrial Design, Materials Science</t>
+  </si>
+  <si>
+    <t>Product Packaging, Electronics, Consumer Goods</t>
+  </si>
+  <si>
+    <t>Manufacturing, Electronics, Packaging</t>
+  </si>
+  <si>
+    <t>Packaging Engineer, Industrial Designer, Product Designer</t>
+  </si>
+  <si>
+    <t>Electronics, Consumer Goods, Packaging Industry</t>
+  </si>
+  <si>
+    <t>Engineering, Design, Manufacturing</t>
+  </si>
+  <si>
+    <t>3D Packaging</t>
+  </si>
+  <si>
+    <t>Molecular Modeling, Visualization Tools (e.g., PyMOL, Chimera)</t>
+  </si>
+  <si>
+    <t>Biochemistry, Bioinformatics, Computer Science</t>
+  </si>
+  <si>
+    <t>Drug Development, Molecular Modeling</t>
+  </si>
+  <si>
+    <t>Healthcare, Biotech, Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>Bioinformatics Specialist, Research Scientist, Computational Biologist</t>
+  </si>
+  <si>
+    <t>Biotechnology, Healthcare, Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>Molecular Biology, Visualization, Computing</t>
+  </si>
+  <si>
+    <t>3D Molecular Visualization</t>
+  </si>
+  <si>
+    <t>Image Processing, Algorithms, Software Proficiency (e.g., MATLAB, OpenCV)</t>
+  </si>
+  <si>
+    <t>Computer Science, Biomedical Engineering, Mathematics</t>
+  </si>
+  <si>
+    <t>Medical Scans, 3D Models, Virtual Reality</t>
+  </si>
+  <si>
+    <t>Healthcare, Research, Gaming, Technology</t>
+  </si>
+  <si>
+    <t>Imaging Specialist, Data Scientist, Research Scientist</t>
+  </si>
+  <si>
+    <t>Medical Imaging, Computer Vision, Virtual Reality</t>
+  </si>
+  <si>
+    <t>Computer Vision, Imaging, Medical Imaging</t>
+  </si>
+  <si>
+    <t>3D Image Reconstruction</t>
+  </si>
+  <si>
+    <t>Circuit Design, CAD Tools, Signal Processing, Physical Design</t>
+  </si>
+  <si>
+    <t>Semiconductors, Consumer Electronics</t>
+  </si>
+  <si>
+    <t>Technology, Manufacturing</t>
+  </si>
+  <si>
+    <t>IC Design Engineer, Circuit Designer, Electronics Engineer</t>
+  </si>
+  <si>
+    <t>Semiconductor Industry, Electronics Manufacturing</t>
+  </si>
+  <si>
+    <t>3D IC Design</t>
+  </si>
+  <si>
+    <t>Geometry Algorithms, Spatial Data Structures, Programming (e.g., C++, Python)</t>
+  </si>
+  <si>
+    <t>Mathematics, Computer Science, Engineering</t>
+  </si>
+  <si>
+    <t>Robotics, Engineering Software, Games</t>
+  </si>
+  <si>
+    <t>Engineering, Robotics, Gaming, Simulation</t>
+  </si>
+  <si>
+    <t>Computational Geometer, Robotics Engineer, Simulation Developer</t>
+  </si>
+  <si>
+    <t>Robotics, Engineering, Game Design, Simulation</t>
+  </si>
+  <si>
+    <t>Geometry, Computer Science, Visualization</t>
+  </si>
+  <si>
+    <t>3D Computational Geometry</t>
+  </si>
+  <si>
+    <t>Creativity, Texturing, Lighting, Attention to Detail, Software Proficiency (e.g., Blender, Maya, ZBrush)</t>
+  </si>
+  <si>
+    <t>Digital Arts, Fine Arts, Game Design</t>
+  </si>
+  <si>
+    <t>Video Games, Films, Virtual Environments</t>
+  </si>
+  <si>
+    <t>Entertainment, Gaming, Architecture, VR/AR</t>
+  </si>
+  <si>
+    <t>3D Modeler, Character Artist, Industrial Designer</t>
+  </si>
+  <si>
+    <t>Game Design, Film Production, Architecture, VR/AR</t>
+  </si>
+  <si>
+    <t>Design, Computer Graphics, Animation</t>
+  </si>
+  <si>
+    <t>Creative &amp; Technical Skill</t>
+  </si>
+  <si>
+    <t>2D &amp; 3D Modeling</t>
+  </si>
+  <si>
+    <t>SKI-000048</t>
+  </si>
+  <si>
+    <t>6-12 months (basic proficiency), 2-3 years (advanced expertise)</t>
+  </si>
+  <si>
+    <t>Cryptography, Distributed Systems, Smart Contracts, Security</t>
+  </si>
+  <si>
+    <t>Computer Science, Engineering, Cryptography</t>
+  </si>
+  <si>
+    <t>Cryptocurrencies, Decentralized Applications, Smart Contracts</t>
+  </si>
+  <si>
+    <t>Technology, Finance, Gaming, Security</t>
+  </si>
+  <si>
+    <t>Blockchain Developer, Software Engineer, Smart Contract Developer</t>
+  </si>
+  <si>
+    <t>FinTech, Software Development, Supply Chain, Gaming</t>
+  </si>
+  <si>
+    <t>Blockchain, Software Engineering, Security</t>
+  </si>
+  <si>
+    <t>Blockchain Development</t>
+  </si>
+  <si>
+    <t>SKI-000001</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SKI-000002</t>
+  </si>
+  <si>
+    <t>SKI-000003</t>
+  </si>
+  <si>
+    <t>SKI-000004</t>
+  </si>
+  <si>
+    <t>SKI-000005</t>
+  </si>
+  <si>
+    <t>SKI-000006</t>
+  </si>
+  <si>
+    <t>SKI-000007</t>
+  </si>
+  <si>
+    <t>SKI-000008</t>
+  </si>
+  <si>
+    <t>SKI-000009</t>
+  </si>
+  <si>
+    <t>SKI-000010</t>
+  </si>
+  <si>
+    <t>SKI-000011</t>
+  </si>
+  <si>
+    <t>SKI-000012</t>
+  </si>
+  <si>
+    <t>SKI-000013</t>
+  </si>
+  <si>
+    <t>SKI-000014</t>
+  </si>
+  <si>
+    <t>SKI-000015</t>
+  </si>
+  <si>
+    <t>SKI-000016</t>
+  </si>
+  <si>
+    <t>SKI-000017</t>
+  </si>
+  <si>
+    <t>SKI-000018</t>
+  </si>
+  <si>
+    <t>SKI-000019</t>
+  </si>
+  <si>
+    <t>SKI-000020</t>
+  </si>
+  <si>
+    <t>SKI-000021</t>
+  </si>
+  <si>
+    <t>SKI-000022</t>
+  </si>
+  <si>
+    <t>SKI-000023</t>
+  </si>
+  <si>
+    <t>SKI-000024</t>
+  </si>
+  <si>
+    <t>SKI-000025</t>
+  </si>
+  <si>
+    <t>SKI-000026</t>
+  </si>
+  <si>
+    <t>SKI-000027</t>
+  </si>
+  <si>
+    <t>SKI-000028</t>
+  </si>
+  <si>
+    <t>SKI-000029</t>
+  </si>
+  <si>
+    <t>SKI-000030</t>
+  </si>
+  <si>
+    <t>SKI-000031</t>
+  </si>
+  <si>
+    <t>SKI-000032</t>
+  </si>
+  <si>
+    <t>SKI-000033</t>
+  </si>
+  <si>
+    <t>SKI-000034</t>
+  </si>
+  <si>
+    <t>SKI-000035</t>
+  </si>
+  <si>
+    <t>SKI-000036</t>
+  </si>
+  <si>
+    <t>SKI-000037</t>
+  </si>
+  <si>
+    <t>SKI-000038</t>
+  </si>
+  <si>
+    <t>SKI-000039</t>
+  </si>
+  <si>
+    <t>SKI-000040</t>
+  </si>
+  <si>
+    <t>SKI-000041</t>
+  </si>
+  <si>
+    <t>SKI-000042</t>
+  </si>
+  <si>
+    <t>SKI-000043</t>
+  </si>
+  <si>
+    <t>SKI-000044</t>
+  </si>
+  <si>
+    <t>SKI-000045</t>
+  </si>
+  <si>
+    <t>SKI-000046</t>
+  </si>
+  <si>
+    <t>SKI-000047</t>
+  </si>
+  <si>
+    <t>SKI-000049</t>
+  </si>
+  <si>
+    <t>SKI-000050</t>
+  </si>
+  <si>
+    <t>SKI-000051</t>
+  </si>
+  <si>
+    <t>SKI-000052</t>
+  </si>
+  <si>
+    <t>SKI-000053</t>
+  </si>
+  <si>
+    <t>SKI-000054</t>
+  </si>
+  <si>
+    <t>SKI-000055</t>
+  </si>
+  <si>
+    <t>SKI-000056</t>
+  </si>
+  <si>
+    <t>SKI-000057</t>
+  </si>
+  <si>
+    <t>SKI-000058</t>
+  </si>
+  <si>
+    <t>SKI-000059</t>
+  </si>
+  <si>
+    <t>SKI-000060</t>
+  </si>
+  <si>
+    <t>SKI-000061</t>
+  </si>
+  <si>
+    <t>SKI-000062</t>
+  </si>
+  <si>
+    <t>SKI-000063</t>
+  </si>
+  <si>
+    <t>SKI-000064</t>
+  </si>
+  <si>
+    <t>SKI-000065</t>
+  </si>
+  <si>
+    <t>SKI-000066</t>
+  </si>
+  <si>
+    <t>SKI-000067</t>
+  </si>
+  <si>
+    <t>SKI-000068</t>
+  </si>
+  <si>
+    <t>SKI-000069</t>
+  </si>
+  <si>
+    <t>SKI-000070</t>
+  </si>
+  <si>
+    <t>SKI-000071</t>
+  </si>
+  <si>
+    <t>SKI-000072</t>
+  </si>
+  <si>
+    <t>SKI-000073</t>
+  </si>
+  <si>
+    <t>SKI-000074</t>
+  </si>
+  <si>
+    <t>SKI-000075</t>
+  </si>
+  <si>
+    <t>SKI-000076</t>
+  </si>
+  <si>
+    <t>SKI-000077</t>
+  </si>
+  <si>
+    <t>SKI-000078</t>
+  </si>
+  <si>
+    <t>SKI-000079</t>
+  </si>
+  <si>
+    <t>SKI-000080</t>
+  </si>
+  <si>
+    <t>SKI-000081</t>
+  </si>
+  <si>
+    <t>SKI-000082</t>
+  </si>
+  <si>
+    <t>SKI-000083</t>
+  </si>
+  <si>
+    <t>SKI-000084</t>
+  </si>
+  <si>
+    <t>SKI-000085</t>
+  </si>
+  <si>
+    <t>SKI-000086</t>
+  </si>
+  <si>
+    <t>SKI-000087</t>
+  </si>
+  <si>
+    <t>SKI-000088</t>
+  </si>
+  <si>
+    <t>SKI-000089</t>
+  </si>
+  <si>
+    <t>SKI-000090</t>
+  </si>
+  <si>
+    <t>SKI-000091</t>
+  </si>
+  <si>
+    <t>SKI-000092</t>
+  </si>
+  <si>
+    <t>SKI-000093</t>
+  </si>
+  <si>
+    <t>SKI-000094</t>
+  </si>
+  <si>
+    <t>SKI-000095</t>
+  </si>
+  <si>
+    <t>SKI-000096</t>
+  </si>
+  <si>
+    <t>SKI-000097</t>
+  </si>
+  <si>
+    <t>SKI-000098</t>
+  </si>
+  <si>
+    <t>SKI-000099</t>
+  </si>
+  <si>
+    <t>SKI-000100</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,21 +2606,24 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -120,15 +2638,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -426,8 +2958,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Q101"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="11" width="18" customWidth="1"/>
     <col min="12" max="12" width="22" customWidth="1"/>
@@ -436,66 +2968,3570 @@
     <col min="15" max="17" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
+      <c r="A42" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="N53" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="O53" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
+      <c r="A54" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
+      <c r="A55" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="N55" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="O55" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
+      <c r="A56" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
+      <c r="A57" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="A58" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
+      <c r="A59" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
+      <c r="A60" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="N61" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="O61" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15">
+      <c r="A62" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
+      <c r="A63" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="N63" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="O63" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
+      <c r="A64" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="N64" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="M65" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="N65" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
+      <c r="A66" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
+      <c r="A67" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="M67" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="N67" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
+      <c r="A68" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="L68" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="M68" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="N68" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
+      <c r="A69" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="M69" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="N69" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="O69" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
+      <c r="A70" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="M70" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="N70" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
+      <c r="A71" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="L71" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="M71" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="N71" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="O71" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
+      <c r="A72" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
+      <c r="A73" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="L73" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="M73" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="N73" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="O73" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
+      <c r="A74" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="M74" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="N74" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="O74" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
+      <c r="A75" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="L75" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="M75" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="N75" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="O75" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="A76" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="L76" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L77" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="N77" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="O77" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="L78" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="M78" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="N78" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="M79" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="N79" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="O79" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="A80" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="L80" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="M80" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="N80" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="O80" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
+      <c r="A81" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15">
+      <c r="A82" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="L82" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="M82" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="N82" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15">
+      <c r="A83" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15">
+      <c r="A84" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="L84" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="M84" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="N84" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="O84" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15">
+      <c r="A85" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="L85" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="M85" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="N85" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="O85" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15">
+      <c r="A86" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="L86" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="M86" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="N86" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="O86" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15">
+      <c r="A87" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K87" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="L87" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M87" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="N87" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="O87" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15">
+      <c r="A88" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="L88" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="M88" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="N88" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="O88" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15">
+      <c r="A89" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15">
+      <c r="A90" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="L90" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="M90" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="N90" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="O90" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15">
+      <c r="A91" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15">
+      <c r="A92" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="L92" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="M92" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="N92" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="O92" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15">
+      <c r="A93" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J93" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K93" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="L93" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="M93" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N93" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="O93" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15">
+      <c r="A94" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15">
+      <c r="A95" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K95" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="L95" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="M95" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N95" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="O95" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15">
+      <c r="A96" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15">
+      <c r="A97" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K97" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L97" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M97" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N97" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="O97" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15">
+      <c r="A98" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L98" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M98" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N98" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O98" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15">
+      <c r="A99" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J99" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K99" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L99" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M99" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N99" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O99" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15">
+      <c r="A100" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15">
+      <c r="A101" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="2"/>
+  <conditionalFormatting sqref="A2:A101">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D999" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D997" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"TECHNICAL,SOFT,LANGUAGE,TOOL,FRAMEWORK,METHODOLOGY,OTHER"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I999" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I997" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"BEGINNER,INTERMEDIATE,ADVANCED,EXPERT"</formula1>
     </dataValidation>
   </dataValidations>

--- a/apps/api/data/excel_templates/skills.xlsx
+++ b/apps/api/data/excel_templates/skills.xlsx
@@ -6761,7 +6761,7 @@
       <c r="P101" s="4" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <autoFilter ref="A1:P1"/>
   <conditionalFormatting sqref="A2:A101">
     <cfRule type="duplicateValues" priority="3" dxfId="0"/>

--- a/apps/api/data/excel_templates/skills.xlsx
+++ b/apps/api/data/excel_templates/skills.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection lockStructure="1"/>
+  <workbookProtection workbookPassword="DB2D" lockStructure="1"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -536,7 +536,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>
   <autoFilter ref="A1:P1"/>
   <dataValidations count="2">
     <dataValidation sqref="H2:H1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">

--- a/apps/api/data/excel_templates/skills.xlsx
+++ b/apps/api/data/excel_templates/skills.xlsx
@@ -57,7 +57,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -67,6 +67,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -534,6 +537,6206 @@
           <t>metadata</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain Development</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000001</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain, Software Engineering, Security</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Finance, Gaming, Security</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>FinTech, Software Development, Supply Chain, Gaming</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain Developer, Software Engineer, Smart Contract Developer</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Cryptocurrencies, Decentralized Applications, Smart Contracts</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Engineering, Cryptography</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Cryptography, Distributed Systems, Smart Contracts, Security</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 2-3 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="n"/>
+      <c r="P2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>2D &amp; 3D Modeling</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000002</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Creative &amp; Technical Skill</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Design, Computer Graphics, Animation</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Entertainment, Gaming, Architecture, VR/AR</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Game Design, Film Production, Architecture, VR/AR</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>3D Modeler, Character Artist, Industrial Designer</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Video Games, Films, Virtual Environments</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Digital Arts, Fine Arts, Game Design</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Creativity, Texturing, Lighting, Attention to Detail, Software Proficiency (e.g., Blender, Maya, ZBrush)</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>3D Computational Geometry</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000003</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Geometry, Computer Science, Visualization</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Engineering, Robotics, Gaming, Simulation</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Robotics, Engineering, Game Design, Simulation</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Computational Geometer, Robotics Engineer, Simulation Developer</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Robotics, Engineering Software, Games</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>Mathematics, Computer Science, Engineering</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Geometry Algorithms, Spatial Data Structures, Programming (e.g., C++, Python)</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>3D IC Design</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000004</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Circuit Design, Engineering</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Manufacturing</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Semiconductor Industry, Electronics Manufacturing</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>IC Design Engineer, Circuit Designer, Electronics Engineer</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Semiconductors, Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Computer Engineering</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Circuit Design, CAD Tools, Signal Processing, Physical Design</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>3D Image Reconstruction</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000005</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Computer Vision, Imaging, Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Research, Gaming, Technology</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Medical Imaging, Computer Vision, Virtual Reality</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Imaging Specialist, Data Scientist, Research Scientist</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Medical Scans, 3D Models, Virtual Reality</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Biomedical Engineering, Mathematics</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Image Processing, Algorithms, Software Proficiency (e.g., MATLAB, OpenCV)</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>3D Molecular Visualization</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000006</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Molecular Biology, Visualization, Computing</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Biotech, Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Biotechnology, Healthcare, Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Bioinformatics Specialist, Research Scientist, Computational Biologist</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Drug Development, Molecular Modeling</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Biochemistry, Bioinformatics, Computer Science</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>Molecular Modeling, Visualization Tools (e.g., PyMOL, Chimera)</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>3D Packaging</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000007</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Engineering, Design, Manufacturing</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Manufacturing, Electronics, Packaging</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Consumer Goods, Packaging Industry</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Packaging Engineer, Industrial Designer, Product Designer</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Product Packaging, Electronics, Consumer Goods</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Engineering, Industrial Design, Materials Science</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>3D Printing, CAD Tools, Structural Design, Materials Selection</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Accelerated Life Testing</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000008</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Testing, Reliability Engineering</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Manufacturing, Aerospace, Electronics</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Manufacturing, Electronics, Aerospace</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Reliability Engineer, Test Engineer, QA Engineer</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Product Testing, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering, Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>Failure Analysis, Statistical Modeling, Stress Testing</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Accelerometer Design</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000009</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Automotive, Aerospace</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Electronics, Automotive, Aerospace</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Sensor Design Engineer, Electronics Engineer, Mechatronics Engineer</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Wearables, Automotive Systems, Drones</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Mechanical Engineering, Physics</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>Sensor Design, Signal Processing, MEMS Technology</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Account Development</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000010</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Business &amp; Technical Skill</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Sales, Customer Relations, Marketing</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Sales, Marketing, Finance</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>SaaS, B2B Sales, Marketing, Business Development</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Account Manager, Sales Representative, Business Development Manager</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Enterprise Solutions, CRM Systems</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Business, Marketing, Sales</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Relationship Management, Negotiation, Communication, Data Analysis</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Account Information Services</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000011</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Technical &amp; Support Skill</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>IT Services, Data Management, Security</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Healthcare, Telecommunications</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Banking, Healthcare, Telecom, Finance</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>IT Specialist, Account Information Manager, Data Analyst</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Data Security, Information Management</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Information Technology, Computer Science</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Data Management, Security Protocols, Database Design</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>ADC/DAC</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000012</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Signal Processing</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Telecommunications, Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Telecommunications, Audio/Video, Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Electronics Engineer, Signal Processing Engineer</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Audio Devices, Communication Systems</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Signal Processing</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Analog to Digital Conversion, Signal Processing, Circuit Design</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Advanced Packaging</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000013</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Engineering, Manufacturing</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Manufacturing, Electronics, Consumer Goods</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Semiconductor, Consumer Goods</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Packaging Engineer, Process Engineer, Materials Scientist</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>Microelectronics, Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering, Materials Science</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>3D Modeling, Thermal Management, Structural Integrity</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>AI for Fraud Detection</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000014</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Data Science</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Cybersecurity, E-commerce</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Finance, E-commerce, Banking, Cybersecurity</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Data Scientist, AI Engineer, Fraud Analyst</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>Fraud Detection Systems, Security Software</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Data Science, Engineering</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Machine Learning, Pattern Recognition, Data Analytics</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Algorithm Development</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000015</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Software Engineering</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Finance, AI, Data Science</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Software Development, Machine Learning, Data Science</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Scientist, Algorithm Engineer</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>Software Algorithms, Data Processing, AI Models</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Mathematics, Engineering</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>Problem Solving, Optimization, Data Structures, Programming</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Algorithmic Bias</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000016</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Analytical Skill</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Data Science, Ethics, AI</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Ethics, Data Science</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>AI, Machine Learning, Social Sciences</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>AI Researcher, Data Scientist, Ethicist</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>AI Models, Machine Learning Systems</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Ethics, Social Science</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>Bias Detection, Fairness in AI, Ethical Decision Making</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Algorithmic Bias Analysis</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000017</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Analytical Skill</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Data Science, Ethics, AI</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Ethics, Data Science</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>AI, Machine Learning, Social Sciences</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>AI Researcher, Data Scientist, Ethicist, Policy Analyst</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>AI Models, Bias Detection Systems</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Ethics, Social Science</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>Fairness Audits, Algorithmic Evaluation, Bias Metrics</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Algorithmic Complexity</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000018</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Analytical &amp; Technical Skill</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Mathematics</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Research, AI, Academia</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Software Development, Research, AI</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Algorithm Engineer, Data Scientist, Software Engineer</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Algorithm Optimization, Complexity Analysis</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Mathematics</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>Complexity Theory, Algorithmic Design, Data Structures</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Algorithmic Problem Solving</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000019</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Analytical &amp; Technical Skill</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Problem Solving, Computer Science</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Finance, Research, AI</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Software Development, Competitive Programming, AI</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Scientist, Algorithm Developer</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Coding Competitions, AI Models, Optimization</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Mathematics, Engineering</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>Critical Thinking, Logical Reasoning, Programming Skills</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Algorithmic Trading</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000020</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Data Science, Software Engineering</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Technology, Trading</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Financial Markets, Hedge Funds, Trading Platforms</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Quantitative Analyst, Algorithmic Trader, Data Scientist</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Trading Algorithms, Financial Models, Market Analytics</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Computer Science, Mathematics</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>Data Analysis, Statistical Modeling, Market Knowledge</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Algorithms for Chemical Data</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000021</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Data Science, Chemistry, Machine Learning</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals, Biotech, Chemistry</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals, Biotechnology, Chemical Engineering</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Data Scientist, Chemoinformatics Specialist, Research Scientist</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Chemical Data Models, Drug Discovery Tools</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>Chemistry, Computer Science, Biostatistics</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>Chemoinformatics, Pattern Recognition, Statistical Analysis</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Altera/Intel FPGA</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000022</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Hardware Engineering, Programming</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Telecommunications, Electronics</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Telecommunications, Consumer Electronics, Computing</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>FPGA Engineer, Hardware Engineer, Embedded Systems Developer</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Embedded Systems, Hardware Acceleration</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Computer Engineering, Physics</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>FPGA Programming, Hardware Design, Circuit Design</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>AML</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000023</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Analytical Skill</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Compliance, Risk Management</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Banking, Regulatory Compliance</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Banking, Finance, Compliance, Security</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Compliance Officer, Risk Analyst, AML Specialist</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>Anti-Money Laundering Systems, Risk Management</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Law, Risk Management</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>Regulatory Knowledge, Risk Assessment, Investigation Techniques</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Amplifiers</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000024</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Signal Processing</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Telecommunications, Audio</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Audio Systems, Telecommunications, Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Electronics Engineer, Audio Engineer, Signal Processing Engineer</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Audio Amplifiers, Communication Systems</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Audio Engineering</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>Signal Amplification, Circuit Design, Frequency Response</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Analog and Digital Design</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000025</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Circuit Design, Engineering</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Automotive, Telecommunications</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Electronics, Automotive, Telecommunications</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Circuit Designer, Electronics Engineer, Embedded Systems Engineer</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Electronics, Communication Devices</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Physics, Computer Engineering</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>Circuit Design, Signal Processing, Mixed-Signal Systems</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="n"/>
+      <c r="P26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Analog Circuit Design</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000026</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Circuit Design</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Automotive, Telecommunications</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Electronics, Telecommunications, Automotive</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Circuit Designer, Electronics Engineer, Embedded Systems Engineer</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>Audio Devices, Communication Systems, Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Physics, Computer Engineering</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>Circuit Design, Signal Integrity, Frequency Response</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Analog-to-Digital Conversion</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000027</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Signal Processing, Data Acquisition</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Telecommunications, Audio</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Audio Systems, Communication Systems, Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Electronics Engineer, Signal Processing Engineer, Embedded Systems Developer</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>ADCs, Communication Systems, Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Physics, Computer Engineering</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>Analog-to-Digital Conversion, Signal Processing, Data Acquisition</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Antenna Design</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000028</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Communication Systems, Engineering</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Telecommunications, Aerospace, Electronics</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Telecommunications, Aerospace, Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>RF Engineer, Antenna Engineer, Communications Systems Engineer</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Communication Systems, Wireless Networks</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Physics, Telecommunications</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>RF Design, Antenna Modeling, Wireless Communication</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="n"/>
+      <c r="P29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>API Gateways</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000029</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Software Engineering, Cloud Computing, Networking</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Cloud Computing, SaaS</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Web Development, Cloud Applications, SaaS</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>API Engineer, Backend Developer, Cloud Solutions Architect</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>Web Applications, Cloud Services, Microservices</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Software Engineering, Networking</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>API Design, Authentication, Load Balancing, Service Integration</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O30" s="5" t="n"/>
+      <c r="P30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>API Security</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000030</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Cybersecurity, Software Engineering</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Cybersecurity, Cloud Computing</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Web Development, Cloud Computing, SaaS</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Security Engineer, API Security Specialist, Backend Developer</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>Web Applications, API Security Systems</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Cybersecurity</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>Encryption, Authentication, Access Control, Security Protocols</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="n"/>
+      <c r="P31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Application Development</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000031</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Software Engineering, Web Development</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Mobile, Web Development</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Mobile Apps, Web Apps, Enterprise Software</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Software Developer, Mobile Developer, Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>Mobile Applications, Web Platforms</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Software Engineering</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>Programming, UI/UX Design, Databases, Problem Solving</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="n"/>
+      <c r="P32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Application Engineering</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000032</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Software Engineering, Product Design</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Electronics, Consumer Goods</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>SaaS, Embedded Systems, Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>Application Engineer, Software Engineer, Systems Engineer</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>Software Applications, Embedded Systems</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Engineering, Product Design</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>Software Design, Debugging, System Integration, User Experience</t>
+        </is>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Appointment Scheduling</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000033</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Software Development, Business Operations</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Education, Business Services</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Business Services, Education</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>Scheduling Software Developer, Operations Coordinator, IT Specialist</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>Appointment Scheduling Systems, Calendar Apps</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Business Administration</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>Time Management, Database Design, User Interface Design</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="n"/>
+      <c r="P34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Approximation Algorithms</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000034</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Analytical &amp; Technical Skill</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Algorithms, Computer Science, Optimization</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Research, AI, Operations Research</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Machine Learning, Data Science, Operations Research</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>Algorithm Engineer, Data Scientist, Researcher</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>Optimization Problems, Computational Models</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Mathematics, Operations Research</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>Algorithm Design, Approximation Techniques, Computational Complexity</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="n"/>
+      <c r="P35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Approximation Theory</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000035</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Analytical &amp; Technical Skill</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Mathematics, Algorithms</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Mathematics, Technology, Research</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>AI, Operations Research, Data Science</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>Researcher, Algorithm Developer, Data Scientist</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>Computational Models, Optimization Algorithms</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>Mathematics, Computer Science, Operations Research</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>Theoretical Analysis, Approximation Methods, Proofs of Bounds</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="n"/>
+      <c r="P36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>ARM Architecture</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000036</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Computer Architecture, Hardware Design</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Consumer Electronics, Mobile</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Mobile Devices, Embedded Systems, Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>Embedded Systems Engineer, Hardware Engineer, Firmware Developer</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>Mobile Devices, Embedded Systems</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Computer Engineering</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>ARM Assembly, Processor Design, Low-Level Programming</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>ASIC Design</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000037</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Hardware Design</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Telecommunications, Computing</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Telecommunications, Consumer Electronics, Computing</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>ASIC Engineer, Hardware Engineer, System-on-Chip (SoC) Designer</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>Integrated Circuits, Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Computer Engineering</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>Circuit Design, Hardware Description Languages, Optimization Techniques</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O38" s="5" t="n"/>
+      <c r="P38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Assertion Languages</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000038</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Software Engineering, Verification</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Software Engineering</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Embedded Systems, Semiconductor Design, Formal Verification</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>Verification Engineer, Hardware Engineer, Software Tester</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>Design Verification, Testbenches</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Computer Science</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>Formal Methods, Hardware Verification, Test Automation</t>
+        </is>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="n"/>
+      <c r="P39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Assertion-Based Verification</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000039</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Software Verification, Hardware Design</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Software Engineering</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Semiconductor Design, Embedded Systems, Software Development</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>Verification Engineer, Embedded Systems Engineer, Hardware Engineer</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>Verification Tools, Testbenches, Simulation Models</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Computer Science, Software Engineering</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>Formal Verification, Test Automation, Debugging, Model Checking</t>
+        </is>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="n"/>
+      <c r="P40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Asset Allocation</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000040</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Financial Skill</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Investment Management</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Investment, Wealth Management</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Hedge Funds, Wealth Management, Financial Planning</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>Portfolio Manager, Financial Analyst, Investment Advisor</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>Investment Portfolios, Risk Management</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Economics, Mathematics</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>Risk Management, Portfolio Diversification, Statistical Analysis</t>
+        </is>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="n"/>
+      <c r="P41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Asset Valuation</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000041</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Financial Skill</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Real Estate, Investment</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Real Estate, Private Equity</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Real Estate, Private Equity, Public Markets</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>Valuation Analyst, Financial Analyst, Real Estate Appraiser</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>Investment Valuation, Property Valuation</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Economics, Real Estate</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>Market Analysis, Discounted Cash Flow, Comparable Analysis</t>
+        </is>
+      </c>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="n"/>
+      <c r="P42" s="5" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Astronomy</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000042</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Scientific Skill</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Space Science, Physics</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Research, Education, Space Exploration</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Research, Education, Space Exploration</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>Astronomer, Astrophysicist, Research Scientist</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>Space Research, Telescopes, Space Missions</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>Physics, Astronomy, Mathematics</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>Celestial Observation, Telescope Operation, Research Methods</t>
+        </is>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>2-3 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="n"/>
+      <c r="P43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Astronomy Data Formats</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000043</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Data Science, Astronomy, Software Engineering</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Research, Space Science, Astronomy</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Space Research, Data Science, Astrophysics</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>Data Scientist, Researcher, Software Developer</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>Space Observations, Data Analysis</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Astronomy, Data Science</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>Data Parsing, Format Conversion, Data Storage Systems</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="n"/>
+      <c r="P44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Astrophysical Modeling</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000044</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Scientific &amp; Technical Skill</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Astrophysics, Computational Modeling</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Research, Space Science, Education</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Space Research, Simulation, Education</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>Astrophysicist, Computational Scientist, Researcher</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>Space Simulations, Astrophysical Models</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>Physics, Mathematics, Computer Science</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>Numerical Simulation, Mathematical Modeling, Computational Physics</t>
+        </is>
+      </c>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O45" s="5" t="n"/>
+      <c r="P45" s="5" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Astrophysical Simulations</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000045</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Astrophysics, Computational Science</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Research, Space Science, Education</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Research, Space Science, Simulations</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>Astrophysicist, Simulation Specialist, Research Scientist</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>Computational Models, Simulation Software</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>Physics, Computer Science, Mathematics</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>Simulation Software, Numerical Methods, High-Performance Computing</t>
+        </is>
+      </c>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O46" s="5" t="n"/>
+      <c r="P46" s="5" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Astrophysics</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000046</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Scientific Skill</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Physics, Space Science</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Research, Space Science, Education</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Research, Education, Space Exploration</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>Astrophysicist, Research Scientist, Educator</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>Space Research, Scientific Discoveries</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>Physics, Mathematics, Astronomy</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>Theoretical Physics, Research, Data Analysis, Observation Methods</t>
+        </is>
+      </c>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>2-3 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="n"/>
+      <c r="P47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000047</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Testing, Engineering</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Aerospace, Automotive</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Electronics Manufacturing, Aerospace, Automotive</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>Test Engineer, ATE Engineer, Electronics Engineer</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>Testing Systems, Electronics Validation</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Computer Science, Physics</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>Test Automation, Hardware Testing, Software Integration</t>
+        </is>
+      </c>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O48" s="5" t="n"/>
+      <c r="P48" s="5" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>ATE Equipment Maintenance</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000048</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Maintenance, Engineering</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Aerospace, Manufacturing</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="n"/>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Manufacturing, Aerospace, Electronics Repair</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance Technician, ATE Engineer, Repair Specialist</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>Test Equipment, Circuit Boards, Diagnostic Systems</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>Troubleshooting, Maintenance Protocols, Diagnostics</t>
+        </is>
+      </c>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O49" s="5" t="n"/>
+      <c r="P49" s="5" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Atmospheric Modeling</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000049</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Scientific &amp; Technical Skill</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Atmospheric Science, Environmental Science</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>Environmental Science, Aerospace, Research</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Meteorology, Climate Science, Aerospace</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>Atmospheric Scientist, Meteorologist, Climate Modeler</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>Weather Forecasting, Climate Simulations</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>Environmental Science, Atmospheric Science, Physics</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>Numerical Weather Prediction, Data Assimilation, Climate Modeling</t>
+        </is>
+      </c>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="n"/>
+      <c r="P50" s="5" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Audit Coordination</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000050</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Business &amp; Organizational Skill</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Audit, Risk Management, Compliance</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Healthcare, Government, Corporate</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Healthcare, Government, Corporate</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>Audit Manager, Audit Coordinator, Compliance Officer</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>Audit Processes, Risk Management</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>Business Administration, Finance, Accounting</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>Coordination, Risk Assessment, Documentation, Regulatory Knowledge</t>
+        </is>
+      </c>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O51" s="5" t="n"/>
+      <c r="P51" s="5" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Audit Methodologies</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000051</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Analytical &amp; Technical Skill</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Audit, Risk Management, Compliance</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Healthcare, Government, Corporate</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Government, Healthcare, Corporate</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>Auditor, Risk Analyst, Compliance Specialist</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>Audit Processes, Compliance Testing</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>Accounting, Finance, Business Administration</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>Internal Control Frameworks, Risk Assessment, Regulatory Knowledge</t>
+        </is>
+      </c>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O52" s="5" t="n"/>
+      <c r="P52" s="5" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Authentication Protocols</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000052</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Cybersecurity, Networking</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Cybersecurity, IT</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Web Development, Cloud Computing, IT Security</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>Security Engineer, Network Engineer, Cybersecurity Analyst</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>Security Systems, Cloud Authentication</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Network Engineering, Cybersecurity</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>Encryption, Access Control, Protocol Analysis, Identity Management</t>
+        </is>
+      </c>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O53" s="5" t="n"/>
+      <c r="P53" s="5" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Automated Assembly</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000053</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Manufacturing, Robotics</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>Manufacturing, Automotive, Electronics</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="n"/>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Manufacturing, Automotive, Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>Automation Engineer, Robotics Engineer, Manufacturing Engineer</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>Production Lines, Robotics Systems</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering, Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
+          <t>Robotics, Process Optimization, Mechatronics, System Integration</t>
+        </is>
+      </c>
+      <c r="N54" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O54" s="5" t="n"/>
+      <c r="P54" s="5" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Automated Test Equipment</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000054</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Testing, Engineering</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Aerospace, Automotive</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Electronics Manufacturing, Aerospace, Automotive</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>Test Engineer, ATE Engineer, Electronics Engineer</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>Testing Systems, Circuit Boards, Validation</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Computer Science, Physics</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>Test Automation, Hardware Testing, Software Integration</t>
+        </is>
+      </c>
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O55" s="5" t="n"/>
+      <c r="P55" s="5" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Automation Systems</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000055</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Engineering, Robotics, Control Systems</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>Manufacturing, Aerospace, Energy, Robotics</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="n"/>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>Manufacturing, Automotive, Energy, Aerospace</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>Automation Engineer, Robotics Engineer, System Integrator</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>Automated Production Lines, Robotics, Control Systems</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering, Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="inlineStr">
+        <is>
+          <t>Robotics, Control Theory, System Design, Automation Technology</t>
+        </is>
+      </c>
+      <c r="N56" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O56" s="5" t="n"/>
+      <c r="P56" s="5" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Automation Tools</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000056</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Software Engineering, Automation, Tools</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>IT, Software, Manufacturing</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>IT, Software Development, Manufacturing</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>Automation Developer, Software Engineer, Tools Specialist</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>Testing Tools, Automation Frameworks</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Software Engineering</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>Scripting, Process Automation, Tool Development, Integration</t>
+        </is>
+      </c>
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O57" s="5" t="n"/>
+      <c r="P57" s="5" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Automotive Safety Standards</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000057</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Technical Skill</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Automotive, Safety, Compliance</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>Automotive, Engineering, Compliance</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>Automotive Manufacturing, Automotive Design</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>Safety Engineer, Regulatory Compliance Officer, Automotive Engineer</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>Vehicle Safety Systems, Compliance Testing</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering, Automotive Engineering, Law</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
+          <t>Safety Protocols, Regulatory Standards, Vehicle Testing</t>
+        </is>
+      </c>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O58" s="5" t="n"/>
+      <c r="P58" s="5" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Automotive Systems</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000058</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Automotive Engineering, Electronics</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Automotive, Electronics</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="n"/>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>Automotive Design, Automotive Manufacturing</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>Automotive Engineer, Systems Engineer, Electronics Engineer</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>Automotive Components, Infotainment Systems</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering, Electrical Engineering, Automotive Technology</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>Systems Design, Integration, Embedded Systems, Diagnostics</t>
+        </is>
+      </c>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O59" s="5" t="n"/>
+      <c r="P59" s="5" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Automotive Testing</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000059</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Automotive Engineering, Testing</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>Automotive, Engineering</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>Automotive Manufacturing, Research, Development</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>Test Engineer, Automotive Engineer, Quality Assurance Specialist</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>Vehicle Testing, Crash Simulation, Performance Evaluation</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering, Automotive Engineering, Testing Methods</t>
+        </is>
+      </c>
+      <c r="M60" s="5" t="inlineStr">
+        <is>
+          <t>Vehicle Diagnostics, Performance Testing, Safety Standards</t>
+        </is>
+      </c>
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O60" s="5" t="n"/>
+      <c r="P60" s="5" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Autonomous Systems</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000060</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Robotics, AI, Engineering</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Robotics, Automotive, Aerospace, Technology</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>Robotics, Autonomous Vehicles, Aerospace</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>Robotics Engineer, Autonomous Vehicle Engineer, AI Specialist</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>Self-Driving Cars, Drones, Robotic Systems</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>Robotics, Computer Science, Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>Machine Learning, Sensor Integration, System Design, Path Planning</t>
+        </is>
+      </c>
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O61" s="5" t="n"/>
+      <c r="P61" s="5" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Backtesting</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000061</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Analytical &amp; Technical Skill</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Data Science, Algorithms</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="n"/>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Investment, Trading</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="n"/>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Trading, Investment, Financial Planning</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>Quantitative Analyst, Algorithmic Trader, Data Scientist</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>Financial Models, Trading Strategies</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Economics, Data Science</t>
+        </is>
+      </c>
+      <c r="M62" s="5" t="inlineStr">
+        <is>
+          <t>Statistical Modeling, Risk Management, Performance Evaluation</t>
+        </is>
+      </c>
+      <c r="N62" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O62" s="5" t="n"/>
+      <c r="P62" s="5" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Banking Platforms Integration</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000062</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Software Engineering</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="n"/>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Banking, Fintech, Technology</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="n"/>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Banking, Fintech, Payment Systems</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>Integration Specialist, Banking Software Engineer, IT Specialist</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>Core Banking Systems, Payment Gateways</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Finance, Software Engineering</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>API Integration, Security, System Interoperability</t>
+        </is>
+      </c>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O63" s="5" t="n"/>
+      <c r="P63" s="5" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Banking Software</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000063</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Software Engineering, Finance</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="n"/>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>Banking, Fintech, Technology</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="n"/>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Banking, Fintech, Payment Systems</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>Software Engineer, Banking Systems Architect, Fintech Developer</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>Banking Applications, Payment Systems</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Finance, Software Engineering</t>
+        </is>
+      </c>
+      <c r="M64" s="5" t="inlineStr">
+        <is>
+          <t>Financial Software Development, Security, UX/UI Design</t>
+        </is>
+      </c>
+      <c r="N64" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O64" s="5" t="n"/>
+      <c r="P64" s="5" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Banking-as-a-Service</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000064</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Business &amp; Technical Skill</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Finance, SaaS, Software Engineering</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="5" t="n"/>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Banking, Fintech, Technology</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="n"/>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Fintech, Digital Banking</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>SaaS Architect, Fintech Developer, Business Development Manager</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>Digital Banking Platforms, Financial Services</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>Business Administration, Software Engineering, Finance</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>Cloud Solutions, API Development, Regulatory Compliance</t>
+        </is>
+      </c>
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O65" s="5" t="n"/>
+      <c r="P65" s="5" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Battery Management Systems</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000065</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Engineering, Electronics, Software</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>Automotive, Energy, Electronics</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="n"/>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Electric Vehicles, Renewable Energy, Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>Battery Systems Engineer, Electrical Engineer, Energy Consultant</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>Electric Vehicle Batteries, Solar Power Systems</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Energy Systems, Computer Science</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>Battery Charging, Energy Storage, Power Management</t>
+        </is>
+      </c>
+      <c r="N66" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O66" s="5" t="n"/>
+      <c r="P66" s="5" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Behavioral Analytics</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000066</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Analytical Skill</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Data Science, Marketing, Psychology</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="n"/>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Marketing, E-commerce, Technology</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="n"/>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>E-commerce, Marketing, Consumer Behavior Research</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>Data Scientist, Behavioral Analyst, Marketing Specialist</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>Customer Insights, Behavioral Data Models</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>Data Science, Psychology, Marketing</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>Pattern Recognition, Customer Segmentation, Predictive Modeling</t>
+        </is>
+      </c>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O67" s="5" t="n"/>
+      <c r="P67" s="5" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>Bioinformatics</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000067</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Scientific &amp; Technical Skill</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Bioinformatics, Computational Biology</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="n"/>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Biotechnology, Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="n"/>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Pharmaceuticals, Biotechnology</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>Bioinformatician, Computational Biologist, Research Scientist</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>Genomic Data Analysis, Healthcare Research</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>Biology, Computer Science, Data Science</t>
+        </is>
+      </c>
+      <c r="M68" s="5" t="inlineStr">
+        <is>
+          <t>Genomic Data Analysis, Statistical Methods, Molecular Biology</t>
+        </is>
+      </c>
+      <c r="N68" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O68" s="5" t="n"/>
+      <c r="P68" s="5" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Bioinformatics Algorithms</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000068</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Analytical &amp; Technical Skill</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Bioinformatics, Computational Biology</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="n"/>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Biotechnology, Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="n"/>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Pharmaceuticals, Biotechnology</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>Computational Biologist, Bioinformatics Researcher, Data Scientist</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>Genomic Research, Drug Discovery Tools</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Biology, Mathematics</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>Algorithm Development, Machine Learning, Data Analysis</t>
+        </is>
+      </c>
+      <c r="N69" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O69" s="5" t="n"/>
+      <c r="P69" s="5" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Bioinformatics Databases</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000069</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Bioinformatics, Data Management, Software</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="n"/>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Biotechnology, Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="n"/>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Pharmaceuticals, Research</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>Bioinformatics Database Administrator, Data Scientist, Researcher</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>Genomic Databases, Medical Data Repositories</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Biology, Data Science</t>
+        </is>
+      </c>
+      <c r="M70" s="5" t="inlineStr">
+        <is>
+          <t>Database Design, Data Mining, Genomic Data Management</t>
+        </is>
+      </c>
+      <c r="N70" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O70" s="5" t="n"/>
+      <c r="P70" s="5" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Bioinformatics Tools</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000070</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Bioinformatics, Data Science, Software</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="n"/>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Biotechnology, Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="n"/>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Pharmaceuticals, Research</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>Bioinformatics Specialist, Data Scientist, Computational Biologist</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>Genomic Research, Medical Data Analysis</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Biology, Data Science</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>Tool Development, Data Analysis, Genomic Data Processing</t>
+        </is>
+      </c>
+      <c r="N71" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O71" s="5" t="n"/>
+      <c r="P71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>Biological Data Integration</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000071</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Bioinformatics, Data Science</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="n"/>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Biotechnology, Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="n"/>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Biotechnology, Research</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>Data Integration Specialist, Bioinformatics Analyst, Researcher</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>Genomic Data Integration, Medical Records</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Biology, Data Science</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr">
+        <is>
+          <t>Data Merging, Multi-Source Integration, Biological Data Analysis</t>
+        </is>
+      </c>
+      <c r="N72" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O72" s="5" t="n"/>
+      <c r="P72" s="5" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Biological Database Management</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000072</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Bioinformatics, Data Management</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="5" t="n"/>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Research, Biotechnology</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="n"/>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Research, Biotechnology</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>Database Administrator, Bioinformatics Data Manager, Research Scientist</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>Medical Data Repositories, Genomic Databases</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Biology, Data Management</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>Database Design, Data Storage, Genomic Data Management</t>
+        </is>
+      </c>
+      <c r="N73" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O73" s="5" t="n"/>
+      <c r="P73" s="5" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Biological Databases</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000073</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Bioinformatics, Data Management, Software</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="n"/>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Biotechnology, Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="n"/>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Pharmaceuticals, Research</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>Bioinformatics Specialist, Database Administrator, Researcher</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>Genomic Databases, Medical Data Repositories</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Biology, Data Science</t>
+        </is>
+      </c>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
+          <t>Data Organization, Data Mining, Bioinformatics Analysis</t>
+        </is>
+      </c>
+      <c r="N74" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O74" s="5" t="n"/>
+      <c r="P74" s="5" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Biological Networks</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000074</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Analytical &amp; Technical Skill</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Bioinformatics, Network Analysis</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="5" t="n"/>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Research, Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="n"/>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Research, Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>Bioinformatics Network Analyst, Systems Biologist, Researcher</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>Protein Interaction Networks, Biological Models</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>Biology, Computer Science, Data Science</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>Network Analysis, Systems Biology, Data Modeling</t>
+        </is>
+      </c>
+      <c r="N75" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O75" s="5" t="n"/>
+      <c r="P75" s="5" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000075</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Cryptography, Distributed Systems</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="5" t="n"/>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Finance, Supply Chain</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="n"/>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Technology, Supply Chain</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain Developer, Cryptography Engineer, Software Engineer</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>Cryptocurrencies, Distributed Ledgers</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Cryptography, Mathematics</t>
+        </is>
+      </c>
+      <c r="M76" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain Development, Smart Contracts, Security Protocols</t>
+        </is>
+      </c>
+      <c r="N76" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O76" s="5" t="n"/>
+      <c r="P76" s="5" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain for Compliance</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000076</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain, Regulatory Technology</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="n"/>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Technology, Legal, Compliance</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="n"/>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Compliance, Legal, Technology</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>Compliance Engineer, Blockchain Consultant, Regulatory Analyst</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>Regulatory Compliance, Smart Contracts</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Law, Business Administration</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>Regulatory Frameworks, Smart Contract Development, Auditing</t>
+        </is>
+      </c>
+      <c r="N77" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O77" s="5" t="n"/>
+      <c r="P77" s="5" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain for Fraud Detection</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000077</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain, Security, Fraud Prevention</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="n"/>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Cybersecurity, Technology</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="n"/>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Cybersecurity, Banking</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain Developer, Fraud Analyst, Security Specialist</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>Fraud Prevention, Transaction Monitoring</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Cybersecurity, Finance</t>
+        </is>
+      </c>
+      <c r="M78" s="5" t="inlineStr">
+        <is>
+          <t>Transaction Analysis, Fraud Prevention, Blockchain Security</t>
+        </is>
+      </c>
+      <c r="N78" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O78" s="5" t="n"/>
+      <c r="P78" s="5" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain Integration</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000078</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain, Software Engineering</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="5" t="n"/>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Finance, Supply Chain</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="n"/>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Technology, Supply Chain</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain Integration Specialist, Software Engineer</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain Solutions, Legacy System Integration</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Engineering, Business Administration</t>
+        </is>
+      </c>
+      <c r="M79" s="5" t="inlineStr">
+        <is>
+          <t>System Integration, Blockchain APIs, Software Development</t>
+        </is>
+      </c>
+      <c r="N79" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O79" s="5" t="n"/>
+      <c r="P79" s="5" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain Platforms</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000079</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain, Software Engineering</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="5" t="n"/>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Finance, Decentralized Apps</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="n"/>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Technology, Decentralized Applications</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain Developer, Platform Engineer, Technical Architect</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain Networks, Decentralized Apps</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Engineering, Mathematics</t>
+        </is>
+      </c>
+      <c r="M80" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain Development, Network Design, Platform Architecture</t>
+        </is>
+      </c>
+      <c r="N80" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O80" s="5" t="n"/>
+      <c r="P80" s="5" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain Scaling</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000080</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain, Distributed Systems</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="n"/>
+      <c r="F81" s="5" t="n"/>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Finance, Cryptocurrency</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="n"/>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Technology, Cryptocurrency</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain Engineer, Distributed Systems Architect, Solutions Architect</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain Networks, Cryptocurrencies</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Cryptography, Mathematics</t>
+        </is>
+      </c>
+      <c r="M81" s="5" t="inlineStr">
+        <is>
+          <t>Network Optimization, Consensus Algorithms, Scaling Solutions</t>
+        </is>
+      </c>
+      <c r="N81" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O81" s="5" t="n"/>
+      <c r="P81" s="5" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain Security</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000081</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Cybersecurity, Blockchain</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n"/>
+      <c r="F82" s="5" t="n"/>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Finance, Cybersecurity</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="n"/>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>Finance, Technology, Cryptocurrency</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain Security Engineer, Security Analyst, Cryptography Expert</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>Secure Transactions, Smart Contracts</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Cryptography, Cybersecurity</t>
+        </is>
+      </c>
+      <c r="M82" s="5" t="inlineStr">
+        <is>
+          <t>Encryption, Threat Detection, Security Auditing, Penetration Testing</t>
+        </is>
+      </c>
+      <c r="N82" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O82" s="5" t="n"/>
+      <c r="P82" s="5" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Board-Level Debugging</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000082</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Embedded Systems, Debugging</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="n"/>
+      <c r="F83" s="5" t="n"/>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Telecommunications, Technology</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="n"/>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>Electronics Manufacturing, Hardware Development</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Engineer, Embedded Systems Engineer, Debugging Specialist</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>Circuit Debugging, Microcontrollers</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Computer Science</t>
+        </is>
+      </c>
+      <c r="M83" s="5" t="inlineStr">
+        <is>
+          <t>Signal Testing, Circuit Troubleshooting, Debugging Techniques</t>
+        </is>
+      </c>
+      <c r="N83" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O83" s="5" t="n"/>
+      <c r="P83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Board-Level Design</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000083</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Hardware Engineering</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="n"/>
+      <c r="F84" s="5" t="n"/>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Automotive, Telecommunications</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="n"/>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Electronics, Telecommunications, Automotive</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Engineer, PCB Designer, Electronics Designer</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>PCB Design, Embedded Systems</t>
+        </is>
+      </c>
+      <c r="L84" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Computer Engineering</t>
+        </is>
+      </c>
+      <c r="M84" s="5" t="inlineStr">
+        <is>
+          <t>Schematic Design, Signal Integrity, PCB Layout</t>
+        </is>
+      </c>
+      <c r="N84" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O84" s="5" t="n"/>
+      <c r="P84" s="5" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>Bonding Technology</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000084</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Materials Science, Electronics</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n"/>
+      <c r="F85" s="5" t="n"/>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Manufacturing</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="n"/>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>Semiconductor Manufacturing, Electronics Assembly</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>Process Engineer, Materials Scientist, Electronics Engineer</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>Semiconductor Devices, Microelectronics</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>Materials Science, Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="M85" s="5" t="inlineStr">
+        <is>
+          <t>Bonding Techniques, Adhesive Application, Surface Interaction</t>
+        </is>
+      </c>
+      <c r="N85" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O85" s="5" t="n"/>
+      <c r="P85" s="5" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>Bootloaders</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000085</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Embedded Systems, Software Engineering</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n"/>
+      <c r="F86" s="5" t="n"/>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Automotive, Software Development</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="n"/>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>Firmware Development, Electronics, Automotive</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>Firmware Engineer, Embedded Systems Developer, Bootloader Engineer</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>Bootloading Software, Embedded Systems</t>
+        </is>
+      </c>
+      <c r="L86" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="M86" s="5" t="inlineStr">
+        <is>
+          <t>Firmware Programming, System Initialization, Low-Level Debugging</t>
+        </is>
+      </c>
+      <c r="N86" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O86" s="5" t="n"/>
+      <c r="P86" s="5" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>Brain Networks</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000086</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Scientific &amp; Technical Skill</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Neuroscience, Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="5" t="n"/>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, AI, Research</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="n"/>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, AI Research, Cognitive Science</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>Neuroscientist, AI Researcher, Cognitive Systems Engineer</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="inlineStr">
+        <is>
+          <t>Neural Networks, Brain Simulation</t>
+        </is>
+      </c>
+      <c r="L87" s="5" t="inlineStr">
+        <is>
+          <t>Neuroscience, AI, Computer Science</t>
+        </is>
+      </c>
+      <c r="M87" s="5" t="inlineStr">
+        <is>
+          <t>Neural Connectivity, Computational Neuroscience, Brain Mapping</t>
+        </is>
+      </c>
+      <c r="N87" s="5" t="inlineStr">
+        <is>
+          <t>2-3 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O87" s="5" t="n"/>
+      <c r="P87" s="5" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>Brain Simulation</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000087</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Scientific &amp; Technical Skill</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Neuroscience, AI, Simulation</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n"/>
+      <c r="F88" s="5" t="n"/>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Research, AI</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="n"/>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, Cognitive Science, AI Research</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>Neuroscientist, Simulation Scientist, Computational Neuroscientist</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>Brain Models, Cognitive Simulations</t>
+        </is>
+      </c>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>Neuroscience, AI, Computer Science</t>
+        </is>
+      </c>
+      <c r="M88" s="5" t="inlineStr">
+        <is>
+          <t>Neural Simulation, Cognitive Modeling, Brain Network Analysis</t>
+        </is>
+      </c>
+      <c r="N88" s="5" t="inlineStr">
+        <is>
+          <t>2-3 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O88" s="5" t="n"/>
+      <c r="P88" s="5" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>Brand Building</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000088</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Business &amp; Marketing Skill</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>Marketing, Branding</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="n"/>
+      <c r="F89" s="5" t="n"/>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>Retail, Consumer Goods, Marketing</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="n"/>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Goods, Digital Marketing, Retail</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>Brand Manager, Marketing Director, Digital Marketing Specialist</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="inlineStr">
+        <is>
+          <t>Brand Strategy, Marketing Campaigns</t>
+        </is>
+      </c>
+      <c r="L89" s="5" t="inlineStr">
+        <is>
+          <t>Marketing, Business Administration, Communications</t>
+        </is>
+      </c>
+      <c r="M89" s="5" t="inlineStr">
+        <is>
+          <t>Market Research, Content Creation, Audience Engagement</t>
+        </is>
+      </c>
+      <c r="N89" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O89" s="5" t="n"/>
+      <c r="P89" s="5" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>Brand Development</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000089</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Business &amp; Marketing Skill</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Marketing, Branding, Strategy</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="n"/>
+      <c r="F90" s="5" t="n"/>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>Retail, Advertising, Consumer Goods</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="n"/>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>Advertising, Retail, Consumer Goods</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>Brand Strategist, Marketing Manager, Product Manager</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="inlineStr">
+        <is>
+          <t>Brand Positioning, Product Identity</t>
+        </is>
+      </c>
+      <c r="L90" s="5" t="inlineStr">
+        <is>
+          <t>Marketing, Business Administration, Communications</t>
+        </is>
+      </c>
+      <c r="M90" s="5" t="inlineStr">
+        <is>
+          <t>Brand Strategy, Customer Insights, Competitive Analysis</t>
+        </is>
+      </c>
+      <c r="N90" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O90" s="5" t="n"/>
+      <c r="P90" s="5" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>Burn-In Testing</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000090</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Quality Assurance, Testing</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="n"/>
+      <c r="F91" s="5" t="n"/>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Automotive, Manufacturing</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="n"/>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Manufacturing, Automotive</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>Test Engineer, QA Engineer, Manufacturing Specialist</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>Product Testing, Reliability Evaluation</t>
+        </is>
+      </c>
+      <c r="L91" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="M91" s="5" t="inlineStr">
+        <is>
+          <t>Stress Testing, System Testing, Failure Prediction</t>
+        </is>
+      </c>
+      <c r="N91" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O91" s="5" t="n"/>
+      <c r="P91" s="5" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>Bus Architectures</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000091</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Computer Architecture, Hardware Design</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="n"/>
+      <c r="F92" s="5" t="n"/>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Technology, Embedded Systems</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="n"/>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>Electronics, Computer Science, Embedded Systems</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>Systems Architect, Hardware Engineer, Embedded Systems Designer</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="inlineStr">
+        <is>
+          <t>Computer Systems, Microprocessor Design</t>
+        </is>
+      </c>
+      <c r="L92" s="5" t="inlineStr">
+        <is>
+          <t>Computer Engineering, Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="M92" s="5" t="inlineStr">
+        <is>
+          <t>Data Transfer Optimization, Hardware Design, System Architecture</t>
+        </is>
+      </c>
+      <c r="N92" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O92" s="5" t="n"/>
+      <c r="P92" s="5" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Business Continuity Planning</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000092</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Business &amp; Organizational Skill</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Risk Management, Business Strategy</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="n"/>
+      <c r="F93" s="5" t="n"/>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>IT, Healthcare, Government, Corporate</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="n"/>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>IT, Healthcare, Corporate, Government</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>Business Continuity Planner, Risk Manager, Operations Manager</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="inlineStr">
+        <is>
+          <t>Continuity Plans, Disaster Recovery</t>
+        </is>
+      </c>
+      <c r="L93" s="5" t="inlineStr">
+        <is>
+          <t>Business Administration, Risk Management, IT Management</t>
+        </is>
+      </c>
+      <c r="M93" s="5" t="inlineStr">
+        <is>
+          <t>Crisis Management, Risk Analysis, Strategic Planning</t>
+        </is>
+      </c>
+      <c r="N93" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O93" s="5" t="n"/>
+      <c r="P93" s="5" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>C Programming</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000093</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Software Development, Programming</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="n"/>
+      <c r="F94" s="5" t="n"/>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Electronics, Software Development</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="n"/>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>Software Development, Embedded Systems</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>Software Developer, Embedded Systems Engineer, Programmer</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="inlineStr">
+        <is>
+          <t>Applications, Firmware, Systems Software</t>
+        </is>
+      </c>
+      <c r="L94" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Software Engineering</t>
+        </is>
+      </c>
+      <c r="M94" s="5" t="inlineStr">
+        <is>
+          <t>Algorithm Development, Memory Management, System-Level Programming</t>
+        </is>
+      </c>
+      <c r="N94" s="5" t="inlineStr">
+        <is>
+          <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O94" s="5" t="n"/>
+      <c r="P94" s="5" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>C/C++ Programming</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000094</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Software Development, Programming</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="n"/>
+      <c r="F95" s="5" t="n"/>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Gaming, Electronics, Software</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="n"/>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>Software Development, Embedded Systems, Game Development</t>
+        </is>
+      </c>
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t>Software Developer, Game Developer, Systems Programmer</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="inlineStr">
+        <is>
+          <t>Applications, Game Engines, Systems Software</t>
+        </is>
+      </c>
+      <c r="L95" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Software Engineering</t>
+        </is>
+      </c>
+      <c r="M95" s="5" t="inlineStr">
+        <is>
+          <t>Memory Management, Object-Oriented Programming, Multi-threading</t>
+        </is>
+      </c>
+      <c r="N95" s="5" t="inlineStr">
+        <is>
+          <t>1 year (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O95" s="5" t="n"/>
+      <c r="P95" s="5" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>C/C++/Fortran Programming</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000095</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Software Development, Programming</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="5" t="n"/>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Science, Research</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="n"/>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>High-Performance Computing, Embedded Systems</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>HPC Developer, Embedded Systems Engineer, Programmer</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="inlineStr">
+        <is>
+          <t>Simulation Software, Scientific Applications</t>
+        </is>
+      </c>
+      <c r="L96" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Engineering, Computational Science</t>
+        </is>
+      </c>
+      <c r="M96" s="5" t="inlineStr">
+        <is>
+          <t>Numerical Methods, Performance Optimization, Parallel Programming</t>
+        </is>
+      </c>
+      <c r="N96" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O96" s="5" t="n"/>
+      <c r="P96" s="5" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>C/C++/Python Programming</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000096</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Software Development, Programming</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="n"/>
+      <c r="F97" s="5" t="n"/>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Data Science, Gaming, Software</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="n"/>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>Software Development, Data Science, Game Development</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t>Software Developer, Data Scientist, Game Programmer</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="inlineStr">
+        <is>
+          <t>Applications, Data Analysis, Game Development</t>
+        </is>
+      </c>
+      <c r="L97" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Software Engineering, Data Science</t>
+        </is>
+      </c>
+      <c r="M97" s="5" t="inlineStr">
+        <is>
+          <t>Object-Oriented Programming, Algorithm Design, Data Structures</t>
+        </is>
+      </c>
+      <c r="N97" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O97" s="5" t="n"/>
+      <c r="P97" s="5" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>C++/Java Programming</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000097</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>Software Development, Programming</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="n"/>
+      <c r="F98" s="5" t="n"/>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Software, Mobile Development</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="n"/>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>Software Development, Web Development, Mobile Apps</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>Software Developer, Mobile App Developer, Web Developer</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="inlineStr">
+        <is>
+          <t>Applications, Web Apps, Mobile Apps</t>
+        </is>
+      </c>
+      <c r="L98" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Software Engineering</t>
+        </is>
+      </c>
+      <c r="M98" s="5" t="inlineStr">
+        <is>
+          <t>Object-Oriented Programming, Cross-platform Development, Web Development</t>
+        </is>
+      </c>
+      <c r="N98" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate expertise)</t>
+        </is>
+      </c>
+      <c r="O98" s="5" t="n"/>
+      <c r="P98" s="5" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>C++/Java/Python Programming</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000098</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Software Development, Programming</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="n"/>
+      <c r="F99" s="5" t="n"/>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Data Science, Software Development</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="n"/>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>Software Development, Data Science, Web Development</t>
+        </is>
+      </c>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>Software Developer, Data Scientist, Web Developer</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="inlineStr">
+        <is>
+          <t>Applications, Data Analysis, Web Development</t>
+        </is>
+      </c>
+      <c r="L99" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Software Engineering, Data Science</t>
+        </is>
+      </c>
+      <c r="M99" s="5" t="inlineStr">
+        <is>
+          <t>Object-Oriented Programming, Full-stack Development, Data Structures</t>
+        </is>
+      </c>
+      <c r="N99" s="5" t="inlineStr">
+        <is>
+          <t>2-3 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O99" s="5" t="n"/>
+      <c r="P99" s="5" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>C++/Python Programming</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000099</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>Software Development, Programming</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="n"/>
+      <c r="F100" s="5" t="n"/>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Software, Data Science</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="n"/>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>Software Development, Data Science, Embedded Systems</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>Software Developer, Data Scientist, Embedded Systems Engineer</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="inlineStr">
+        <is>
+          <t>Applications, Machine Learning, Embedded Systems</t>
+        </is>
+      </c>
+      <c r="L100" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Software Engineering, Data Science</t>
+        </is>
+      </c>
+      <c r="M100" s="5" t="inlineStr">
+        <is>
+          <t>Data Structures, Algorithm Optimization, Embedded Programming</t>
+        </is>
+      </c>
+      <c r="N100" s="5" t="inlineStr">
+        <is>
+          <t>1-2 years (intermediate to advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O100" s="5" t="n"/>
+      <c r="P100" s="5" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>C++/Python/Java Programming</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>SKI-000100</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Software Development, Programming</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="n"/>
+      <c r="F101" s="5" t="n"/>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>Technology, Software, Data Science</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="n"/>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>Software Development, Data Science, AI</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>Software Developer, Data Scientist, AI Engineer</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="inlineStr">
+        <is>
+          <t>Applications, Data Analysis, AI Development</t>
+        </is>
+      </c>
+      <c r="L101" s="5" t="inlineStr">
+        <is>
+          <t>Computer Science, Software Engineering, Data Science</t>
+        </is>
+      </c>
+      <c r="M101" s="5" t="inlineStr">
+        <is>
+          <t>Object-Oriented Programming, Full-stack Development, Machine Learning</t>
+        </is>
+      </c>
+      <c r="N101" s="5" t="inlineStr">
+        <is>
+          <t>2-3 years (advanced expertise)</t>
+        </is>
+      </c>
+      <c r="O101" s="5" t="n"/>
+      <c r="P101" s="5" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>

--- a/apps/api/data/excel_templates/skills.xlsx
+++ b/apps/api/data/excel_templates/skills.xlsx
@@ -57,7 +57,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -67,9 +67,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -539,6204 +536,5704 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Blockchain Development</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>SKI-000001</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>Blockchain, Software Engineering, Security</t>
         </is>
       </c>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Technology, Finance, Gaming, Security</t>
         </is>
       </c>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>FinTech, Software Development, Supply Chain, Gaming</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Blockchain Developer, Software Engineer, Smart Contract Developer</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Cryptocurrencies, Decentralized Applications, Smart Contracts</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Computer Science, Engineering, Cryptography</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Cryptography, Distributed Systems, Smart Contracts, Security</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 2-3 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O2" s="5" t="n"/>
-      <c r="P2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2D &amp; 3D Modeling</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>SKI-000002</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Creative &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Design, Computer Graphics, Animation</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Entertainment, Gaming, Architecture, VR/AR</t>
         </is>
       </c>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Game Design, Film Production, Architecture, VR/AR</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>3D Modeler, Character Artist, Industrial Designer</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Video Games, Films, Virtual Environments</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Digital Arts, Fine Arts, Game Design</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Creativity, Texturing, Lighting, Attention to Detail, Software Proficiency (e.g., Blender, Maya, ZBrush)</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O3" s="5" t="n"/>
-      <c r="P3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>3D Computational Geometry</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>SKI-000003</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Geometry, Computer Science, Visualization</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Engineering, Robotics, Gaming, Simulation</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Robotics, Engineering, Game Design, Simulation</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Computational Geometer, Robotics Engineer, Simulation Developer</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Robotics, Engineering Software, Games</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Mathematics, Computer Science, Engineering</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Geometry Algorithms, Spatial Data Structures, Programming (e.g., C++, Python)</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O4" s="5" t="n"/>
-      <c r="P4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>3D IC Design</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>SKI-000004</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Electronics, Circuit Design, Engineering</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Technology, Manufacturing</t>
         </is>
       </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Semiconductor Industry, Electronics Manufacturing</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>IC Design Engineer, Circuit Designer, Electronics Engineer</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Semiconductors, Consumer Electronics</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Electrical Engineering, Computer Engineering</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Circuit Design, CAD Tools, Signal Processing, Physical Design</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>3D Image Reconstruction</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>SKI-000005</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Computer Vision, Imaging, Medical Imaging</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Healthcare, Research, Gaming, Technology</t>
         </is>
       </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Medical Imaging, Computer Vision, Virtual Reality</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Imaging Specialist, Data Scientist, Research Scientist</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Medical Scans, 3D Models, Virtual Reality</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Computer Science, Biomedical Engineering, Mathematics</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Image Processing, Algorithms, Software Proficiency (e.g., MATLAB, OpenCV)</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>3D Molecular Visualization</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>SKI-000006</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Molecular Biology, Visualization, Computing</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Healthcare, Biotech, Pharmaceuticals</t>
         </is>
       </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Biotechnology, Healthcare, Pharmaceuticals</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Bioinformatics Specialist, Research Scientist, Computational Biologist</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Drug Development, Molecular Modeling</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Biochemistry, Bioinformatics, Computer Science</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Molecular Modeling, Visualization Tools (e.g., PyMOL, Chimera)</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>3D Packaging</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>SKI-000007</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Engineering, Design, Manufacturing</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Manufacturing, Electronics, Packaging</t>
         </is>
       </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Electronics, Consumer Goods, Packaging Industry</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Packaging Engineer, Industrial Designer, Product Designer</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Product Packaging, Electronics, Consumer Goods</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Engineering, Industrial Design, Materials Science</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>3D Printing, CAD Tools, Structural Design, Materials Selection</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Accelerated Life Testing</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>SKI-000008</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Testing, Reliability Engineering</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Manufacturing, Aerospace, Electronics</t>
         </is>
       </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Manufacturing, Electronics, Aerospace</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Reliability Engineer, Test Engineer, QA Engineer</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Product Testing, Quality Assurance</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Mechanical Engineering, Electrical Engineering</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Failure Analysis, Statistical Modeling, Stress Testing</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O9" s="5" t="n"/>
-      <c r="P9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Accelerometer Design</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>SKI-000009</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Electronics, Mechanical Engineering</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Electronics, Automotive, Aerospace</t>
         </is>
       </c>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Consumer Electronics, Automotive, Aerospace</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Sensor Design Engineer, Electronics Engineer, Mechatronics Engineer</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Wearables, Automotive Systems, Drones</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Electrical Engineering, Mechanical Engineering, Physics</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Sensor Design, Signal Processing, MEMS Technology</t>
         </is>
       </c>
-      <c r="N10" s="5" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O10" s="5" t="n"/>
-      <c r="P10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Account Development</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>SKI-000010</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Business &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Sales, Customer Relations, Marketing</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Technology, Sales, Marketing, Finance</t>
         </is>
       </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>SaaS, B2B Sales, Marketing, Business Development</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Account Manager, Sales Representative, Business Development Manager</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Enterprise Solutions, CRM Systems</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Business, Marketing, Sales</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Relationship Management, Negotiation, Communication, Data Analysis</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O11" s="5" t="n"/>
-      <c r="P11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Account Information Services</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>SKI-000011</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Technical &amp; Support Skill</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>IT Services, Data Management, Security</t>
         </is>
       </c>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Finance, Healthcare, Telecommunications</t>
         </is>
       </c>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Banking, Healthcare, Telecom, Finance</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>IT Specialist, Account Information Manager, Data Analyst</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Data Security, Information Management</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Information Technology, Computer Science</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Data Management, Security Protocols, Database Design</t>
         </is>
       </c>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O12" s="5" t="n"/>
-      <c r="P12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>ADC/DAC</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>SKI-000012</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Electronics, Signal Processing</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Telecommunications, Consumer Electronics</t>
         </is>
       </c>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Telecommunications, Audio/Video, Consumer Electronics</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Electronics Engineer, Signal Processing Engineer</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Audio Devices, Communication Systems</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Electrical Engineering, Signal Processing</t>
         </is>
       </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Analog to Digital Conversion, Signal Processing, Circuit Design</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O13" s="5" t="n"/>
-      <c r="P13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Advanced Packaging</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>SKI-000013</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Engineering, Manufacturing</t>
         </is>
       </c>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Manufacturing, Electronics, Consumer Goods</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Electronics, Semiconductor, Consumer Goods</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Packaging Engineer, Process Engineer, Materials Scientist</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Microelectronics, Consumer Electronics</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Mechanical Engineering, Materials Science</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>3D Modeling, Thermal Management, Structural Integrity</t>
         </is>
       </c>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O14" s="5" t="n"/>
-      <c r="P14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>AI for Fraud Detection</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>SKI-000014</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Artificial Intelligence, Data Science</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Finance, Cybersecurity, E-commerce</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Finance, E-commerce, Banking, Cybersecurity</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Data Scientist, AI Engineer, Fraud Analyst</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Fraud Detection Systems, Security Software</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Computer Science, Data Science, Engineering</t>
         </is>
       </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Machine Learning, Pattern Recognition, Data Analytics</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O15" s="5" t="n"/>
-      <c r="P15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Algorithm Development</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>SKI-000015</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering</t>
         </is>
       </c>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Technology, Finance, AI, Data Science</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Software Development, Machine Learning, Data Science</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Software Engineer, Data Scientist, Algorithm Engineer</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Software Algorithms, Data Processing, AI Models</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Computer Science, Mathematics, Engineering</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Problem Solving, Optimization, Data Structures, Programming</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O16" s="5" t="n"/>
-      <c r="P16" s="5" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Algorithmic Bias</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>SKI-000016</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Analytical Skill</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Data Science, Ethics, AI</t>
         </is>
       </c>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Technology, Ethics, Data Science</t>
         </is>
       </c>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>AI, Machine Learning, Social Sciences</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>AI Researcher, Data Scientist, Ethicist</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>AI Models, Machine Learning Systems</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Computer Science, Ethics, Social Science</t>
         </is>
       </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Bias Detection, Fairness in AI, Ethical Decision Making</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O17" s="5" t="n"/>
-      <c r="P17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Algorithmic Bias Analysis</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>SKI-000017</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Analytical Skill</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Data Science, Ethics, AI</t>
         </is>
       </c>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Technology, Ethics, Data Science</t>
         </is>
       </c>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>AI, Machine Learning, Social Sciences</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>AI Researcher, Data Scientist, Ethicist, Policy Analyst</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>AI Models, Bias Detection Systems</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Computer Science, Ethics, Social Science</t>
         </is>
       </c>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Fairness Audits, Algorithmic Evaluation, Bias Metrics</t>
         </is>
       </c>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O18" s="5" t="n"/>
-      <c r="P18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Algorithmic Complexity</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>SKI-000018</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Analytical &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Computer Science, Mathematics</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Technology, Research, AI, Academia</t>
         </is>
       </c>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Software Development, Research, AI</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Algorithm Engineer, Data Scientist, Software Engineer</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Algorithm Optimization, Complexity Analysis</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Computer Science, Mathematics</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Complexity Theory, Algorithmic Design, Data Structures</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O19" s="5" t="n"/>
-      <c r="P19" s="5" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Algorithmic Problem Solving</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>SKI-000019</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Analytical &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Problem Solving, Computer Science</t>
         </is>
       </c>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Technology, Finance, Research, AI</t>
         </is>
       </c>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Software Development, Competitive Programming, AI</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Software Engineer, Data Scientist, Algorithm Developer</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Coding Competitions, AI Models, Optimization</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>Computer Science, Mathematics, Engineering</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Critical Thinking, Logical Reasoning, Programming Skills</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O20" s="5" t="n"/>
-      <c r="P20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Algorithmic Trading</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>SKI-000020</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Finance, Data Science, Software Engineering</t>
         </is>
       </c>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Finance, Technology, Trading</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Financial Markets, Hedge Funds, Trading Platforms</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Quantitative Analyst, Algorithmic Trader, Data Scientist</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Trading Algorithms, Financial Models, Market Analytics</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Finance, Computer Science, Mathematics</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Data Analysis, Statistical Modeling, Market Knowledge</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O21" s="5" t="n"/>
-      <c r="P21" s="5" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Algorithms for Chemical Data</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>SKI-000021</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>Data Science, Chemistry, Machine Learning</t>
         </is>
       </c>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Pharmaceuticals, Biotech, Chemistry</t>
         </is>
       </c>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Pharmaceuticals, Biotechnology, Chemical Engineering</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Data Scientist, Chemoinformatics Specialist, Research Scientist</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Chemical Data Models, Drug Discovery Tools</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Chemistry, Computer Science, Biostatistics</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Chemoinformatics, Pattern Recognition, Statistical Analysis</t>
         </is>
       </c>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O22" s="5" t="n"/>
-      <c r="P22" s="5" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Altera/Intel FPGA</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>SKI-000022</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>Electronics, Hardware Engineering, Programming</t>
         </is>
       </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Technology, Telecommunications, Electronics</t>
         </is>
       </c>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Telecommunications, Consumer Electronics, Computing</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>FPGA Engineer, Hardware Engineer, Embedded Systems Developer</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Embedded Systems, Hardware Acceleration</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Electrical Engineering, Computer Engineering, Physics</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>FPGA Programming, Hardware Design, Circuit Design</t>
         </is>
       </c>
-      <c r="N23" s="5" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O23" s="5" t="n"/>
-      <c r="P23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>AML</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>SKI-000023</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Regulatory &amp; Analytical Skill</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Finance, Compliance, Risk Management</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Finance, Banking, Regulatory Compliance</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Banking, Finance, Compliance, Security</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Compliance Officer, Risk Analyst, AML Specialist</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Anti-Money Laundering Systems, Risk Management</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>Finance, Law, Risk Management</t>
         </is>
       </c>
-      <c r="M24" s="5" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Regulatory Knowledge, Risk Assessment, Investigation Techniques</t>
         </is>
       </c>
-      <c r="N24" s="5" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O24" s="5" t="n"/>
-      <c r="P24" s="5" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Amplifiers</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>SKI-000024</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Electronics, Signal Processing</t>
         </is>
       </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Electronics, Telecommunications, Audio</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Audio Systems, Telecommunications, Consumer Electronics</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Electronics Engineer, Audio Engineer, Signal Processing Engineer</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Audio Amplifiers, Communication Systems</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Electrical Engineering, Audio Engineering</t>
         </is>
       </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Signal Amplification, Circuit Design, Frequency Response</t>
         </is>
       </c>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O25" s="5" t="n"/>
-      <c r="P25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Analog and Digital Design</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>SKI-000025</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>Electronics, Circuit Design, Engineering</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Electronics, Automotive, Telecommunications</t>
         </is>
       </c>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Consumer Electronics, Automotive, Telecommunications</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Circuit Designer, Electronics Engineer, Embedded Systems Engineer</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Consumer Electronics, Communication Devices</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Electrical Engineering, Physics, Computer Engineering</t>
         </is>
       </c>
-      <c r="M26" s="5" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Circuit Design, Signal Processing, Mixed-Signal Systems</t>
         </is>
       </c>
-      <c r="N26" s="5" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O26" s="5" t="n"/>
-      <c r="P26" s="5" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Analog Circuit Design</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>SKI-000026</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Electronics, Circuit Design</t>
         </is>
       </c>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Electronics, Automotive, Telecommunications</t>
         </is>
       </c>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Consumer Electronics, Telecommunications, Automotive</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Circuit Designer, Electronics Engineer, Embedded Systems Engineer</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>Audio Devices, Communication Systems, Consumer Electronics</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Electrical Engineering, Physics, Computer Engineering</t>
         </is>
       </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Circuit Design, Signal Integrity, Frequency Response</t>
         </is>
       </c>
-      <c r="N27" s="5" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O27" s="5" t="n"/>
-      <c r="P27" s="5" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Analog-to-Digital Conversion</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>SKI-000027</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>Electronics, Signal Processing, Data Acquisition</t>
         </is>
       </c>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Electronics, Telecommunications, Audio</t>
         </is>
       </c>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Audio Systems, Communication Systems, Consumer Electronics</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Electronics Engineer, Signal Processing Engineer, Embedded Systems Developer</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>ADCs, Communication Systems, Consumer Electronics</t>
         </is>
       </c>
-      <c r="L28" s="5" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Electrical Engineering, Physics, Computer Engineering</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Analog-to-Digital Conversion, Signal Processing, Data Acquisition</t>
         </is>
       </c>
-      <c r="N28" s="5" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O28" s="5" t="n"/>
-      <c r="P28" s="5" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Antenna Design</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>SKI-000028</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Electronics, Communication Systems, Engineering</t>
         </is>
       </c>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Telecommunications, Aerospace, Electronics</t>
         </is>
       </c>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Telecommunications, Aerospace, Consumer Electronics</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>RF Engineer, Antenna Engineer, Communications Systems Engineer</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Communication Systems, Wireless Networks</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Electrical Engineering, Physics, Telecommunications</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>RF Design, Antenna Modeling, Wireless Communication</t>
         </is>
       </c>
-      <c r="N29" s="5" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O29" s="5" t="n"/>
-      <c r="P29" s="5" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>API Gateways</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>SKI-000029</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Software Engineering, Cloud Computing, Networking</t>
         </is>
       </c>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Technology, Cloud Computing, SaaS</t>
         </is>
       </c>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Web Development, Cloud Applications, SaaS</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>API Engineer, Backend Developer, Cloud Solutions Architect</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>Web Applications, Cloud Services, Microservices</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering, Networking</t>
         </is>
       </c>
-      <c r="M30" s="5" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>API Design, Authentication, Load Balancing, Service Integration</t>
         </is>
       </c>
-      <c r="N30" s="5" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O30" s="5" t="n"/>
-      <c r="P30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>API Security</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>SKI-000030</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>Cybersecurity, Software Engineering</t>
         </is>
       </c>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Technology, Cybersecurity, Cloud Computing</t>
         </is>
       </c>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Web Development, Cloud Computing, SaaS</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Security Engineer, API Security Specialist, Backend Developer</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>Web Applications, API Security Systems</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Computer Science, Cybersecurity</t>
         </is>
       </c>
-      <c r="M31" s="5" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Encryption, Authentication, Access Control, Security Protocols</t>
         </is>
       </c>
-      <c r="N31" s="5" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O31" s="5" t="n"/>
-      <c r="P31" s="5" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Application Development</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>SKI-000031</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>Software Engineering, Web Development</t>
         </is>
       </c>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Technology, Mobile, Web Development</t>
         </is>
       </c>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>Mobile Apps, Web Apps, Enterprise Software</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Software Developer, Mobile Developer, Full Stack Developer</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Mobile Applications, Web Platforms</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering</t>
         </is>
       </c>
-      <c r="M32" s="5" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Programming, UI/UX Design, Databases, Problem Solving</t>
         </is>
       </c>
-      <c r="N32" s="5" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O32" s="5" t="n"/>
-      <c r="P32" s="5" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Application Engineering</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>SKI-000032</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>Software Engineering, Product Design</t>
         </is>
       </c>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Technology, Electronics, Consumer Goods</t>
         </is>
       </c>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>SaaS, Embedded Systems, Consumer Electronics</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Application Engineer, Software Engineer, Systems Engineer</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Software Applications, Embedded Systems</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Computer Science, Engineering, Product Design</t>
         </is>
       </c>
-      <c r="M33" s="5" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Software Design, Debugging, System Integration, User Experience</t>
         </is>
       </c>
-      <c r="N33" s="5" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O33" s="5" t="n"/>
-      <c r="P33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Appointment Scheduling</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>SKI-000033</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Software Development, Business Operations</t>
         </is>
       </c>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Healthcare, Education, Business Services</t>
         </is>
       </c>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>Healthcare, Business Services, Education</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Scheduling Software Developer, Operations Coordinator, IT Specialist</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Appointment Scheduling Systems, Calendar Apps</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Computer Science, Business Administration</t>
         </is>
       </c>
-      <c r="M34" s="5" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Time Management, Database Design, User Interface Design</t>
         </is>
       </c>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O34" s="5" t="n"/>
-      <c r="P34" s="5" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Approximation Algorithms</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>SKI-000034</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Analytical &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Algorithms, Computer Science, Optimization</t>
         </is>
       </c>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Technology, Research, AI, Operations Research</t>
         </is>
       </c>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>Machine Learning, Data Science, Operations Research</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Algorithm Engineer, Data Scientist, Researcher</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Optimization Problems, Computational Models</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>Computer Science, Mathematics, Operations Research</t>
         </is>
       </c>
-      <c r="M35" s="5" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Algorithm Design, Approximation Techniques, Computational Complexity</t>
         </is>
       </c>
-      <c r="N35" s="5" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O35" s="5" t="n"/>
-      <c r="P35" s="5" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Approximation Theory</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>SKI-000035</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Analytical &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Mathematics, Algorithms</t>
         </is>
       </c>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Mathematics, Technology, Research</t>
         </is>
       </c>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>AI, Operations Research, Data Science</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Researcher, Algorithm Developer, Data Scientist</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>Computational Models, Optimization Algorithms</t>
         </is>
       </c>
-      <c r="L36" s="5" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>Mathematics, Computer Science, Operations Research</t>
         </is>
       </c>
-      <c r="M36" s="5" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Theoretical Analysis, Approximation Methods, Proofs of Bounds</t>
         </is>
       </c>
-      <c r="N36" s="5" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O36" s="5" t="n"/>
-      <c r="P36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>ARM Architecture</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>SKI-000036</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Computer Architecture, Hardware Design</t>
         </is>
       </c>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Electronics, Consumer Electronics, Mobile</t>
         </is>
       </c>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Mobile Devices, Embedded Systems, Consumer Electronics</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Embedded Systems Engineer, Hardware Engineer, Firmware Developer</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>Mobile Devices, Embedded Systems</t>
         </is>
       </c>
-      <c r="L37" s="5" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Electrical Engineering, Computer Engineering</t>
         </is>
       </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>ARM Assembly, Processor Design, Low-Level Programming</t>
         </is>
       </c>
-      <c r="N37" s="5" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O37" s="5" t="n"/>
-      <c r="P37" s="5" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>ASIC Design</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>SKI-000037</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>Electronics, Hardware Design</t>
         </is>
       </c>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Electronics, Telecommunications, Computing</t>
         </is>
       </c>
-      <c r="H38" s="5" t="n"/>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>Telecommunications, Consumer Electronics, Computing</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>ASIC Engineer, Hardware Engineer, System-on-Chip (SoC) Designer</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>Integrated Circuits, Consumer Electronics</t>
         </is>
       </c>
-      <c r="L38" s="5" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>Electrical Engineering, Computer Engineering</t>
         </is>
       </c>
-      <c r="M38" s="5" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Circuit Design, Hardware Description Languages, Optimization Techniques</t>
         </is>
       </c>
-      <c r="N38" s="5" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O38" s="5" t="n"/>
-      <c r="P38" s="5" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Assertion Languages</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>SKI-000038</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Software Engineering, Verification</t>
         </is>
       </c>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Electronics, Software Engineering</t>
         </is>
       </c>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Embedded Systems, Semiconductor Design, Formal Verification</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Verification Engineer, Hardware Engineer, Software Tester</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Design Verification, Testbenches</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>Electrical Engineering, Computer Science</t>
         </is>
       </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Formal Methods, Hardware Verification, Test Automation</t>
         </is>
       </c>
-      <c r="N39" s="5" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O39" s="5" t="n"/>
-      <c r="P39" s="5" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Assertion-Based Verification</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>SKI-000039</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>Software Verification, Hardware Design</t>
         </is>
       </c>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Electronics, Software Engineering</t>
         </is>
       </c>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>Semiconductor Design, Embedded Systems, Software Development</t>
         </is>
       </c>
-      <c r="J40" s="5" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Verification Engineer, Embedded Systems Engineer, Hardware Engineer</t>
         </is>
       </c>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>Verification Tools, Testbenches, Simulation Models</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>Electrical Engineering, Computer Science, Software Engineering</t>
         </is>
       </c>
-      <c r="M40" s="5" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Formal Verification, Test Automation, Debugging, Model Checking</t>
         </is>
       </c>
-      <c r="N40" s="5" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O40" s="5" t="n"/>
-      <c r="P40" s="5" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Asset Allocation</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>SKI-000040</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Financial Skill</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Finance, Investment Management</t>
         </is>
       </c>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Finance, Investment, Wealth Management</t>
         </is>
       </c>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>Hedge Funds, Wealth Management, Financial Planning</t>
         </is>
       </c>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Portfolio Manager, Financial Analyst, Investment Advisor</t>
         </is>
       </c>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>Investment Portfolios, Risk Management</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>Finance, Economics, Mathematics</t>
         </is>
       </c>
-      <c r="M41" s="5" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Risk Management, Portfolio Diversification, Statistical Analysis</t>
         </is>
       </c>
-      <c r="N41" s="5" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O41" s="5" t="n"/>
-      <c r="P41" s="5" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Asset Valuation</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>SKI-000041</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Financial Skill</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Finance, Real Estate, Investment</t>
         </is>
       </c>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Finance, Real Estate, Private Equity</t>
         </is>
       </c>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>Real Estate, Private Equity, Public Markets</t>
         </is>
       </c>
-      <c r="J42" s="5" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Valuation Analyst, Financial Analyst, Real Estate Appraiser</t>
         </is>
       </c>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>Investment Valuation, Property Valuation</t>
         </is>
       </c>
-      <c r="L42" s="5" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>Finance, Economics, Real Estate</t>
         </is>
       </c>
-      <c r="M42" s="5" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>Market Analysis, Discounted Cash Flow, Comparable Analysis</t>
         </is>
       </c>
-      <c r="N42" s="5" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O42" s="5" t="n"/>
-      <c r="P42" s="5" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Astronomy</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>SKI-000042</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Scientific Skill</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Space Science, Physics</t>
         </is>
       </c>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Research, Education, Space Exploration</t>
         </is>
       </c>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>Research, Education, Space Exploration</t>
         </is>
       </c>
-      <c r="J43" s="5" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Astronomer, Astrophysicist, Research Scientist</t>
         </is>
       </c>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>Space Research, Telescopes, Space Missions</t>
         </is>
       </c>
-      <c r="L43" s="5" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>Physics, Astronomy, Mathematics</t>
         </is>
       </c>
-      <c r="M43" s="5" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>Celestial Observation, Telescope Operation, Research Methods</t>
         </is>
       </c>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>2-3 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O43" s="5" t="n"/>
-      <c r="P43" s="5" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Astronomy Data Formats</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>SKI-000043</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>Data Science, Astronomy, Software Engineering</t>
         </is>
       </c>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Research, Space Science, Astronomy</t>
         </is>
       </c>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>Space Research, Data Science, Astrophysics</t>
         </is>
       </c>
-      <c r="J44" s="5" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Data Scientist, Researcher, Software Developer</t>
         </is>
       </c>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>Space Observations, Data Analysis</t>
         </is>
       </c>
-      <c r="L44" s="5" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>Computer Science, Astronomy, Data Science</t>
         </is>
       </c>
-      <c r="M44" s="5" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>Data Parsing, Format Conversion, Data Storage Systems</t>
         </is>
       </c>
-      <c r="N44" s="5" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O44" s="5" t="n"/>
-      <c r="P44" s="5" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Astrophysical Modeling</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>SKI-000044</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Scientific &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Astrophysics, Computational Modeling</t>
         </is>
       </c>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Research, Space Science, Education</t>
         </is>
       </c>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>Space Research, Simulation, Education</t>
         </is>
       </c>
-      <c r="J45" s="5" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Astrophysicist, Computational Scientist, Researcher</t>
         </is>
       </c>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>Space Simulations, Astrophysical Models</t>
         </is>
       </c>
-      <c r="L45" s="5" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>Physics, Mathematics, Computer Science</t>
         </is>
       </c>
-      <c r="M45" s="5" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Numerical Simulation, Mathematical Modeling, Computational Physics</t>
         </is>
       </c>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O45" s="5" t="n"/>
-      <c r="P45" s="5" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Astrophysical Simulations</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>SKI-000045</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>Astrophysics, Computational Science</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="n"/>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Research, Space Science, Education</t>
         </is>
       </c>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>Research, Space Science, Simulations</t>
         </is>
       </c>
-      <c r="J46" s="5" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Astrophysicist, Simulation Specialist, Research Scientist</t>
         </is>
       </c>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>Computational Models, Simulation Software</t>
         </is>
       </c>
-      <c r="L46" s="5" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>Physics, Computer Science, Mathematics</t>
         </is>
       </c>
-      <c r="M46" s="5" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>Simulation Software, Numerical Methods, High-Performance Computing</t>
         </is>
       </c>
-      <c r="N46" s="5" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O46" s="5" t="n"/>
-      <c r="P46" s="5" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Astrophysics</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>SKI-000046</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Scientific Skill</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Physics, Space Science</t>
         </is>
       </c>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Research, Space Science, Education</t>
         </is>
       </c>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>Research, Education, Space Exploration</t>
         </is>
       </c>
-      <c r="J47" s="5" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Astrophysicist, Research Scientist, Educator</t>
         </is>
       </c>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>Space Research, Scientific Discoveries</t>
         </is>
       </c>
-      <c r="L47" s="5" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>Physics, Mathematics, Astronomy</t>
         </is>
       </c>
-      <c r="M47" s="5" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>Theoretical Physics, Research, Data Analysis, Observation Methods</t>
         </is>
       </c>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>2-3 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O47" s="5" t="n"/>
-      <c r="P47" s="5" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>ATE</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>SKI-000047</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>Electronics, Testing, Engineering</t>
         </is>
       </c>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="n"/>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Electronics, Aerospace, Automotive</t>
         </is>
       </c>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>Electronics Manufacturing, Aerospace, Automotive</t>
         </is>
       </c>
-      <c r="J48" s="5" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Test Engineer, ATE Engineer, Electronics Engineer</t>
         </is>
       </c>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>Testing Systems, Electronics Validation</t>
         </is>
       </c>
-      <c r="L48" s="5" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>Electrical Engineering, Computer Science, Physics</t>
         </is>
       </c>
-      <c r="M48" s="5" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Test Automation, Hardware Testing, Software Integration</t>
         </is>
       </c>
-      <c r="N48" s="5" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O48" s="5" t="n"/>
-      <c r="P48" s="5" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>ATE Equipment Maintenance</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>SKI-000048</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>Electronics, Maintenance, Engineering</t>
         </is>
       </c>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="n"/>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Electronics, Aerospace, Manufacturing</t>
         </is>
       </c>
-      <c r="H49" s="5" t="n"/>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>Manufacturing, Aerospace, Electronics Repair</t>
         </is>
       </c>
-      <c r="J49" s="5" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Maintenance Technician, ATE Engineer, Repair Specialist</t>
         </is>
       </c>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>Test Equipment, Circuit Boards, Diagnostic Systems</t>
         </is>
       </c>
-      <c r="L49" s="5" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>Electrical Engineering, Mechanical Engineering</t>
         </is>
       </c>
-      <c r="M49" s="5" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>Troubleshooting, Maintenance Protocols, Diagnostics</t>
         </is>
       </c>
-      <c r="N49" s="5" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O49" s="5" t="n"/>
-      <c r="P49" s="5" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Atmospheric Modeling</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>SKI-000049</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Scientific &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Atmospheric Science, Environmental Science</t>
         </is>
       </c>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="n"/>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Environmental Science, Aerospace, Research</t>
         </is>
       </c>
-      <c r="H50" s="5" t="n"/>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>Meteorology, Climate Science, Aerospace</t>
         </is>
       </c>
-      <c r="J50" s="5" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>Atmospheric Scientist, Meteorologist, Climate Modeler</t>
         </is>
       </c>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>Weather Forecasting, Climate Simulations</t>
         </is>
       </c>
-      <c r="L50" s="5" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>Environmental Science, Atmospheric Science, Physics</t>
         </is>
       </c>
-      <c r="M50" s="5" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>Numerical Weather Prediction, Data Assimilation, Climate Modeling</t>
         </is>
       </c>
-      <c r="N50" s="5" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O50" s="5" t="n"/>
-      <c r="P50" s="5" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Audit Coordination</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>SKI-000050</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Business &amp; Organizational Skill</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Audit, Risk Management, Compliance</t>
         </is>
       </c>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="n"/>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Finance, Healthcare, Government, Corporate</t>
         </is>
       </c>
-      <c r="H51" s="5" t="n"/>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>Finance, Healthcare, Government, Corporate</t>
         </is>
       </c>
-      <c r="J51" s="5" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>Audit Manager, Audit Coordinator, Compliance Officer</t>
         </is>
       </c>
-      <c r="K51" s="5" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>Audit Processes, Risk Management</t>
         </is>
       </c>
-      <c r="L51" s="5" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>Business Administration, Finance, Accounting</t>
         </is>
       </c>
-      <c r="M51" s="5" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>Coordination, Risk Assessment, Documentation, Regulatory Knowledge</t>
         </is>
       </c>
-      <c r="N51" s="5" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O51" s="5" t="n"/>
-      <c r="P51" s="5" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Audit Methodologies</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>SKI-000051</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Analytical &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Audit, Risk Management, Compliance</t>
         </is>
       </c>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Finance, Healthcare, Government, Corporate</t>
         </is>
       </c>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>Finance, Government, Healthcare, Corporate</t>
         </is>
       </c>
-      <c r="J52" s="5" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>Auditor, Risk Analyst, Compliance Specialist</t>
         </is>
       </c>
-      <c r="K52" s="5" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>Audit Processes, Compliance Testing</t>
         </is>
       </c>
-      <c r="L52" s="5" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>Accounting, Finance, Business Administration</t>
         </is>
       </c>
-      <c r="M52" s="5" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>Internal Control Frameworks, Risk Assessment, Regulatory Knowledge</t>
         </is>
       </c>
-      <c r="N52" s="5" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O52" s="5" t="n"/>
-      <c r="P52" s="5" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Authentication Protocols</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>SKI-000052</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>Cybersecurity, Networking</t>
         </is>
       </c>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="n"/>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Technology, Cybersecurity, IT</t>
         </is>
       </c>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>Web Development, Cloud Computing, IT Security</t>
         </is>
       </c>
-      <c r="J53" s="5" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>Security Engineer, Network Engineer, Cybersecurity Analyst</t>
         </is>
       </c>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>Security Systems, Cloud Authentication</t>
         </is>
       </c>
-      <c r="L53" s="5" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>Computer Science, Network Engineering, Cybersecurity</t>
         </is>
       </c>
-      <c r="M53" s="5" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>Encryption, Access Control, Protocol Analysis, Identity Management</t>
         </is>
       </c>
-      <c r="N53" s="5" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O53" s="5" t="n"/>
-      <c r="P53" s="5" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Automated Assembly</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>SKI-000053</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>Manufacturing, Robotics</t>
         </is>
       </c>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="n"/>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Manufacturing, Automotive, Electronics</t>
         </is>
       </c>
-      <c r="H54" s="5" t="n"/>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>Manufacturing, Automotive, Consumer Electronics</t>
         </is>
       </c>
-      <c r="J54" s="5" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>Automation Engineer, Robotics Engineer, Manufacturing Engineer</t>
         </is>
       </c>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>Production Lines, Robotics Systems</t>
         </is>
       </c>
-      <c r="L54" s="5" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>Mechanical Engineering, Electrical Engineering</t>
         </is>
       </c>
-      <c r="M54" s="5" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>Robotics, Process Optimization, Mechatronics, System Integration</t>
         </is>
       </c>
-      <c r="N54" s="5" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O54" s="5" t="n"/>
-      <c r="P54" s="5" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Automated Test Equipment</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>SKI-000054</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>Electronics, Testing, Engineering</t>
         </is>
       </c>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="n"/>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Electronics, Aerospace, Automotive</t>
         </is>
       </c>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>Electronics Manufacturing, Aerospace, Automotive</t>
         </is>
       </c>
-      <c r="J55" s="5" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>Test Engineer, ATE Engineer, Electronics Engineer</t>
         </is>
       </c>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>Testing Systems, Circuit Boards, Validation</t>
         </is>
       </c>
-      <c r="L55" s="5" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>Electrical Engineering, Computer Science, Physics</t>
         </is>
       </c>
-      <c r="M55" s="5" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>Test Automation, Hardware Testing, Software Integration</t>
         </is>
       </c>
-      <c r="N55" s="5" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O55" s="5" t="n"/>
-      <c r="P55" s="5" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Automation Systems</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>SKI-000055</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>Engineering, Robotics, Control Systems</t>
         </is>
       </c>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="n"/>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Manufacturing, Aerospace, Energy, Robotics</t>
         </is>
       </c>
-      <c r="H56" s="5" t="n"/>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>Manufacturing, Automotive, Energy, Aerospace</t>
         </is>
       </c>
-      <c r="J56" s="5" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>Automation Engineer, Robotics Engineer, System Integrator</t>
         </is>
       </c>
-      <c r="K56" s="5" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>Automated Production Lines, Robotics, Control Systems</t>
         </is>
       </c>
-      <c r="L56" s="5" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>Mechanical Engineering, Electrical Engineering</t>
         </is>
       </c>
-      <c r="M56" s="5" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>Robotics, Control Theory, System Design, Automation Technology</t>
         </is>
       </c>
-      <c r="N56" s="5" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O56" s="5" t="n"/>
-      <c r="P56" s="5" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Automation Tools</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>SKI-000056</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>Software Engineering, Automation, Tools</t>
         </is>
       </c>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="n"/>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>IT, Software, Manufacturing</t>
         </is>
       </c>
-      <c r="H57" s="5" t="n"/>
-      <c r="I57" s="5" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>IT, Software Development, Manufacturing</t>
         </is>
       </c>
-      <c r="J57" s="5" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>Automation Developer, Software Engineer, Tools Specialist</t>
         </is>
       </c>
-      <c r="K57" s="5" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>Testing Tools, Automation Frameworks</t>
         </is>
       </c>
-      <c r="L57" s="5" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering</t>
         </is>
       </c>
-      <c r="M57" s="5" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>Scripting, Process Automation, Tool Development, Integration</t>
         </is>
       </c>
-      <c r="N57" s="5" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O57" s="5" t="n"/>
-      <c r="P57" s="5" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Automotive Safety Standards</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>SKI-000057</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Regulatory &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Automotive, Safety, Compliance</t>
         </is>
       </c>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="n"/>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Automotive, Engineering, Compliance</t>
         </is>
       </c>
-      <c r="H58" s="5" t="n"/>
-      <c r="I58" s="5" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>Automotive Manufacturing, Automotive Design</t>
         </is>
       </c>
-      <c r="J58" s="5" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>Safety Engineer, Regulatory Compliance Officer, Automotive Engineer</t>
         </is>
       </c>
-      <c r="K58" s="5" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>Vehicle Safety Systems, Compliance Testing</t>
         </is>
       </c>
-      <c r="L58" s="5" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>Mechanical Engineering, Automotive Engineering, Law</t>
         </is>
       </c>
-      <c r="M58" s="5" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>Safety Protocols, Regulatory Standards, Vehicle Testing</t>
         </is>
       </c>
-      <c r="N58" s="5" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O58" s="5" t="n"/>
-      <c r="P58" s="5" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Automotive Systems</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>SKI-000058</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
         <is>
           <t>Automotive Engineering, Electronics</t>
         </is>
       </c>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="5" t="n"/>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Automotive, Electronics</t>
         </is>
       </c>
-      <c r="H59" s="5" t="n"/>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>Automotive Design, Automotive Manufacturing</t>
         </is>
       </c>
-      <c r="J59" s="5" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>Automotive Engineer, Systems Engineer, Electronics Engineer</t>
         </is>
       </c>
-      <c r="K59" s="5" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>Automotive Components, Infotainment Systems</t>
         </is>
       </c>
-      <c r="L59" s="5" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>Mechanical Engineering, Electrical Engineering, Automotive Technology</t>
         </is>
       </c>
-      <c r="M59" s="5" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>Systems Design, Integration, Embedded Systems, Diagnostics</t>
         </is>
       </c>
-      <c r="N59" s="5" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O59" s="5" t="n"/>
-      <c r="P59" s="5" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Automotive Testing</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>SKI-000059</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
         <is>
           <t>Automotive Engineering, Testing</t>
         </is>
       </c>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="n"/>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Automotive, Engineering</t>
         </is>
       </c>
-      <c r="H60" s="5" t="n"/>
-      <c r="I60" s="5" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>Automotive Manufacturing, Research, Development</t>
         </is>
       </c>
-      <c r="J60" s="5" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>Test Engineer, Automotive Engineer, Quality Assurance Specialist</t>
         </is>
       </c>
-      <c r="K60" s="5" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>Vehicle Testing, Crash Simulation, Performance Evaluation</t>
         </is>
       </c>
-      <c r="L60" s="5" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>Mechanical Engineering, Automotive Engineering, Testing Methods</t>
         </is>
       </c>
-      <c r="M60" s="5" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>Vehicle Diagnostics, Performance Testing, Safety Standards</t>
         </is>
       </c>
-      <c r="N60" s="5" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O60" s="5" t="n"/>
-      <c r="P60" s="5" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Autonomous Systems</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>SKI-000060</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>Robotics, AI, Engineering</t>
         </is>
       </c>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="5" t="n"/>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Robotics, Automotive, Aerospace, Technology</t>
         </is>
       </c>
-      <c r="H61" s="5" t="n"/>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>Robotics, Autonomous Vehicles, Aerospace</t>
         </is>
       </c>
-      <c r="J61" s="5" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>Robotics Engineer, Autonomous Vehicle Engineer, AI Specialist</t>
         </is>
       </c>
-      <c r="K61" s="5" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>Self-Driving Cars, Drones, Robotic Systems</t>
         </is>
       </c>
-      <c r="L61" s="5" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>Robotics, Computer Science, Electrical Engineering</t>
         </is>
       </c>
-      <c r="M61" s="5" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>Machine Learning, Sensor Integration, System Design, Path Planning</t>
         </is>
       </c>
-      <c r="N61" s="5" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O61" s="5" t="n"/>
-      <c r="P61" s="5" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Backtesting</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>SKI-000061</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Analytical &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>Finance, Data Science, Algorithms</t>
         </is>
       </c>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="5" t="n"/>
-      <c r="G62" s="5" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Finance, Investment, Trading</t>
         </is>
       </c>
-      <c r="H62" s="5" t="n"/>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>Trading, Investment, Financial Planning</t>
         </is>
       </c>
-      <c r="J62" s="5" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>Quantitative Analyst, Algorithmic Trader, Data Scientist</t>
         </is>
       </c>
-      <c r="K62" s="5" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>Financial Models, Trading Strategies</t>
         </is>
       </c>
-      <c r="L62" s="5" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>Finance, Economics, Data Science</t>
         </is>
       </c>
-      <c r="M62" s="5" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>Statistical Modeling, Risk Management, Performance Evaluation</t>
         </is>
       </c>
-      <c r="N62" s="5" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O62" s="5" t="n"/>
-      <c r="P62" s="5" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>Banking Platforms Integration</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>SKI-000062</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
         <is>
           <t>Finance, Software Engineering</t>
         </is>
       </c>
-      <c r="E63" s="5" t="n"/>
-      <c r="F63" s="5" t="n"/>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Banking, Fintech, Technology</t>
         </is>
       </c>
-      <c r="H63" s="5" t="n"/>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>Banking, Fintech, Payment Systems</t>
         </is>
       </c>
-      <c r="J63" s="5" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>Integration Specialist, Banking Software Engineer, IT Specialist</t>
         </is>
       </c>
-      <c r="K63" s="5" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>Core Banking Systems, Payment Gateways</t>
         </is>
       </c>
-      <c r="L63" s="5" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>Computer Science, Finance, Software Engineering</t>
         </is>
       </c>
-      <c r="M63" s="5" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>API Integration, Security, System Interoperability</t>
         </is>
       </c>
-      <c r="N63" s="5" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O63" s="5" t="n"/>
-      <c r="P63" s="5" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Banking Software</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>SKI-000063</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
         <is>
           <t>Software Engineering, Finance</t>
         </is>
       </c>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="n"/>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Banking, Fintech, Technology</t>
         </is>
       </c>
-      <c r="H64" s="5" t="n"/>
-      <c r="I64" s="5" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>Banking, Fintech, Payment Systems</t>
         </is>
       </c>
-      <c r="J64" s="5" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>Software Engineer, Banking Systems Architect, Fintech Developer</t>
         </is>
       </c>
-      <c r="K64" s="5" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>Banking Applications, Payment Systems</t>
         </is>
       </c>
-      <c r="L64" s="5" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>Computer Science, Finance, Software Engineering</t>
         </is>
       </c>
-      <c r="M64" s="5" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>Financial Software Development, Security, UX/UI Design</t>
         </is>
       </c>
-      <c r="N64" s="5" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O64" s="5" t="n"/>
-      <c r="P64" s="5" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>Banking-as-a-Service</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>SKI-000064</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Business &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>Finance, SaaS, Software Engineering</t>
         </is>
       </c>
-      <c r="E65" s="5" t="n"/>
-      <c r="F65" s="5" t="n"/>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Banking, Fintech, Technology</t>
         </is>
       </c>
-      <c r="H65" s="5" t="n"/>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>Fintech, Digital Banking</t>
         </is>
       </c>
-      <c r="J65" s="5" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>SaaS Architect, Fintech Developer, Business Development Manager</t>
         </is>
       </c>
-      <c r="K65" s="5" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>Digital Banking Platforms, Financial Services</t>
         </is>
       </c>
-      <c r="L65" s="5" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>Business Administration, Software Engineering, Finance</t>
         </is>
       </c>
-      <c r="M65" s="5" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>Cloud Solutions, API Development, Regulatory Compliance</t>
         </is>
       </c>
-      <c r="N65" s="5" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O65" s="5" t="n"/>
-      <c r="P65" s="5" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>Battery Management Systems</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>SKI-000065</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
         <is>
           <t>Engineering, Electronics, Software</t>
         </is>
       </c>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="n"/>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Automotive, Energy, Electronics</t>
         </is>
       </c>
-      <c r="H66" s="5" t="n"/>
-      <c r="I66" s="5" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>Electric Vehicles, Renewable Energy, Consumer Electronics</t>
         </is>
       </c>
-      <c r="J66" s="5" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>Battery Systems Engineer, Electrical Engineer, Energy Consultant</t>
         </is>
       </c>
-      <c r="K66" s="5" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>Electric Vehicle Batteries, Solar Power Systems</t>
         </is>
       </c>
-      <c r="L66" s="5" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>Electrical Engineering, Energy Systems, Computer Science</t>
         </is>
       </c>
-      <c r="M66" s="5" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>Battery Charging, Energy Storage, Power Management</t>
         </is>
       </c>
-      <c r="N66" s="5" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O66" s="5" t="n"/>
-      <c r="P66" s="5" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>Behavioral Analytics</t>
         </is>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>SKI-000066</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Analytical Skill</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Data Science, Marketing, Psychology</t>
         </is>
       </c>
-      <c r="E67" s="5" t="n"/>
-      <c r="F67" s="5" t="n"/>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Marketing, E-commerce, Technology</t>
         </is>
       </c>
-      <c r="H67" s="5" t="n"/>
-      <c r="I67" s="5" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>E-commerce, Marketing, Consumer Behavior Research</t>
         </is>
       </c>
-      <c r="J67" s="5" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>Data Scientist, Behavioral Analyst, Marketing Specialist</t>
         </is>
       </c>
-      <c r="K67" s="5" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>Customer Insights, Behavioral Data Models</t>
         </is>
       </c>
-      <c r="L67" s="5" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>Data Science, Psychology, Marketing</t>
         </is>
       </c>
-      <c r="M67" s="5" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>Pattern Recognition, Customer Segmentation, Predictive Modeling</t>
         </is>
       </c>
-      <c r="N67" s="5" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O67" s="5" t="n"/>
-      <c r="P67" s="5" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>SKI-000067</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Scientific &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>Bioinformatics, Computational Biology</t>
         </is>
       </c>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="n"/>
-      <c r="G68" s="5" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Healthcare, Biotechnology, Pharmaceuticals</t>
         </is>
       </c>
-      <c r="H68" s="5" t="n"/>
-      <c r="I68" s="5" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>Healthcare, Pharmaceuticals, Biotechnology</t>
         </is>
       </c>
-      <c r="J68" s="5" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>Bioinformatician, Computational Biologist, Research Scientist</t>
         </is>
       </c>
-      <c r="K68" s="5" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>Genomic Data Analysis, Healthcare Research</t>
         </is>
       </c>
-      <c r="L68" s="5" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>Biology, Computer Science, Data Science</t>
         </is>
       </c>
-      <c r="M68" s="5" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>Genomic Data Analysis, Statistical Methods, Molecular Biology</t>
         </is>
       </c>
-      <c r="N68" s="5" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O68" s="5" t="n"/>
-      <c r="P68" s="5" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>Bioinformatics Algorithms</t>
         </is>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>SKI-000068</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Analytical &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>Bioinformatics, Computational Biology</t>
         </is>
       </c>
-      <c r="E69" s="5" t="n"/>
-      <c r="F69" s="5" t="n"/>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Healthcare, Biotechnology, Pharmaceuticals</t>
         </is>
       </c>
-      <c r="H69" s="5" t="n"/>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>Healthcare, Pharmaceuticals, Biotechnology</t>
         </is>
       </c>
-      <c r="J69" s="5" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>Computational Biologist, Bioinformatics Researcher, Data Scientist</t>
         </is>
       </c>
-      <c r="K69" s="5" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>Genomic Research, Drug Discovery Tools</t>
         </is>
       </c>
-      <c r="L69" s="5" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>Computer Science, Biology, Mathematics</t>
         </is>
       </c>
-      <c r="M69" s="5" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>Algorithm Development, Machine Learning, Data Analysis</t>
         </is>
       </c>
-      <c r="N69" s="5" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O69" s="5" t="n"/>
-      <c r="P69" s="5" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Bioinformatics Databases</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>SKI-000069</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
         <is>
           <t>Bioinformatics, Data Management, Software</t>
         </is>
       </c>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="n"/>
-      <c r="G70" s="5" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Healthcare, Biotechnology, Pharmaceuticals</t>
         </is>
       </c>
-      <c r="H70" s="5" t="n"/>
-      <c r="I70" s="5" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>Healthcare, Pharmaceuticals, Research</t>
         </is>
       </c>
-      <c r="J70" s="5" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>Bioinformatics Database Administrator, Data Scientist, Researcher</t>
         </is>
       </c>
-      <c r="K70" s="5" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>Genomic Databases, Medical Data Repositories</t>
         </is>
       </c>
-      <c r="L70" s="5" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>Computer Science, Biology, Data Science</t>
         </is>
       </c>
-      <c r="M70" s="5" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>Database Design, Data Mining, Genomic Data Management</t>
         </is>
       </c>
-      <c r="N70" s="5" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O70" s="5" t="n"/>
-      <c r="P70" s="5" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>Bioinformatics Tools</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>SKI-000070</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
         <is>
           <t>Bioinformatics, Data Science, Software</t>
         </is>
       </c>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="n"/>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Healthcare, Biotechnology, Pharmaceuticals</t>
         </is>
       </c>
-      <c r="H71" s="5" t="n"/>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>Healthcare, Pharmaceuticals, Research</t>
         </is>
       </c>
-      <c r="J71" s="5" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>Bioinformatics Specialist, Data Scientist, Computational Biologist</t>
         </is>
       </c>
-      <c r="K71" s="5" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>Genomic Research, Medical Data Analysis</t>
         </is>
       </c>
-      <c r="L71" s="5" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>Computer Science, Biology, Data Science</t>
         </is>
       </c>
-      <c r="M71" s="5" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>Tool Development, Data Analysis, Genomic Data Processing</t>
         </is>
       </c>
-      <c r="N71" s="5" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O71" s="5" t="n"/>
-      <c r="P71" s="5" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>Biological Data Integration</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>SKI-000071</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
         <is>
           <t>Bioinformatics, Data Science</t>
         </is>
       </c>
-      <c r="E72" s="5" t="n"/>
-      <c r="F72" s="5" t="n"/>
-      <c r="G72" s="5" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Healthcare, Biotechnology, Pharmaceuticals</t>
         </is>
       </c>
-      <c r="H72" s="5" t="n"/>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>Healthcare, Biotechnology, Research</t>
         </is>
       </c>
-      <c r="J72" s="5" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>Data Integration Specialist, Bioinformatics Analyst, Researcher</t>
         </is>
       </c>
-      <c r="K72" s="5" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>Genomic Data Integration, Medical Records</t>
         </is>
       </c>
-      <c r="L72" s="5" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>Computer Science, Biology, Data Science</t>
         </is>
       </c>
-      <c r="M72" s="5" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>Data Merging, Multi-Source Integration, Biological Data Analysis</t>
         </is>
       </c>
-      <c r="N72" s="5" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O72" s="5" t="n"/>
-      <c r="P72" s="5" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>Biological Database Management</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>SKI-000072</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
         <is>
           <t>Bioinformatics, Data Management</t>
         </is>
       </c>
-      <c r="E73" s="5" t="n"/>
-      <c r="F73" s="5" t="n"/>
-      <c r="G73" s="5" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Healthcare, Research, Biotechnology</t>
         </is>
       </c>
-      <c r="H73" s="5" t="n"/>
-      <c r="I73" s="5" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>Healthcare, Research, Biotechnology</t>
         </is>
       </c>
-      <c r="J73" s="5" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>Database Administrator, Bioinformatics Data Manager, Research Scientist</t>
         </is>
       </c>
-      <c r="K73" s="5" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>Medical Data Repositories, Genomic Databases</t>
         </is>
       </c>
-      <c r="L73" s="5" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>Computer Science, Biology, Data Management</t>
         </is>
       </c>
-      <c r="M73" s="5" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>Database Design, Data Storage, Genomic Data Management</t>
         </is>
       </c>
-      <c r="N73" s="5" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O73" s="5" t="n"/>
-      <c r="P73" s="5" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>Biological Databases</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>SKI-000073</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
         <is>
           <t>Bioinformatics, Data Management, Software</t>
         </is>
       </c>
-      <c r="E74" s="5" t="n"/>
-      <c r="F74" s="5" t="n"/>
-      <c r="G74" s="5" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Healthcare, Biotechnology, Pharmaceuticals</t>
         </is>
       </c>
-      <c r="H74" s="5" t="n"/>
-      <c r="I74" s="5" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>Healthcare, Pharmaceuticals, Research</t>
         </is>
       </c>
-      <c r="J74" s="5" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>Bioinformatics Specialist, Database Administrator, Researcher</t>
         </is>
       </c>
-      <c r="K74" s="5" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>Genomic Databases, Medical Data Repositories</t>
         </is>
       </c>
-      <c r="L74" s="5" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>Computer Science, Biology, Data Science</t>
         </is>
       </c>
-      <c r="M74" s="5" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>Data Organization, Data Mining, Bioinformatics Analysis</t>
         </is>
       </c>
-      <c r="N74" s="5" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O74" s="5" t="n"/>
-      <c r="P74" s="5" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>Biological Networks</t>
         </is>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>SKI-000074</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Analytical &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>Bioinformatics, Network Analysis</t>
         </is>
       </c>
-      <c r="E75" s="5" t="n"/>
-      <c r="F75" s="5" t="n"/>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Healthcare, Research, Pharmaceuticals</t>
         </is>
       </c>
-      <c r="H75" s="5" t="n"/>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>Healthcare, Research, Pharmaceuticals</t>
         </is>
       </c>
-      <c r="J75" s="5" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>Bioinformatics Network Analyst, Systems Biologist, Researcher</t>
         </is>
       </c>
-      <c r="K75" s="5" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>Protein Interaction Networks, Biological Models</t>
         </is>
       </c>
-      <c r="L75" s="5" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>Biology, Computer Science, Data Science</t>
         </is>
       </c>
-      <c r="M75" s="5" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>Network Analysis, Systems Biology, Data Modeling</t>
         </is>
       </c>
-      <c r="N75" s="5" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O75" s="5" t="n"/>
-      <c r="P75" s="5" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>Blockchain</t>
         </is>
       </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>SKI-000075</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
         <is>
           <t>Cryptography, Distributed Systems</t>
         </is>
       </c>
-      <c r="E76" s="5" t="n"/>
-      <c r="F76" s="5" t="n"/>
-      <c r="G76" s="5" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Technology, Finance, Supply Chain</t>
         </is>
       </c>
-      <c r="H76" s="5" t="n"/>
-      <c r="I76" s="5" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>Finance, Technology, Supply Chain</t>
         </is>
       </c>
-      <c r="J76" s="5" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>Blockchain Developer, Cryptography Engineer, Software Engineer</t>
         </is>
       </c>
-      <c r="K76" s="5" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>Cryptocurrencies, Distributed Ledgers</t>
         </is>
       </c>
-      <c r="L76" s="5" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>Computer Science, Cryptography, Mathematics</t>
         </is>
       </c>
-      <c r="M76" s="5" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>Blockchain Development, Smart Contracts, Security Protocols</t>
         </is>
       </c>
-      <c r="N76" s="5" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O76" s="5" t="n"/>
-      <c r="P76" s="5" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>Blockchain for Compliance</t>
         </is>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>SKI-000076</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
         <is>
           <t>Blockchain, Regulatory Technology</t>
         </is>
       </c>
-      <c r="E77" s="5" t="n"/>
-      <c r="F77" s="5" t="n"/>
-      <c r="G77" s="5" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Finance, Technology, Legal, Compliance</t>
         </is>
       </c>
-      <c r="H77" s="5" t="n"/>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>Finance, Compliance, Legal, Technology</t>
         </is>
       </c>
-      <c r="J77" s="5" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>Compliance Engineer, Blockchain Consultant, Regulatory Analyst</t>
         </is>
       </c>
-      <c r="K77" s="5" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>Regulatory Compliance, Smart Contracts</t>
         </is>
       </c>
-      <c r="L77" s="5" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>Computer Science, Law, Business Administration</t>
         </is>
       </c>
-      <c r="M77" s="5" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>Regulatory Frameworks, Smart Contract Development, Auditing</t>
         </is>
       </c>
-      <c r="N77" s="5" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O77" s="5" t="n"/>
-      <c r="P77" s="5" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>Blockchain for Fraud Detection</t>
         </is>
       </c>
-      <c r="B78" s="5" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>SKI-000077</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
         <is>
           <t>Blockchain, Security, Fraud Prevention</t>
         </is>
       </c>
-      <c r="E78" s="5" t="n"/>
-      <c r="F78" s="5" t="n"/>
-      <c r="G78" s="5" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Finance, Cybersecurity, Technology</t>
         </is>
       </c>
-      <c r="H78" s="5" t="n"/>
-      <c r="I78" s="5" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>Finance, Cybersecurity, Banking</t>
         </is>
       </c>
-      <c r="J78" s="5" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>Blockchain Developer, Fraud Analyst, Security Specialist</t>
         </is>
       </c>
-      <c r="K78" s="5" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>Fraud Prevention, Transaction Monitoring</t>
         </is>
       </c>
-      <c r="L78" s="5" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>Computer Science, Cybersecurity, Finance</t>
         </is>
       </c>
-      <c r="M78" s="5" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>Transaction Analysis, Fraud Prevention, Blockchain Security</t>
         </is>
       </c>
-      <c r="N78" s="5" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O78" s="5" t="n"/>
-      <c r="P78" s="5" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>Blockchain Integration</t>
         </is>
       </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>SKI-000078</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
         <is>
           <t>Blockchain, Software Engineering</t>
         </is>
       </c>
-      <c r="E79" s="5" t="n"/>
-      <c r="F79" s="5" t="n"/>
-      <c r="G79" s="5" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Technology, Finance, Supply Chain</t>
         </is>
       </c>
-      <c r="H79" s="5" t="n"/>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>Finance, Technology, Supply Chain</t>
         </is>
       </c>
-      <c r="J79" s="5" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>Blockchain Integration Specialist, Software Engineer</t>
         </is>
       </c>
-      <c r="K79" s="5" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>Blockchain Solutions, Legacy System Integration</t>
         </is>
       </c>
-      <c r="L79" s="5" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>Computer Science, Engineering, Business Administration</t>
         </is>
       </c>
-      <c r="M79" s="5" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>System Integration, Blockchain APIs, Software Development</t>
         </is>
       </c>
-      <c r="N79" s="5" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O79" s="5" t="n"/>
-      <c r="P79" s="5" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>Blockchain Platforms</t>
         </is>
       </c>
-      <c r="B80" s="5" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>SKI-000079</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
         <is>
           <t>Blockchain, Software Engineering</t>
         </is>
       </c>
-      <c r="E80" s="5" t="n"/>
-      <c r="F80" s="5" t="n"/>
-      <c r="G80" s="5" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Technology, Finance, Decentralized Apps</t>
         </is>
       </c>
-      <c r="H80" s="5" t="n"/>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>Finance, Technology, Decentralized Applications</t>
         </is>
       </c>
-      <c r="J80" s="5" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>Blockchain Developer, Platform Engineer, Technical Architect</t>
         </is>
       </c>
-      <c r="K80" s="5" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>Blockchain Networks, Decentralized Apps</t>
         </is>
       </c>
-      <c r="L80" s="5" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>Computer Science, Engineering, Mathematics</t>
         </is>
       </c>
-      <c r="M80" s="5" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>Blockchain Development, Network Design, Platform Architecture</t>
         </is>
       </c>
-      <c r="N80" s="5" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O80" s="5" t="n"/>
-      <c r="P80" s="5" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>Blockchain Scaling</t>
         </is>
       </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>SKI-000080</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
         <is>
           <t>Blockchain, Distributed Systems</t>
         </is>
       </c>
-      <c r="E81" s="5" t="n"/>
-      <c r="F81" s="5" t="n"/>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Technology, Finance, Cryptocurrency</t>
         </is>
       </c>
-      <c r="H81" s="5" t="n"/>
-      <c r="I81" s="5" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>Finance, Technology, Cryptocurrency</t>
         </is>
       </c>
-      <c r="J81" s="5" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>Blockchain Engineer, Distributed Systems Architect, Solutions Architect</t>
         </is>
       </c>
-      <c r="K81" s="5" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>Blockchain Networks, Cryptocurrencies</t>
         </is>
       </c>
-      <c r="L81" s="5" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>Computer Science, Cryptography, Mathematics</t>
         </is>
       </c>
-      <c r="M81" s="5" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>Network Optimization, Consensus Algorithms, Scaling Solutions</t>
         </is>
       </c>
-      <c r="N81" s="5" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O81" s="5" t="n"/>
-      <c r="P81" s="5" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>Blockchain Security</t>
         </is>
       </c>
-      <c r="B82" s="5" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>SKI-000081</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
         <is>
           <t>Cybersecurity, Blockchain</t>
         </is>
       </c>
-      <c r="E82" s="5" t="n"/>
-      <c r="F82" s="5" t="n"/>
-      <c r="G82" s="5" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Technology, Finance, Cybersecurity</t>
         </is>
       </c>
-      <c r="H82" s="5" t="n"/>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>Finance, Technology, Cryptocurrency</t>
         </is>
       </c>
-      <c r="J82" s="5" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>Blockchain Security Engineer, Security Analyst, Cryptography Expert</t>
         </is>
       </c>
-      <c r="K82" s="5" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>Secure Transactions, Smart Contracts</t>
         </is>
       </c>
-      <c r="L82" s="5" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>Computer Science, Cryptography, Cybersecurity</t>
         </is>
       </c>
-      <c r="M82" s="5" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>Encryption, Threat Detection, Security Auditing, Penetration Testing</t>
         </is>
       </c>
-      <c r="N82" s="5" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O82" s="5" t="n"/>
-      <c r="P82" s="5" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="A83" t="inlineStr">
         <is>
           <t>Board-Level Debugging</t>
         </is>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>SKI-000082</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
         <is>
           <t>Electronics, Embedded Systems, Debugging</t>
         </is>
       </c>
-      <c r="E83" s="5" t="n"/>
-      <c r="F83" s="5" t="n"/>
-      <c r="G83" s="5" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>Electronics, Telecommunications, Technology</t>
         </is>
       </c>
-      <c r="H83" s="5" t="n"/>
-      <c r="I83" s="5" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>Electronics Manufacturing, Hardware Development</t>
         </is>
       </c>
-      <c r="J83" s="5" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>Hardware Engineer, Embedded Systems Engineer, Debugging Specialist</t>
         </is>
       </c>
-      <c r="K83" s="5" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>Circuit Debugging, Microcontrollers</t>
         </is>
       </c>
-      <c r="L83" s="5" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>Electrical Engineering, Computer Science</t>
         </is>
       </c>
-      <c r="M83" s="5" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>Signal Testing, Circuit Troubleshooting, Debugging Techniques</t>
         </is>
       </c>
-      <c r="N83" s="5" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O83" s="5" t="n"/>
-      <c r="P83" s="5" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>Board-Level Design</t>
         </is>
       </c>
-      <c r="B84" s="5" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>SKI-000083</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
         <is>
           <t>Electronics, Hardware Engineering</t>
         </is>
       </c>
-      <c r="E84" s="5" t="n"/>
-      <c r="F84" s="5" t="n"/>
-      <c r="G84" s="5" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>Electronics, Automotive, Telecommunications</t>
         </is>
       </c>
-      <c r="H84" s="5" t="n"/>
-      <c r="I84" s="5" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>Consumer Electronics, Telecommunications, Automotive</t>
         </is>
       </c>
-      <c r="J84" s="5" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>Hardware Engineer, PCB Designer, Electronics Designer</t>
         </is>
       </c>
-      <c r="K84" s="5" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>PCB Design, Embedded Systems</t>
         </is>
       </c>
-      <c r="L84" s="5" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>Electrical Engineering, Computer Engineering</t>
         </is>
       </c>
-      <c r="M84" s="5" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>Schematic Design, Signal Integrity, PCB Layout</t>
         </is>
       </c>
-      <c r="N84" s="5" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O84" s="5" t="n"/>
-      <c r="P84" s="5" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>Bonding Technology</t>
         </is>
       </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>SKI-000084</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
         <is>
           <t>Materials Science, Electronics</t>
         </is>
       </c>
-      <c r="E85" s="5" t="n"/>
-      <c r="F85" s="5" t="n"/>
-      <c r="G85" s="5" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>Electronics, Manufacturing</t>
         </is>
       </c>
-      <c r="H85" s="5" t="n"/>
-      <c r="I85" s="5" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>Semiconductor Manufacturing, Electronics Assembly</t>
         </is>
       </c>
-      <c r="J85" s="5" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>Process Engineer, Materials Scientist, Electronics Engineer</t>
         </is>
       </c>
-      <c r="K85" s="5" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>Semiconductor Devices, Microelectronics</t>
         </is>
       </c>
-      <c r="L85" s="5" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>Materials Science, Electrical Engineering</t>
         </is>
       </c>
-      <c r="M85" s="5" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>Bonding Techniques, Adhesive Application, Surface Interaction</t>
         </is>
       </c>
-      <c r="N85" s="5" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O85" s="5" t="n"/>
-      <c r="P85" s="5" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>Bootloaders</t>
         </is>
       </c>
-      <c r="B86" s="5" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>SKI-000085</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
         <is>
           <t>Embedded Systems, Software Engineering</t>
         </is>
       </c>
-      <c r="E86" s="5" t="n"/>
-      <c r="F86" s="5" t="n"/>
-      <c r="G86" s="5" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>Electronics, Automotive, Software Development</t>
         </is>
       </c>
-      <c r="H86" s="5" t="n"/>
-      <c r="I86" s="5" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>Firmware Development, Electronics, Automotive</t>
         </is>
       </c>
-      <c r="J86" s="5" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>Firmware Engineer, Embedded Systems Developer, Bootloader Engineer</t>
         </is>
       </c>
-      <c r="K86" s="5" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t>Bootloading Software, Embedded Systems</t>
         </is>
       </c>
-      <c r="L86" s="5" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>Computer Science, Electrical Engineering</t>
         </is>
       </c>
-      <c r="M86" s="5" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>Firmware Programming, System Initialization, Low-Level Debugging</t>
         </is>
       </c>
-      <c r="N86" s="5" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O86" s="5" t="n"/>
-      <c r="P86" s="5" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="inlineStr">
+      <c r="A87" t="inlineStr">
         <is>
           <t>Brain Networks</t>
         </is>
       </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>SKI-000086</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Scientific &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>Neuroscience, Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E87" s="5" t="n"/>
-      <c r="F87" s="5" t="n"/>
-      <c r="G87" s="5" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>Healthcare, AI, Research</t>
         </is>
       </c>
-      <c r="H87" s="5" t="n"/>
-      <c r="I87" s="5" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>Healthcare, AI Research, Cognitive Science</t>
         </is>
       </c>
-      <c r="J87" s="5" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>Neuroscientist, AI Researcher, Cognitive Systems Engineer</t>
         </is>
       </c>
-      <c r="K87" s="5" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>Neural Networks, Brain Simulation</t>
         </is>
       </c>
-      <c r="L87" s="5" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>Neuroscience, AI, Computer Science</t>
         </is>
       </c>
-      <c r="M87" s="5" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>Neural Connectivity, Computational Neuroscience, Brain Mapping</t>
         </is>
       </c>
-      <c r="N87" s="5" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>2-3 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O87" s="5" t="n"/>
-      <c r="P87" s="5" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="A88" t="inlineStr">
         <is>
           <t>Brain Simulation</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>SKI-000087</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Scientific &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>Neuroscience, AI, Simulation</t>
         </is>
       </c>
-      <c r="E88" s="5" t="n"/>
-      <c r="F88" s="5" t="n"/>
-      <c r="G88" s="5" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>Healthcare, Research, AI</t>
         </is>
       </c>
-      <c r="H88" s="5" t="n"/>
-      <c r="I88" s="5" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>Healthcare, Cognitive Science, AI Research</t>
         </is>
       </c>
-      <c r="J88" s="5" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>Neuroscientist, Simulation Scientist, Computational Neuroscientist</t>
         </is>
       </c>
-      <c r="K88" s="5" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t>Brain Models, Cognitive Simulations</t>
         </is>
       </c>
-      <c r="L88" s="5" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>Neuroscience, AI, Computer Science</t>
         </is>
       </c>
-      <c r="M88" s="5" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>Neural Simulation, Cognitive Modeling, Brain Network Analysis</t>
         </is>
       </c>
-      <c r="N88" s="5" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>2-3 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O88" s="5" t="n"/>
-      <c r="P88" s="5" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="A89" t="inlineStr">
         <is>
           <t>Brand Building</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>SKI-000088</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Business &amp; Marketing Skill</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>Marketing, Branding</t>
         </is>
       </c>
-      <c r="E89" s="5" t="n"/>
-      <c r="F89" s="5" t="n"/>
-      <c r="G89" s="5" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>Retail, Consumer Goods, Marketing</t>
         </is>
       </c>
-      <c r="H89" s="5" t="n"/>
-      <c r="I89" s="5" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>Consumer Goods, Digital Marketing, Retail</t>
         </is>
       </c>
-      <c r="J89" s="5" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>Brand Manager, Marketing Director, Digital Marketing Specialist</t>
         </is>
       </c>
-      <c r="K89" s="5" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>Brand Strategy, Marketing Campaigns</t>
         </is>
       </c>
-      <c r="L89" s="5" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>Marketing, Business Administration, Communications</t>
         </is>
       </c>
-      <c r="M89" s="5" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>Market Research, Content Creation, Audience Engagement</t>
         </is>
       </c>
-      <c r="N89" s="5" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O89" s="5" t="n"/>
-      <c r="P89" s="5" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
+      <c r="A90" t="inlineStr">
         <is>
           <t>Brand Development</t>
         </is>
       </c>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>SKI-000089</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Business &amp; Marketing Skill</t>
         </is>
       </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>Marketing, Branding, Strategy</t>
         </is>
       </c>
-      <c r="E90" s="5" t="n"/>
-      <c r="F90" s="5" t="n"/>
-      <c r="G90" s="5" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>Retail, Advertising, Consumer Goods</t>
         </is>
       </c>
-      <c r="H90" s="5" t="n"/>
-      <c r="I90" s="5" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>Advertising, Retail, Consumer Goods</t>
         </is>
       </c>
-      <c r="J90" s="5" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>Brand Strategist, Marketing Manager, Product Manager</t>
         </is>
       </c>
-      <c r="K90" s="5" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>Brand Positioning, Product Identity</t>
         </is>
       </c>
-      <c r="L90" s="5" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>Marketing, Business Administration, Communications</t>
         </is>
       </c>
-      <c r="M90" s="5" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>Brand Strategy, Customer Insights, Competitive Analysis</t>
         </is>
       </c>
-      <c r="N90" s="5" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O90" s="5" t="n"/>
-      <c r="P90" s="5" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="inlineStr">
+      <c r="A91" t="inlineStr">
         <is>
           <t>Burn-In Testing</t>
         </is>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>SKI-000090</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
         <is>
           <t>Quality Assurance, Testing</t>
         </is>
       </c>
-      <c r="E91" s="5" t="n"/>
-      <c r="F91" s="5" t="n"/>
-      <c r="G91" s="5" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>Electronics, Automotive, Manufacturing</t>
         </is>
       </c>
-      <c r="H91" s="5" t="n"/>
-      <c r="I91" s="5" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>Electronics, Manufacturing, Automotive</t>
         </is>
       </c>
-      <c r="J91" s="5" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>Test Engineer, QA Engineer, Manufacturing Specialist</t>
         </is>
       </c>
-      <c r="K91" s="5" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>Product Testing, Reliability Evaluation</t>
         </is>
       </c>
-      <c r="L91" s="5" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>Electrical Engineering, Mechanical Engineering</t>
         </is>
       </c>
-      <c r="M91" s="5" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>Stress Testing, System Testing, Failure Prediction</t>
         </is>
       </c>
-      <c r="N91" s="5" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O91" s="5" t="n"/>
-      <c r="P91" s="5" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
+      <c r="A92" t="inlineStr">
         <is>
           <t>Bus Architectures</t>
         </is>
       </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>SKI-000091</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
         <is>
           <t>Computer Architecture, Hardware Design</t>
         </is>
       </c>
-      <c r="E92" s="5" t="n"/>
-      <c r="F92" s="5" t="n"/>
-      <c r="G92" s="5" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>Electronics, Technology, Embedded Systems</t>
         </is>
       </c>
-      <c r="H92" s="5" t="n"/>
-      <c r="I92" s="5" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>Electronics, Computer Science, Embedded Systems</t>
         </is>
       </c>
-      <c r="J92" s="5" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>Systems Architect, Hardware Engineer, Embedded Systems Designer</t>
         </is>
       </c>
-      <c r="K92" s="5" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>Computer Systems, Microprocessor Design</t>
         </is>
       </c>
-      <c r="L92" s="5" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>Computer Engineering, Electrical Engineering</t>
         </is>
       </c>
-      <c r="M92" s="5" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>Data Transfer Optimization, Hardware Design, System Architecture</t>
         </is>
       </c>
-      <c r="N92" s="5" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O92" s="5" t="n"/>
-      <c r="P92" s="5" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
+      <c r="A93" t="inlineStr">
         <is>
           <t>Business Continuity Planning</t>
         </is>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>SKI-000092</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Business &amp; Organizational Skill</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>Risk Management, Business Strategy</t>
         </is>
       </c>
-      <c r="E93" s="5" t="n"/>
-      <c r="F93" s="5" t="n"/>
-      <c r="G93" s="5" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>IT, Healthcare, Government, Corporate</t>
         </is>
       </c>
-      <c r="H93" s="5" t="n"/>
-      <c r="I93" s="5" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>IT, Healthcare, Corporate, Government</t>
         </is>
       </c>
-      <c r="J93" s="5" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>Business Continuity Planner, Risk Manager, Operations Manager</t>
         </is>
       </c>
-      <c r="K93" s="5" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>Continuity Plans, Disaster Recovery</t>
         </is>
       </c>
-      <c r="L93" s="5" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>Business Administration, Risk Management, IT Management</t>
         </is>
       </c>
-      <c r="M93" s="5" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>Crisis Management, Risk Analysis, Strategic Planning</t>
         </is>
       </c>
-      <c r="N93" s="5" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O93" s="5" t="n"/>
-      <c r="P93" s="5" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>C Programming</t>
         </is>
       </c>
-      <c r="B94" s="5" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>SKI-000093</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
         <is>
           <t>Software Development, Programming</t>
         </is>
       </c>
-      <c r="E94" s="5" t="n"/>
-      <c r="F94" s="5" t="n"/>
-      <c r="G94" s="5" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>Technology, Electronics, Software Development</t>
         </is>
       </c>
-      <c r="H94" s="5" t="n"/>
-      <c r="I94" s="5" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>Software Development, Embedded Systems</t>
         </is>
       </c>
-      <c r="J94" s="5" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>Software Developer, Embedded Systems Engineer, Programmer</t>
         </is>
       </c>
-      <c r="K94" s="5" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t>Applications, Firmware, Systems Software</t>
         </is>
       </c>
-      <c r="L94" s="5" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering</t>
         </is>
       </c>
-      <c r="M94" s="5" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>Algorithm Development, Memory Management, System-Level Programming</t>
         </is>
       </c>
-      <c r="N94" s="5" t="inlineStr">
+      <c r="N94" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O94" s="5" t="n"/>
-      <c r="P94" s="5" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr">
+      <c r="A95" t="inlineStr">
         <is>
           <t>C/C++ Programming</t>
         </is>
       </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>SKI-000094</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
         <is>
           <t>Software Development, Programming</t>
         </is>
       </c>
-      <c r="E95" s="5" t="n"/>
-      <c r="F95" s="5" t="n"/>
-      <c r="G95" s="5" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>Technology, Gaming, Electronics, Software</t>
         </is>
       </c>
-      <c r="H95" s="5" t="n"/>
-      <c r="I95" s="5" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>Software Development, Embedded Systems, Game Development</t>
         </is>
       </c>
-      <c r="J95" s="5" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>Software Developer, Game Developer, Systems Programmer</t>
         </is>
       </c>
-      <c r="K95" s="5" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t>Applications, Game Engines, Systems Software</t>
         </is>
       </c>
-      <c r="L95" s="5" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering</t>
         </is>
       </c>
-      <c r="M95" s="5" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t>Memory Management, Object-Oriented Programming, Multi-threading</t>
         </is>
       </c>
-      <c r="N95" s="5" t="inlineStr">
+      <c r="N95" t="inlineStr">
         <is>
           <t>1 year (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O95" s="5" t="n"/>
-      <c r="P95" s="5" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="inlineStr">
+      <c r="A96" t="inlineStr">
         <is>
           <t>C/C++/Fortran Programming</t>
         </is>
       </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>SKI-000095</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
         <is>
           <t>Software Development, Programming</t>
         </is>
       </c>
-      <c r="E96" s="5" t="n"/>
-      <c r="F96" s="5" t="n"/>
-      <c r="G96" s="5" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>Technology, Science, Research</t>
         </is>
       </c>
-      <c r="H96" s="5" t="n"/>
-      <c r="I96" s="5" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>High-Performance Computing, Embedded Systems</t>
         </is>
       </c>
-      <c r="J96" s="5" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>HPC Developer, Embedded Systems Engineer, Programmer</t>
         </is>
       </c>
-      <c r="K96" s="5" t="inlineStr">
+      <c r="K96" t="inlineStr">
         <is>
           <t>Simulation Software, Scientific Applications</t>
         </is>
       </c>
-      <c r="L96" s="5" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t>Computer Science, Engineering, Computational Science</t>
         </is>
       </c>
-      <c r="M96" s="5" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t>Numerical Methods, Performance Optimization, Parallel Programming</t>
         </is>
       </c>
-      <c r="N96" s="5" t="inlineStr">
+      <c r="N96" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O96" s="5" t="n"/>
-      <c r="P96" s="5" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>C/C++/Python Programming</t>
         </is>
       </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>SKI-000096</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
         <is>
           <t>Software Development, Programming</t>
         </is>
       </c>
-      <c r="E97" s="5" t="n"/>
-      <c r="F97" s="5" t="n"/>
-      <c r="G97" s="5" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>Technology, Data Science, Gaming, Software</t>
         </is>
       </c>
-      <c r="H97" s="5" t="n"/>
-      <c r="I97" s="5" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>Software Development, Data Science, Game Development</t>
         </is>
       </c>
-      <c r="J97" s="5" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>Software Developer, Data Scientist, Game Programmer</t>
         </is>
       </c>
-      <c r="K97" s="5" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t>Applications, Data Analysis, Game Development</t>
         </is>
       </c>
-      <c r="L97" s="5" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering, Data Science</t>
         </is>
       </c>
-      <c r="M97" s="5" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t>Object-Oriented Programming, Algorithm Design, Data Structures</t>
         </is>
       </c>
-      <c r="N97" s="5" t="inlineStr">
+      <c r="N97" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O97" s="5" t="n"/>
-      <c r="P97" s="5" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="inlineStr">
+      <c r="A98" t="inlineStr">
         <is>
           <t>C++/Java Programming</t>
         </is>
       </c>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>SKI-000097</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
         <is>
           <t>Software Development, Programming</t>
         </is>
       </c>
-      <c r="E98" s="5" t="n"/>
-      <c r="F98" s="5" t="n"/>
-      <c r="G98" s="5" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>Technology, Software, Mobile Development</t>
         </is>
       </c>
-      <c r="H98" s="5" t="n"/>
-      <c r="I98" s="5" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>Software Development, Web Development, Mobile Apps</t>
         </is>
       </c>
-      <c r="J98" s="5" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>Software Developer, Mobile App Developer, Web Developer</t>
         </is>
       </c>
-      <c r="K98" s="5" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t>Applications, Web Apps, Mobile Apps</t>
         </is>
       </c>
-      <c r="L98" s="5" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering</t>
         </is>
       </c>
-      <c r="M98" s="5" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t>Object-Oriented Programming, Cross-platform Development, Web Development</t>
         </is>
       </c>
-      <c r="N98" s="5" t="inlineStr">
+      <c r="N98" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
-      <c r="O98" s="5" t="n"/>
-      <c r="P98" s="5" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr">
+      <c r="A99" t="inlineStr">
         <is>
           <t>C++/Java/Python Programming</t>
         </is>
       </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>SKI-000098</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
         <is>
           <t>Software Development, Programming</t>
         </is>
       </c>
-      <c r="E99" s="5" t="n"/>
-      <c r="F99" s="5" t="n"/>
-      <c r="G99" s="5" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>Technology, Data Science, Software Development</t>
         </is>
       </c>
-      <c r="H99" s="5" t="n"/>
-      <c r="I99" s="5" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>Software Development, Data Science, Web Development</t>
         </is>
       </c>
-      <c r="J99" s="5" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>Software Developer, Data Scientist, Web Developer</t>
         </is>
       </c>
-      <c r="K99" s="5" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t>Applications, Data Analysis, Web Development</t>
         </is>
       </c>
-      <c r="L99" s="5" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering, Data Science</t>
         </is>
       </c>
-      <c r="M99" s="5" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t>Object-Oriented Programming, Full-stack Development, Data Structures</t>
         </is>
       </c>
-      <c r="N99" s="5" t="inlineStr">
+      <c r="N99" t="inlineStr">
         <is>
           <t>2-3 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O99" s="5" t="n"/>
-      <c r="P99" s="5" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="inlineStr">
+      <c r="A100" t="inlineStr">
         <is>
           <t>C++/Python Programming</t>
         </is>
       </c>
-      <c r="B100" s="5" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>SKI-000099</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
         <is>
           <t>Software Development, Programming</t>
         </is>
       </c>
-      <c r="E100" s="5" t="n"/>
-      <c r="F100" s="5" t="n"/>
-      <c r="G100" s="5" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>Technology, Software, Data Science</t>
         </is>
       </c>
-      <c r="H100" s="5" t="n"/>
-      <c r="I100" s="5" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>Software Development, Data Science, Embedded Systems</t>
         </is>
       </c>
-      <c r="J100" s="5" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>Software Developer, Data Scientist, Embedded Systems Engineer</t>
         </is>
       </c>
-      <c r="K100" s="5" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t>Applications, Machine Learning, Embedded Systems</t>
         </is>
       </c>
-      <c r="L100" s="5" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering, Data Science</t>
         </is>
       </c>
-      <c r="M100" s="5" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>Data Structures, Algorithm Optimization, Embedded Programming</t>
         </is>
       </c>
-      <c r="N100" s="5" t="inlineStr">
+      <c r="N100" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
-      <c r="O100" s="5" t="n"/>
-      <c r="P100" s="5" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="inlineStr">
+      <c r="A101" t="inlineStr">
         <is>
           <t>C++/Python/Java Programming</t>
         </is>
       </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>SKI-000100</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
         <is>
           <t>Software Development, Programming</t>
         </is>
       </c>
-      <c r="E101" s="5" t="n"/>
-      <c r="F101" s="5" t="n"/>
-      <c r="G101" s="5" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>Technology, Software, Data Science</t>
         </is>
       </c>
-      <c r="H101" s="5" t="n"/>
-      <c r="I101" s="5" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t>Software Development, Data Science, AI</t>
         </is>
       </c>
-      <c r="J101" s="5" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>Software Developer, Data Scientist, AI Engineer</t>
         </is>
       </c>
-      <c r="K101" s="5" t="inlineStr">
+      <c r="K101" t="inlineStr">
         <is>
           <t>Applications, Data Analysis, AI Development</t>
         </is>
       </c>
-      <c r="L101" s="5" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering, Data Science</t>
         </is>
       </c>
-      <c r="M101" s="5" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t>Object-Oriented Programming, Full-stack Development, Machine Learning</t>
         </is>
       </c>
-      <c r="N101" s="5" t="inlineStr">
+      <c r="N101" t="inlineStr">
         <is>
           <t>2-3 years (advanced expertise)</t>
         </is>
       </c>
-      <c r="O101" s="5" t="n"/>
-      <c r="P101" s="5" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>

--- a/apps/api/data/excel_templates/skills.xlsx
+++ b/apps/api/data/excel_templates/skills.xlsx
@@ -57,7 +57,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -67,6 +67,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -536,5704 +539,6204 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Blockchain Development</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>SKI-000001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Blockchain, Software Engineering, Security</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Technology, Finance, Gaming, Security</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>FinTech, Software Development, Supply Chain, Gaming</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Blockchain Developer, Software Engineer, Smart Contract Developer</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>Cryptocurrencies, Decentralized Applications, Smart Contracts</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Engineering, Cryptography</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>Cryptography, Distributed Systems, Smart Contracts, Security</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 2-3 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O2" s="5" t="n"/>
+      <c r="P2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>2D &amp; 3D Modeling</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>SKI-000002</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Creative &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Design, Computer Graphics, Animation</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Entertainment, Gaming, Architecture, VR/AR</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Game Design, Film Production, Architecture, VR/AR</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>3D Modeler, Character Artist, Industrial Designer</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Video Games, Films, Virtual Environments</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Digital Arts, Fine Arts, Game Design</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Creativity, Texturing, Lighting, Attention to Detail, Software Proficiency (e.g., Blender, Maya, ZBrush)</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>3D Computational Geometry</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>SKI-000003</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Geometry, Computer Science, Visualization</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Engineering, Robotics, Gaming, Simulation</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Robotics, Engineering, Game Design, Simulation</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Computational Geometer, Robotics Engineer, Simulation Developer</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>Robotics, Engineering Software, Games</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>Mathematics, Computer Science, Engineering</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>Geometry Algorithms, Spatial Data Structures, Programming (e.g., C++, Python)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>3D IC Design</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>SKI-000004</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Electronics, Circuit Design, Engineering</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Technology, Manufacturing</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Semiconductor Industry, Electronics Manufacturing</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>IC Design Engineer, Circuit Designer, Electronics Engineer</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>Semiconductors, Consumer Electronics</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>Electrical Engineering, Computer Engineering</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>Circuit Design, CAD Tools, Signal Processing, Physical Design</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>3D Image Reconstruction</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>SKI-000005</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Computer Vision, Imaging, Medical Imaging</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Research, Gaming, Technology</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Medical Imaging, Computer Vision, Virtual Reality</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Imaging Specialist, Data Scientist, Research Scientist</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Medical Scans, 3D Models, Virtual Reality</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Biomedical Engineering, Mathematics</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>Image Processing, Algorithms, Software Proficiency (e.g., MATLAB, OpenCV)</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>3D Molecular Visualization</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>SKI-000006</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Molecular Biology, Visualization, Computing</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Biotech, Pharmaceuticals</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Biotechnology, Healthcare, Pharmaceuticals</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Bioinformatics Specialist, Research Scientist, Computational Biologist</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Drug Development, Molecular Modeling</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Biochemistry, Bioinformatics, Computer Science</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Molecular Modeling, Visualization Tools (e.g., PyMOL, Chimera)</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>3D Packaging</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>SKI-000007</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Engineering, Design, Manufacturing</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Manufacturing, Electronics, Packaging</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Electronics, Consumer Goods, Packaging Industry</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Packaging Engineer, Industrial Designer, Product Designer</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>Product Packaging, Electronics, Consumer Goods</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>Engineering, Industrial Design, Materials Science</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" s="5" t="inlineStr">
         <is>
           <t>3D Printing, CAD Tools, Structural Design, Materials Selection</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Accelerated Life Testing</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>SKI-000008</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Testing, Reliability Engineering</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Manufacturing, Aerospace, Electronics</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Manufacturing, Electronics, Aerospace</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Reliability Engineer, Test Engineer, QA Engineer</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>Product Testing, Quality Assurance</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>Mechanical Engineering, Electrical Engineering</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>Failure Analysis, Statistical Modeling, Stress Testing</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Accelerometer Design</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>SKI-000009</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Electronics, Mechanical Engineering</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Electronics, Automotive, Aerospace</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Consumer Electronics, Automotive, Aerospace</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Sensor Design Engineer, Electronics Engineer, Mechatronics Engineer</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>Wearables, Automotive Systems, Drones</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>Electrical Engineering, Mechanical Engineering, Physics</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M10" s="5" t="inlineStr">
         <is>
           <t>Sensor Design, Signal Processing, MEMS Technology</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Account Development</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>SKI-000010</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Business &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Sales, Customer Relations, Marketing</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Technology, Sales, Marketing, Finance</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>SaaS, B2B Sales, Marketing, Business Development</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Account Manager, Sales Representative, Business Development Manager</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>Enterprise Solutions, CRM Systems</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>Business, Marketing, Sales</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>Relationship Management, Negotiation, Communication, Data Analysis</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Account Information Services</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>SKI-000011</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Technical &amp; Support Skill</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>IT Services, Data Management, Security</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Finance, Healthcare, Telecommunications</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Banking, Healthcare, Telecom, Finance</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>IT Specialist, Account Information Manager, Data Analyst</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>Data Security, Information Management</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>Information Technology, Computer Science</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>Data Management, Security Protocols, Database Design</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>ADC/DAC</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>SKI-000012</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Electronics, Signal Processing</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Telecommunications, Consumer Electronics</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>Telecommunications, Audio/Video, Consumer Electronics</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Electronics Engineer, Signal Processing Engineer</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>Audio Devices, Communication Systems</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>Electrical Engineering, Signal Processing</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>Analog to Digital Conversion, Signal Processing, Circuit Design</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Advanced Packaging</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>SKI-000013</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Engineering, Manufacturing</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Manufacturing, Electronics, Consumer Goods</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Electronics, Semiconductor, Consumer Goods</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Packaging Engineer, Process Engineer, Materials Scientist</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>Microelectronics, Consumer Electronics</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>Mechanical Engineering, Materials Science</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M14" s="5" t="inlineStr">
         <is>
           <t>3D Modeling, Thermal Management, Structural Integrity</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>AI for Fraud Detection</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>SKI-000014</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Artificial Intelligence, Data Science</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Finance, Cybersecurity, E-commerce</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>Finance, E-commerce, Banking, Cybersecurity</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Data Scientist, AI Engineer, Fraud Analyst</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>Fraud Detection Systems, Security Software</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Data Science, Engineering</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M15" s="5" t="inlineStr">
         <is>
           <t>Machine Learning, Pattern Recognition, Data Analytics</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Algorithm Development</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>SKI-000015</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Technology, Finance, AI, Data Science</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>Software Development, Machine Learning, Data Science</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Software Engineer, Data Scientist, Algorithm Engineer</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>Software Algorithms, Data Processing, AI Models</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Mathematics, Engineering</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M16" s="5" t="inlineStr">
         <is>
           <t>Problem Solving, Optimization, Data Structures, Programming</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="5" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Algorithmic Bias</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>SKI-000016</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Analytical Skill</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Data Science, Ethics, AI</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Technology, Ethics, Data Science</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>AI, Machine Learning, Social Sciences</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>AI Researcher, Data Scientist, Ethicist</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>AI Models, Machine Learning Systems</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Ethics, Social Science</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>Bias Detection, Fairness in AI, Ethical Decision Making</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Algorithmic Bias Analysis</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>SKI-000017</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Analytical Skill</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Data Science, Ethics, AI</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Technology, Ethics, Data Science</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>AI, Machine Learning, Social Sciences</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>AI Researcher, Data Scientist, Ethicist, Policy Analyst</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>AI Models, Bias Detection Systems</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Ethics, Social Science</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M18" s="5" t="inlineStr">
         <is>
           <t>Fairness Audits, Algorithmic Evaluation, Bias Metrics</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Algorithmic Complexity</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>SKI-000018</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Analytical &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Mathematics</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Technology, Research, AI, Academia</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>Software Development, Research, AI</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Algorithm Engineer, Data Scientist, Software Engineer</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>Algorithm Optimization, Complexity Analysis</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Mathematics</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M19" s="5" t="inlineStr">
         <is>
           <t>Complexity Theory, Algorithmic Design, Data Structures</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Algorithmic Problem Solving</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>SKI-000019</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Analytical &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Problem Solving, Computer Science</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Technology, Finance, Research, AI</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>Software Development, Competitive Programming, AI</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Software Engineer, Data Scientist, Algorithm Developer</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>Coding Competitions, AI Models, Optimization</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Mathematics, Engineering</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M20" s="5" t="inlineStr">
         <is>
           <t>Critical Thinking, Logical Reasoning, Programming Skills</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Algorithmic Trading</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>SKI-000020</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Finance, Data Science, Software Engineering</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Finance, Technology, Trading</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>Financial Markets, Hedge Funds, Trading Platforms</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Quantitative Analyst, Algorithmic Trader, Data Scientist</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>Trading Algorithms, Financial Models, Market Analytics</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>Finance, Computer Science, Mathematics</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>Data Analysis, Statistical Modeling, Market Knowledge</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Algorithms for Chemical Data</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>SKI-000021</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Data Science, Chemistry, Machine Learning</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Pharmaceuticals, Biotech, Chemistry</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>Pharmaceuticals, Biotechnology, Chemical Engineering</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Data Scientist, Chemoinformatics Specialist, Research Scientist</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>Chemical Data Models, Drug Discovery Tools</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>Chemistry, Computer Science, Biostatistics</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M22" s="5" t="inlineStr">
         <is>
           <t>Chemoinformatics, Pattern Recognition, Statistical Analysis</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Altera/Intel FPGA</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>SKI-000022</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Electronics, Hardware Engineering, Programming</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Technology, Telecommunications, Electronics</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>Telecommunications, Consumer Electronics, Computing</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>FPGA Engineer, Hardware Engineer, Embedded Systems Developer</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>Embedded Systems, Hardware Acceleration</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>Electrical Engineering, Computer Engineering, Physics</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>FPGA Programming, Hardware Design, Circuit Design</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>AML</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>SKI-000023</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Regulatory &amp; Analytical Skill</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Finance, Compliance, Risk Management</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Finance, Banking, Regulatory Compliance</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>Banking, Finance, Compliance, Security</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Compliance Officer, Risk Analyst, AML Specialist</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>Anti-Money Laundering Systems, Risk Management</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>Finance, Law, Risk Management</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M24" s="5" t="inlineStr">
         <is>
           <t>Regulatory Knowledge, Risk Assessment, Investigation Techniques</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N24" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Amplifiers</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>SKI-000024</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Electronics, Signal Processing</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Electronics, Telecommunications, Audio</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>Audio Systems, Telecommunications, Consumer Electronics</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Electronics Engineer, Audio Engineer, Signal Processing Engineer</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>Audio Amplifiers, Communication Systems</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>Electrical Engineering, Audio Engineering</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>Signal Amplification, Circuit Design, Frequency Response</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N25" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Analog and Digital Design</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>SKI-000025</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Electronics, Circuit Design, Engineering</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Electronics, Automotive, Telecommunications</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>Consumer Electronics, Automotive, Telecommunications</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>Circuit Designer, Electronics Engineer, Embedded Systems Engineer</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>Consumer Electronics, Communication Devices</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L26" s="5" t="inlineStr">
         <is>
           <t>Electrical Engineering, Physics, Computer Engineering</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M26" s="5" t="inlineStr">
         <is>
           <t>Circuit Design, Signal Processing, Mixed-Signal Systems</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N26" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O26" s="5" t="n"/>
+      <c r="P26" s="5" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Analog Circuit Design</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>SKI-000026</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Electronics, Circuit Design</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Electronics, Automotive, Telecommunications</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>Consumer Electronics, Telecommunications, Automotive</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Circuit Designer, Electronics Engineer, Embedded Systems Engineer</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>Audio Devices, Communication Systems, Consumer Electronics</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>Electrical Engineering, Physics, Computer Engineering</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
         <is>
           <t>Circuit Design, Signal Integrity, Frequency Response</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N27" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Analog-to-Digital Conversion</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>SKI-000027</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Electronics, Signal Processing, Data Acquisition</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Electronics, Telecommunications, Audio</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Audio Systems, Communication Systems, Consumer Electronics</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Electronics Engineer, Signal Processing Engineer, Embedded Systems Developer</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>ADCs, Communication Systems, Consumer Electronics</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L28" s="5" t="inlineStr">
         <is>
           <t>Electrical Engineering, Physics, Computer Engineering</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M28" s="5" t="inlineStr">
         <is>
           <t>Analog-to-Digital Conversion, Signal Processing, Data Acquisition</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N28" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Antenna Design</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>SKI-000028</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Electronics, Communication Systems, Engineering</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>Telecommunications, Aerospace, Electronics</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>Telecommunications, Aerospace, Consumer Electronics</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>RF Engineer, Antenna Engineer, Communications Systems Engineer</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>Communication Systems, Wireless Networks</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>Electrical Engineering, Physics, Telecommunications</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M29" s="5" t="inlineStr">
         <is>
           <t>RF Design, Antenna Modeling, Wireless Communication</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N29" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O29" s="5" t="n"/>
+      <c r="P29" s="5" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>API Gateways</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>SKI-000029</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Software Engineering, Cloud Computing, Networking</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Technology, Cloud Computing, SaaS</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>Web Development, Cloud Applications, SaaS</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>API Engineer, Backend Developer, Cloud Solutions Architect</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>Web Applications, Cloud Services, Microservices</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L30" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering, Networking</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M30" s="5" t="inlineStr">
         <is>
           <t>API Design, Authentication, Load Balancing, Service Integration</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N30" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O30" s="5" t="n"/>
+      <c r="P30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>API Security</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>SKI-000030</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Cybersecurity, Software Engineering</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Technology, Cybersecurity, Cloud Computing</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>Web Development, Cloud Computing, SaaS</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Security Engineer, API Security Specialist, Backend Developer</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>Web Applications, API Security Systems</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Cybersecurity</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M31" s="5" t="inlineStr">
         <is>
           <t>Encryption, Authentication, Access Control, Security Protocols</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N31" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O31" s="5" t="n"/>
+      <c r="P31" s="5" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>Application Development</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>SKI-000031</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Software Engineering, Web Development</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Technology, Mobile, Web Development</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>Mobile Apps, Web Apps, Enterprise Software</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Software Developer, Mobile Developer, Full Stack Developer</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>Mobile Applications, Web Platforms</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L32" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M32" s="5" t="inlineStr">
         <is>
           <t>Programming, UI/UX Design, Databases, Problem Solving</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N32" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O32" s="5" t="n"/>
+      <c r="P32" s="5" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Application Engineering</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>SKI-000032</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Software Engineering, Product Design</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Technology, Electronics, Consumer Goods</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>SaaS, Embedded Systems, Consumer Electronics</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Application Engineer, Software Engineer, Systems Engineer</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>Software Applications, Embedded Systems</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Engineering, Product Design</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr">
         <is>
           <t>Software Design, Debugging, System Integration, User Experience</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N33" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Appointment Scheduling</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>SKI-000033</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Software Development, Business Operations</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Education, Business Services</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Business Services, Education</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Scheduling Software Developer, Operations Coordinator, IT Specialist</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>Appointment Scheduling Systems, Calendar Apps</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Business Administration</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M34" s="5" t="inlineStr">
         <is>
           <t>Time Management, Database Design, User Interface Design</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O34" s="5" t="n"/>
+      <c r="P34" s="5" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>Approximation Algorithms</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>SKI-000034</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Analytical &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Algorithms, Computer Science, Optimization</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Technology, Research, AI, Operations Research</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>Machine Learning, Data Science, Operations Research</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Algorithm Engineer, Data Scientist, Researcher</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>Optimization Problems, Computational Models</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Mathematics, Operations Research</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M35" s="5" t="inlineStr">
         <is>
           <t>Algorithm Design, Approximation Techniques, Computational Complexity</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="N35" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O35" s="5" t="n"/>
+      <c r="P35" s="5" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>Approximation Theory</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>SKI-000035</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Analytical &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Mathematics, Algorithms</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Mathematics, Technology, Research</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>AI, Operations Research, Data Science</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Researcher, Algorithm Developer, Data Scientist</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>Computational Models, Optimization Algorithms</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L36" s="5" t="inlineStr">
         <is>
           <t>Mathematics, Computer Science, Operations Research</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M36" s="5" t="inlineStr">
         <is>
           <t>Theoretical Analysis, Approximation Methods, Proofs of Bounds</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="N36" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O36" s="5" t="n"/>
+      <c r="P36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>ARM Architecture</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>SKI-000036</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Computer Architecture, Hardware Design</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Electronics, Consumer Electronics, Mobile</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>Mobile Devices, Embedded Systems, Consumer Electronics</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>Embedded Systems Engineer, Hardware Engineer, Firmware Developer</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>Mobile Devices, Embedded Systems</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>Electrical Engineering, Computer Engineering</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M37" s="5" t="inlineStr">
         <is>
           <t>ARM Assembly, Processor Design, Low-Level Programming</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N37" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>ASIC Design</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>SKI-000037</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Electronics, Hardware Design</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Electronics, Telecommunications, Computing</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>Telecommunications, Consumer Electronics, Computing</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>ASIC Engineer, Hardware Engineer, System-on-Chip (SoC) Designer</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>Integrated Circuits, Consumer Electronics</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L38" s="5" t="inlineStr">
         <is>
           <t>Electrical Engineering, Computer Engineering</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M38" s="5" t="inlineStr">
         <is>
           <t>Circuit Design, Hardware Description Languages, Optimization Techniques</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="N38" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O38" s="5" t="n"/>
+      <c r="P38" s="5" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Assertion Languages</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>SKI-000038</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Software Engineering, Verification</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>Electronics, Software Engineering</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>Embedded Systems, Semiconductor Design, Formal Verification</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>Verification Engineer, Hardware Engineer, Software Tester</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>Design Verification, Testbenches</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>Electrical Engineering, Computer Science</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr">
         <is>
           <t>Formal Methods, Hardware Verification, Test Automation</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N39" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O39" s="5" t="n"/>
+      <c r="P39" s="5" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>Assertion-Based Verification</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>SKI-000039</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Software Verification, Hardware Design</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>Electronics, Software Engineering</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>Semiconductor Design, Embedded Systems, Software Development</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>Verification Engineer, Embedded Systems Engineer, Hardware Engineer</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>Verification Tools, Testbenches, Simulation Models</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>Electrical Engineering, Computer Science, Software Engineering</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M40" s="5" t="inlineStr">
         <is>
           <t>Formal Verification, Test Automation, Debugging, Model Checking</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="N40" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O40" s="5" t="n"/>
+      <c r="P40" s="5" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Asset Allocation</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>SKI-000040</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Financial Skill</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Finance, Investment Management</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>Finance, Investment, Wealth Management</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>Hedge Funds, Wealth Management, Financial Planning</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>Portfolio Manager, Financial Analyst, Investment Advisor</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>Investment Portfolios, Risk Management</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>Finance, Economics, Mathematics</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M41" s="5" t="inlineStr">
         <is>
           <t>Risk Management, Portfolio Diversification, Statistical Analysis</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N41" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O41" s="5" t="n"/>
+      <c r="P41" s="5" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>Asset Valuation</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>SKI-000041</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>Financial Skill</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>Finance, Real Estate, Investment</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>Finance, Real Estate, Private Equity</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>Real Estate, Private Equity, Public Markets</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>Valuation Analyst, Financial Analyst, Real Estate Appraiser</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>Investment Valuation, Property Valuation</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L42" s="5" t="inlineStr">
         <is>
           <t>Finance, Economics, Real Estate</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M42" s="5" t="inlineStr">
         <is>
           <t>Market Analysis, Discounted Cash Flow, Comparable Analysis</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N42" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O42" s="5" t="n"/>
+      <c r="P42" s="5" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>Astronomy</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>SKI-000042</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>Scientific Skill</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Space Science, Physics</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>Research, Education, Space Exploration</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>Research, Education, Space Exploration</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>Astronomer, Astrophysicist, Research Scientist</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>Space Research, Telescopes, Space Missions</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>Physics, Astronomy, Mathematics</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M43" s="5" t="inlineStr">
         <is>
           <t>Celestial Observation, Telescope Operation, Research Methods</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="N43" s="5" t="inlineStr">
         <is>
           <t>2-3 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O43" s="5" t="n"/>
+      <c r="P43" s="5" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Astronomy Data Formats</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>SKI-000043</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Data Science, Astronomy, Software Engineering</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>Research, Space Science, Astronomy</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>Space Research, Data Science, Astrophysics</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>Data Scientist, Researcher, Software Developer</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K44" s="5" t="inlineStr">
         <is>
           <t>Space Observations, Data Analysis</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L44" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Astronomy, Data Science</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M44" s="5" t="inlineStr">
         <is>
           <t>Data Parsing, Format Conversion, Data Storage Systems</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="N44" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O44" s="5" t="n"/>
+      <c r="P44" s="5" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Astrophysical Modeling</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>SKI-000044</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>Scientific &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>Astrophysics, Computational Modeling</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>Research, Space Science, Education</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>Space Research, Simulation, Education</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>Astrophysicist, Computational Scientist, Researcher</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>Space Simulations, Astrophysical Models</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>Physics, Mathematics, Computer Science</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M45" s="5" t="inlineStr">
         <is>
           <t>Numerical Simulation, Mathematical Modeling, Computational Physics</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N45" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O45" s="5" t="n"/>
+      <c r="P45" s="5" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Astrophysical Simulations</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>SKI-000045</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>Astrophysics, Computational Science</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>Research, Space Science, Education</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="inlineStr">
         <is>
           <t>Research, Space Science, Simulations</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>Astrophysicist, Simulation Specialist, Research Scientist</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>Computational Models, Simulation Software</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L46" s="5" t="inlineStr">
         <is>
           <t>Physics, Computer Science, Mathematics</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M46" s="5" t="inlineStr">
         <is>
           <t>Simulation Software, Numerical Methods, High-Performance Computing</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N46" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O46" s="5" t="n"/>
+      <c r="P46" s="5" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Astrophysics</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>SKI-000046</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>Scientific Skill</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>Physics, Space Science</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>Research, Space Science, Education</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>Research, Education, Space Exploration</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>Astrophysicist, Research Scientist, Educator</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>Space Research, Scientific Discoveries</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L47" s="5" t="inlineStr">
         <is>
           <t>Physics, Mathematics, Astronomy</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M47" s="5" t="inlineStr">
         <is>
           <t>Theoretical Physics, Research, Data Analysis, Observation Methods</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N47" s="5" t="inlineStr">
         <is>
           <t>2-3 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O47" s="5" t="n"/>
+      <c r="P47" s="5" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>ATE</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>SKI-000047</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>Electronics, Testing, Engineering</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>Electronics, Aerospace, Automotive</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>Electronics Manufacturing, Aerospace, Automotive</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J48" s="5" t="inlineStr">
         <is>
           <t>Test Engineer, ATE Engineer, Electronics Engineer</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K48" s="5" t="inlineStr">
         <is>
           <t>Testing Systems, Electronics Validation</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="L48" s="5" t="inlineStr">
         <is>
           <t>Electrical Engineering, Computer Science, Physics</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="M48" s="5" t="inlineStr">
         <is>
           <t>Test Automation, Hardware Testing, Software Integration</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="N48" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O48" s="5" t="n"/>
+      <c r="P48" s="5" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>ATE Equipment Maintenance</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>SKI-000048</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>Electronics, Maintenance, Engineering</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>Electronics, Aerospace, Manufacturing</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="H49" s="5" t="n"/>
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>Manufacturing, Aerospace, Electronics Repair</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>Maintenance Technician, ATE Engineer, Repair Specialist</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>Test Equipment, Circuit Boards, Diagnostic Systems</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L49" s="5" t="inlineStr">
         <is>
           <t>Electrical Engineering, Mechanical Engineering</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M49" s="5" t="inlineStr">
         <is>
           <t>Troubleshooting, Maintenance Protocols, Diagnostics</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="N49" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O49" s="5" t="n"/>
+      <c r="P49" s="5" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>Atmospheric Modeling</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>SKI-000049</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>Scientific &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>Atmospheric Science, Environmental Science</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>Environmental Science, Aerospace, Research</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>Meteorology, Climate Science, Aerospace</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>Atmospheric Scientist, Meteorologist, Climate Modeler</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K50" s="5" t="inlineStr">
         <is>
           <t>Weather Forecasting, Climate Simulations</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="L50" s="5" t="inlineStr">
         <is>
           <t>Environmental Science, Atmospheric Science, Physics</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="M50" s="5" t="inlineStr">
         <is>
           <t>Numerical Weather Prediction, Data Assimilation, Climate Modeling</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="N50" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O50" s="5" t="n"/>
+      <c r="P50" s="5" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>Audit Coordination</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>SKI-000050</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>Business &amp; Organizational Skill</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>Audit, Risk Management, Compliance</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>Finance, Healthcare, Government, Corporate</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>Finance, Healthcare, Government, Corporate</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>Audit Manager, Audit Coordinator, Compliance Officer</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K51" s="5" t="inlineStr">
         <is>
           <t>Audit Processes, Risk Management</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L51" s="5" t="inlineStr">
         <is>
           <t>Business Administration, Finance, Accounting</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="M51" s="5" t="inlineStr">
         <is>
           <t>Coordination, Risk Assessment, Documentation, Regulatory Knowledge</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="N51" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O51" s="5" t="n"/>
+      <c r="P51" s="5" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>Audit Methodologies</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>SKI-000051</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>Analytical &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>Audit, Risk Management, Compliance</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>Finance, Healthcare, Government, Corporate</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>Finance, Government, Healthcare, Corporate</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>Auditor, Risk Analyst, Compliance Specialist</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K52" s="5" t="inlineStr">
         <is>
           <t>Audit Processes, Compliance Testing</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="L52" s="5" t="inlineStr">
         <is>
           <t>Accounting, Finance, Business Administration</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="M52" s="5" t="inlineStr">
         <is>
           <t>Internal Control Frameworks, Risk Assessment, Regulatory Knowledge</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="N52" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O52" s="5" t="n"/>
+      <c r="P52" s="5" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>Authentication Protocols</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>SKI-000052</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>Cybersecurity, Networking</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>Technology, Cybersecurity, IT</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>Web Development, Cloud Computing, IT Security</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>Security Engineer, Network Engineer, Cybersecurity Analyst</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>Security Systems, Cloud Authentication</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L53" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Network Engineering, Cybersecurity</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M53" s="5" t="inlineStr">
         <is>
           <t>Encryption, Access Control, Protocol Analysis, Identity Management</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="N53" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O53" s="5" t="n"/>
+      <c r="P53" s="5" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>Automated Assembly</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>SKI-000053</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>Manufacturing, Robotics</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>Manufacturing, Automotive, Electronics</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="H54" s="5" t="n"/>
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>Manufacturing, Automotive, Consumer Electronics</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>Automation Engineer, Robotics Engineer, Manufacturing Engineer</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="K54" s="5" t="inlineStr">
         <is>
           <t>Production Lines, Robotics Systems</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="L54" s="5" t="inlineStr">
         <is>
           <t>Mechanical Engineering, Electrical Engineering</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="M54" s="5" t="inlineStr">
         <is>
           <t>Robotics, Process Optimization, Mechatronics, System Integration</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="N54" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O54" s="5" t="n"/>
+      <c r="P54" s="5" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>Automated Test Equipment</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>SKI-000054</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>Electronics, Testing, Engineering</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>Electronics, Aerospace, Automotive</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>Electronics Manufacturing, Aerospace, Automotive</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>Test Engineer, ATE Engineer, Electronics Engineer</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>Testing Systems, Circuit Boards, Validation</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="L55" s="5" t="inlineStr">
         <is>
           <t>Electrical Engineering, Computer Science, Physics</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="M55" s="5" t="inlineStr">
         <is>
           <t>Test Automation, Hardware Testing, Software Integration</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="N55" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O55" s="5" t="n"/>
+      <c r="P55" s="5" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>Automation Systems</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>SKI-000055</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>Engineering, Robotics, Control Systems</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>Manufacturing, Aerospace, Energy, Robotics</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="H56" s="5" t="n"/>
+      <c r="I56" s="5" t="inlineStr">
         <is>
           <t>Manufacturing, Automotive, Energy, Aerospace</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J56" s="5" t="inlineStr">
         <is>
           <t>Automation Engineer, Robotics Engineer, System Integrator</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K56" s="5" t="inlineStr">
         <is>
           <t>Automated Production Lines, Robotics, Control Systems</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="L56" s="5" t="inlineStr">
         <is>
           <t>Mechanical Engineering, Electrical Engineering</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="M56" s="5" t="inlineStr">
         <is>
           <t>Robotics, Control Theory, System Design, Automation Technology</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="N56" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O56" s="5" t="n"/>
+      <c r="P56" s="5" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Automation Tools</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>SKI-000056</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>Software Engineering, Automation, Tools</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>IT, Software, Manufacturing</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="inlineStr">
         <is>
           <t>IT, Software Development, Manufacturing</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J57" s="5" t="inlineStr">
         <is>
           <t>Automation Developer, Software Engineer, Tools Specialist</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K57" s="5" t="inlineStr">
         <is>
           <t>Testing Tools, Automation Frameworks</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="L57" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="M57" s="5" t="inlineStr">
         <is>
           <t>Scripting, Process Automation, Tool Development, Integration</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="N57" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O57" s="5" t="n"/>
+      <c r="P57" s="5" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>Automotive Safety Standards</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>SKI-000057</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>Regulatory &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>Automotive, Safety, Compliance</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>Automotive, Engineering, Compliance</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="inlineStr">
         <is>
           <t>Automotive Manufacturing, Automotive Design</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J58" s="5" t="inlineStr">
         <is>
           <t>Safety Engineer, Regulatory Compliance Officer, Automotive Engineer</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="K58" s="5" t="inlineStr">
         <is>
           <t>Vehicle Safety Systems, Compliance Testing</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="L58" s="5" t="inlineStr">
         <is>
           <t>Mechanical Engineering, Automotive Engineering, Law</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="M58" s="5" t="inlineStr">
         <is>
           <t>Safety Protocols, Regulatory Standards, Vehicle Testing</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="N58" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O58" s="5" t="n"/>
+      <c r="P58" s="5" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>Automotive Systems</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>SKI-000058</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>Automotive Engineering, Electronics</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>Automotive, Electronics</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="H59" s="5" t="n"/>
+      <c r="I59" s="5" t="inlineStr">
         <is>
           <t>Automotive Design, Automotive Manufacturing</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J59" s="5" t="inlineStr">
         <is>
           <t>Automotive Engineer, Systems Engineer, Electronics Engineer</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K59" s="5" t="inlineStr">
         <is>
           <t>Automotive Components, Infotainment Systems</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="L59" s="5" t="inlineStr">
         <is>
           <t>Mechanical Engineering, Electrical Engineering, Automotive Technology</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="M59" s="5" t="inlineStr">
         <is>
           <t>Systems Design, Integration, Embedded Systems, Diagnostics</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="N59" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O59" s="5" t="n"/>
+      <c r="P59" s="5" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>Automotive Testing</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>SKI-000059</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>Automotive Engineering, Testing</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>Automotive, Engineering</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="inlineStr">
         <is>
           <t>Automotive Manufacturing, Research, Development</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J60" s="5" t="inlineStr">
         <is>
           <t>Test Engineer, Automotive Engineer, Quality Assurance Specialist</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K60" s="5" t="inlineStr">
         <is>
           <t>Vehicle Testing, Crash Simulation, Performance Evaluation</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="L60" s="5" t="inlineStr">
         <is>
           <t>Mechanical Engineering, Automotive Engineering, Testing Methods</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="M60" s="5" t="inlineStr">
         <is>
           <t>Vehicle Diagnostics, Performance Testing, Safety Standards</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="N60" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O60" s="5" t="n"/>
+      <c r="P60" s="5" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>Autonomous Systems</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>SKI-000060</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>Robotics, AI, Engineering</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>Robotics, Automotive, Aerospace, Technology</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="5" t="inlineStr">
         <is>
           <t>Robotics, Autonomous Vehicles, Aerospace</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J61" s="5" t="inlineStr">
         <is>
           <t>Robotics Engineer, Autonomous Vehicle Engineer, AI Specialist</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="K61" s="5" t="inlineStr">
         <is>
           <t>Self-Driving Cars, Drones, Robotic Systems</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="L61" s="5" t="inlineStr">
         <is>
           <t>Robotics, Computer Science, Electrical Engineering</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="M61" s="5" t="inlineStr">
         <is>
           <t>Machine Learning, Sensor Integration, System Design, Path Planning</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="N61" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O61" s="5" t="n"/>
+      <c r="P61" s="5" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>Backtesting</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>SKI-000061</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>Analytical &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>Finance, Data Science, Algorithms</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="n"/>
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>Finance, Investment, Trading</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="H62" s="5" t="n"/>
+      <c r="I62" s="5" t="inlineStr">
         <is>
           <t>Trading, Investment, Financial Planning</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J62" s="5" t="inlineStr">
         <is>
           <t>Quantitative Analyst, Algorithmic Trader, Data Scientist</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K62" s="5" t="inlineStr">
         <is>
           <t>Financial Models, Trading Strategies</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="L62" s="5" t="inlineStr">
         <is>
           <t>Finance, Economics, Data Science</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="M62" s="5" t="inlineStr">
         <is>
           <t>Statistical Modeling, Risk Management, Performance Evaluation</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="N62" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O62" s="5" t="n"/>
+      <c r="P62" s="5" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>Banking Platforms Integration</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>SKI-000062</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>Finance, Software Engineering</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="n"/>
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <t>Banking, Fintech, Technology</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="H63" s="5" t="n"/>
+      <c r="I63" s="5" t="inlineStr">
         <is>
           <t>Banking, Fintech, Payment Systems</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J63" s="5" t="inlineStr">
         <is>
           <t>Integration Specialist, Banking Software Engineer, IT Specialist</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="K63" s="5" t="inlineStr">
         <is>
           <t>Core Banking Systems, Payment Gateways</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="L63" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Finance, Software Engineering</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="M63" s="5" t="inlineStr">
         <is>
           <t>API Integration, Security, System Interoperability</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="N63" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O63" s="5" t="n"/>
+      <c r="P63" s="5" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>Banking Software</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>SKI-000063</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>Software Engineering, Finance</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="n"/>
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>Banking, Fintech, Technology</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="H64" s="5" t="n"/>
+      <c r="I64" s="5" t="inlineStr">
         <is>
           <t>Banking, Fintech, Payment Systems</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J64" s="5" t="inlineStr">
         <is>
           <t>Software Engineer, Banking Systems Architect, Fintech Developer</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="K64" s="5" t="inlineStr">
         <is>
           <t>Banking Applications, Payment Systems</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="L64" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Finance, Software Engineering</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="M64" s="5" t="inlineStr">
         <is>
           <t>Financial Software Development, Security, UX/UI Design</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="N64" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O64" s="5" t="n"/>
+      <c r="P64" s="5" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>Banking-as-a-Service</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>SKI-000064</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>Business &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>Finance, SaaS, Software Engineering</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="5" t="n"/>
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>Banking, Fintech, Technology</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="H65" s="5" t="n"/>
+      <c r="I65" s="5" t="inlineStr">
         <is>
           <t>Fintech, Digital Banking</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J65" s="5" t="inlineStr">
         <is>
           <t>SaaS Architect, Fintech Developer, Business Development Manager</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="K65" s="5" t="inlineStr">
         <is>
           <t>Digital Banking Platforms, Financial Services</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="L65" s="5" t="inlineStr">
         <is>
           <t>Business Administration, Software Engineering, Finance</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="M65" s="5" t="inlineStr">
         <is>
           <t>Cloud Solutions, API Development, Regulatory Compliance</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="N65" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O65" s="5" t="n"/>
+      <c r="P65" s="5" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>Battery Management Systems</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>SKI-000065</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>Engineering, Electronics, Software</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>Automotive, Energy, Electronics</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="H66" s="5" t="n"/>
+      <c r="I66" s="5" t="inlineStr">
         <is>
           <t>Electric Vehicles, Renewable Energy, Consumer Electronics</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J66" s="5" t="inlineStr">
         <is>
           <t>Battery Systems Engineer, Electrical Engineer, Energy Consultant</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="K66" s="5" t="inlineStr">
         <is>
           <t>Electric Vehicle Batteries, Solar Power Systems</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="L66" s="5" t="inlineStr">
         <is>
           <t>Electrical Engineering, Energy Systems, Computer Science</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="M66" s="5" t="inlineStr">
         <is>
           <t>Battery Charging, Energy Storage, Power Management</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="N66" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O66" s="5" t="n"/>
+      <c r="P66" s="5" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>Behavioral Analytics</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>SKI-000066</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>Analytical Skill</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>Data Science, Marketing, Psychology</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="n"/>
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <t>Marketing, E-commerce, Technology</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="H67" s="5" t="n"/>
+      <c r="I67" s="5" t="inlineStr">
         <is>
           <t>E-commerce, Marketing, Consumer Behavior Research</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J67" s="5" t="inlineStr">
         <is>
           <t>Data Scientist, Behavioral Analyst, Marketing Specialist</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="K67" s="5" t="inlineStr">
         <is>
           <t>Customer Insights, Behavioral Data Models</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="L67" s="5" t="inlineStr">
         <is>
           <t>Data Science, Psychology, Marketing</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="M67" s="5" t="inlineStr">
         <is>
           <t>Pattern Recognition, Customer Segmentation, Predictive Modeling</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="N67" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O67" s="5" t="n"/>
+      <c r="P67" s="5" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>Bioinformatics</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>SKI-000067</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>Scientific &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>Bioinformatics, Computational Biology</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="n"/>
+      <c r="G68" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Biotechnology, Pharmaceuticals</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="H68" s="5" t="n"/>
+      <c r="I68" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Pharmaceuticals, Biotechnology</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J68" s="5" t="inlineStr">
         <is>
           <t>Bioinformatician, Computational Biologist, Research Scientist</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="K68" s="5" t="inlineStr">
         <is>
           <t>Genomic Data Analysis, Healthcare Research</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="L68" s="5" t="inlineStr">
         <is>
           <t>Biology, Computer Science, Data Science</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="M68" s="5" t="inlineStr">
         <is>
           <t>Genomic Data Analysis, Statistical Methods, Molecular Biology</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="N68" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O68" s="5" t="n"/>
+      <c r="P68" s="5" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>Bioinformatics Algorithms</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>SKI-000068</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>Analytical &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>Bioinformatics, Computational Biology</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="n"/>
+      <c r="G69" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Biotechnology, Pharmaceuticals</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="H69" s="5" t="n"/>
+      <c r="I69" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Pharmaceuticals, Biotechnology</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J69" s="5" t="inlineStr">
         <is>
           <t>Computational Biologist, Bioinformatics Researcher, Data Scientist</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="K69" s="5" t="inlineStr">
         <is>
           <t>Genomic Research, Drug Discovery Tools</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="L69" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Biology, Mathematics</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="M69" s="5" t="inlineStr">
         <is>
           <t>Algorithm Development, Machine Learning, Data Analysis</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="N69" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O69" s="5" t="n"/>
+      <c r="P69" s="5" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>Bioinformatics Databases</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>SKI-000069</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>Bioinformatics, Data Management, Software</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="n"/>
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Biotechnology, Pharmaceuticals</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="H70" s="5" t="n"/>
+      <c r="I70" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Pharmaceuticals, Research</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="J70" s="5" t="inlineStr">
         <is>
           <t>Bioinformatics Database Administrator, Data Scientist, Researcher</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="K70" s="5" t="inlineStr">
         <is>
           <t>Genomic Databases, Medical Data Repositories</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="L70" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Biology, Data Science</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="M70" s="5" t="inlineStr">
         <is>
           <t>Database Design, Data Mining, Genomic Data Management</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="N70" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O70" s="5" t="n"/>
+      <c r="P70" s="5" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>Bioinformatics Tools</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>SKI-000070</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>Bioinformatics, Data Science, Software</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="n"/>
+      <c r="G71" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Biotechnology, Pharmaceuticals</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="H71" s="5" t="n"/>
+      <c r="I71" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Pharmaceuticals, Research</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="J71" s="5" t="inlineStr">
         <is>
           <t>Bioinformatics Specialist, Data Scientist, Computational Biologist</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="K71" s="5" t="inlineStr">
         <is>
           <t>Genomic Research, Medical Data Analysis</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="L71" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Biology, Data Science</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="M71" s="5" t="inlineStr">
         <is>
           <t>Tool Development, Data Analysis, Genomic Data Processing</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="N71" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O71" s="5" t="n"/>
+      <c r="P71" s="5" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>Biological Data Integration</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>SKI-000071</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>Bioinformatics, Data Science</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="n"/>
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Biotechnology, Pharmaceuticals</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="H72" s="5" t="n"/>
+      <c r="I72" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Biotechnology, Research</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="J72" s="5" t="inlineStr">
         <is>
           <t>Data Integration Specialist, Bioinformatics Analyst, Researcher</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="K72" s="5" t="inlineStr">
         <is>
           <t>Genomic Data Integration, Medical Records</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="L72" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Biology, Data Science</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="M72" s="5" t="inlineStr">
         <is>
           <t>Data Merging, Multi-Source Integration, Biological Data Analysis</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="N72" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O72" s="5" t="n"/>
+      <c r="P72" s="5" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>Biological Database Management</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>SKI-000072</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>Bioinformatics, Data Management</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="5" t="n"/>
+      <c r="G73" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Research, Biotechnology</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="H73" s="5" t="n"/>
+      <c r="I73" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Research, Biotechnology</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="J73" s="5" t="inlineStr">
         <is>
           <t>Database Administrator, Bioinformatics Data Manager, Research Scientist</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="K73" s="5" t="inlineStr">
         <is>
           <t>Medical Data Repositories, Genomic Databases</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="L73" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Biology, Data Management</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="M73" s="5" t="inlineStr">
         <is>
           <t>Database Design, Data Storage, Genomic Data Management</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="N73" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O73" s="5" t="n"/>
+      <c r="P73" s="5" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>Biological Databases</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>SKI-000073</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>Bioinformatics, Data Management, Software</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="n"/>
+      <c r="G74" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Biotechnology, Pharmaceuticals</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="H74" s="5" t="n"/>
+      <c r="I74" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Pharmaceuticals, Research</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="J74" s="5" t="inlineStr">
         <is>
           <t>Bioinformatics Specialist, Database Administrator, Researcher</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="K74" s="5" t="inlineStr">
         <is>
           <t>Genomic Databases, Medical Data Repositories</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="L74" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Biology, Data Science</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="M74" s="5" t="inlineStr">
         <is>
           <t>Data Organization, Data Mining, Bioinformatics Analysis</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="N74" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O74" s="5" t="n"/>
+      <c r="P74" s="5" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>Biological Networks</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>SKI-000074</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>Analytical &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>Bioinformatics, Network Analysis</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="5" t="n"/>
+      <c r="G75" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Research, Pharmaceuticals</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="H75" s="5" t="n"/>
+      <c r="I75" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Research, Pharmaceuticals</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="J75" s="5" t="inlineStr">
         <is>
           <t>Bioinformatics Network Analyst, Systems Biologist, Researcher</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="K75" s="5" t="inlineStr">
         <is>
           <t>Protein Interaction Networks, Biological Models</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="L75" s="5" t="inlineStr">
         <is>
           <t>Biology, Computer Science, Data Science</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="M75" s="5" t="inlineStr">
         <is>
           <t>Network Analysis, Systems Biology, Data Modeling</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="N75" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O75" s="5" t="n"/>
+      <c r="P75" s="5" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>Blockchain</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>SKI-000075</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>Cryptography, Distributed Systems</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="5" t="n"/>
+      <c r="G76" s="5" t="inlineStr">
         <is>
           <t>Technology, Finance, Supply Chain</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="H76" s="5" t="n"/>
+      <c r="I76" s="5" t="inlineStr">
         <is>
           <t>Finance, Technology, Supply Chain</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="J76" s="5" t="inlineStr">
         <is>
           <t>Blockchain Developer, Cryptography Engineer, Software Engineer</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="K76" s="5" t="inlineStr">
         <is>
           <t>Cryptocurrencies, Distributed Ledgers</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="L76" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Cryptography, Mathematics</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="M76" s="5" t="inlineStr">
         <is>
           <t>Blockchain Development, Smart Contracts, Security Protocols</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="N76" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O76" s="5" t="n"/>
+      <c r="P76" s="5" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>Blockchain for Compliance</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>SKI-000076</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>Blockchain, Regulatory Technology</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="n"/>
+      <c r="G77" s="5" t="inlineStr">
         <is>
           <t>Finance, Technology, Legal, Compliance</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="H77" s="5" t="n"/>
+      <c r="I77" s="5" t="inlineStr">
         <is>
           <t>Finance, Compliance, Legal, Technology</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="J77" s="5" t="inlineStr">
         <is>
           <t>Compliance Engineer, Blockchain Consultant, Regulatory Analyst</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="K77" s="5" t="inlineStr">
         <is>
           <t>Regulatory Compliance, Smart Contracts</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="L77" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Law, Business Administration</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="M77" s="5" t="inlineStr">
         <is>
           <t>Regulatory Frameworks, Smart Contract Development, Auditing</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="N77" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O77" s="5" t="n"/>
+      <c r="P77" s="5" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>Blockchain for Fraud Detection</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>SKI-000077</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>Blockchain, Security, Fraud Prevention</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="n"/>
+      <c r="G78" s="5" t="inlineStr">
         <is>
           <t>Finance, Cybersecurity, Technology</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="H78" s="5" t="n"/>
+      <c r="I78" s="5" t="inlineStr">
         <is>
           <t>Finance, Cybersecurity, Banking</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="J78" s="5" t="inlineStr">
         <is>
           <t>Blockchain Developer, Fraud Analyst, Security Specialist</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="K78" s="5" t="inlineStr">
         <is>
           <t>Fraud Prevention, Transaction Monitoring</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="L78" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Cybersecurity, Finance</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="M78" s="5" t="inlineStr">
         <is>
           <t>Transaction Analysis, Fraud Prevention, Blockchain Security</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="N78" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O78" s="5" t="n"/>
+      <c r="P78" s="5" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>Blockchain Integration</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>SKI-000078</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>Blockchain, Software Engineering</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="5" t="n"/>
+      <c r="G79" s="5" t="inlineStr">
         <is>
           <t>Technology, Finance, Supply Chain</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="H79" s="5" t="n"/>
+      <c r="I79" s="5" t="inlineStr">
         <is>
           <t>Finance, Technology, Supply Chain</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="J79" s="5" t="inlineStr">
         <is>
           <t>Blockchain Integration Specialist, Software Engineer</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="K79" s="5" t="inlineStr">
         <is>
           <t>Blockchain Solutions, Legacy System Integration</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="L79" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Engineering, Business Administration</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="M79" s="5" t="inlineStr">
         <is>
           <t>System Integration, Blockchain APIs, Software Development</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="N79" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O79" s="5" t="n"/>
+      <c r="P79" s="5" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>Blockchain Platforms</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>SKI-000079</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>Blockchain, Software Engineering</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="5" t="n"/>
+      <c r="G80" s="5" t="inlineStr">
         <is>
           <t>Technology, Finance, Decentralized Apps</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="H80" s="5" t="n"/>
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>Finance, Technology, Decentralized Applications</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="J80" s="5" t="inlineStr">
         <is>
           <t>Blockchain Developer, Platform Engineer, Technical Architect</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="K80" s="5" t="inlineStr">
         <is>
           <t>Blockchain Networks, Decentralized Apps</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="L80" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Engineering, Mathematics</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="M80" s="5" t="inlineStr">
         <is>
           <t>Blockchain Development, Network Design, Platform Architecture</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="N80" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O80" s="5" t="n"/>
+      <c r="P80" s="5" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>Blockchain Scaling</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>SKI-000080</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>Blockchain, Distributed Systems</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="E81" s="5" t="n"/>
+      <c r="F81" s="5" t="n"/>
+      <c r="G81" s="5" t="inlineStr">
         <is>
           <t>Technology, Finance, Cryptocurrency</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="H81" s="5" t="n"/>
+      <c r="I81" s="5" t="inlineStr">
         <is>
           <t>Finance, Technology, Cryptocurrency</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="J81" s="5" t="inlineStr">
         <is>
           <t>Blockchain Engineer, Distributed Systems Architect, Solutions Architect</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="K81" s="5" t="inlineStr">
         <is>
           <t>Blockchain Networks, Cryptocurrencies</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="L81" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Cryptography, Mathematics</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="M81" s="5" t="inlineStr">
         <is>
           <t>Network Optimization, Consensus Algorithms, Scaling Solutions</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="N81" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O81" s="5" t="n"/>
+      <c r="P81" s="5" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>Blockchain Security</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>SKI-000081</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>Cybersecurity, Blockchain</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="E82" s="5" t="n"/>
+      <c r="F82" s="5" t="n"/>
+      <c r="G82" s="5" t="inlineStr">
         <is>
           <t>Technology, Finance, Cybersecurity</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="H82" s="5" t="n"/>
+      <c r="I82" s="5" t="inlineStr">
         <is>
           <t>Finance, Technology, Cryptocurrency</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="J82" s="5" t="inlineStr">
         <is>
           <t>Blockchain Security Engineer, Security Analyst, Cryptography Expert</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="K82" s="5" t="inlineStr">
         <is>
           <t>Secure Transactions, Smart Contracts</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="L82" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Cryptography, Cybersecurity</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="M82" s="5" t="inlineStr">
         <is>
           <t>Encryption, Threat Detection, Security Auditing, Penetration Testing</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="N82" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O82" s="5" t="n"/>
+      <c r="P82" s="5" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="5" t="inlineStr">
         <is>
           <t>Board-Level Debugging</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>SKI-000082</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>Electronics, Embedded Systems, Debugging</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="E83" s="5" t="n"/>
+      <c r="F83" s="5" t="n"/>
+      <c r="G83" s="5" t="inlineStr">
         <is>
           <t>Electronics, Telecommunications, Technology</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="H83" s="5" t="n"/>
+      <c r="I83" s="5" t="inlineStr">
         <is>
           <t>Electronics Manufacturing, Hardware Development</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="J83" s="5" t="inlineStr">
         <is>
           <t>Hardware Engineer, Embedded Systems Engineer, Debugging Specialist</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="K83" s="5" t="inlineStr">
         <is>
           <t>Circuit Debugging, Microcontrollers</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="L83" s="5" t="inlineStr">
         <is>
           <t>Electrical Engineering, Computer Science</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="M83" s="5" t="inlineStr">
         <is>
           <t>Signal Testing, Circuit Troubleshooting, Debugging Techniques</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="N83" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O83" s="5" t="n"/>
+      <c r="P83" s="5" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>Board-Level Design</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>SKI-000083</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>Electronics, Hardware Engineering</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="E84" s="5" t="n"/>
+      <c r="F84" s="5" t="n"/>
+      <c r="G84" s="5" t="inlineStr">
         <is>
           <t>Electronics, Automotive, Telecommunications</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="H84" s="5" t="n"/>
+      <c r="I84" s="5" t="inlineStr">
         <is>
           <t>Consumer Electronics, Telecommunications, Automotive</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="J84" s="5" t="inlineStr">
         <is>
           <t>Hardware Engineer, PCB Designer, Electronics Designer</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="K84" s="5" t="inlineStr">
         <is>
           <t>PCB Design, Embedded Systems</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="L84" s="5" t="inlineStr">
         <is>
           <t>Electrical Engineering, Computer Engineering</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="M84" s="5" t="inlineStr">
         <is>
           <t>Schematic Design, Signal Integrity, PCB Layout</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="N84" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O84" s="5" t="n"/>
+      <c r="P84" s="5" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>Bonding Technology</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>SKI-000084</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>Materials Science, Electronics</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="E85" s="5" t="n"/>
+      <c r="F85" s="5" t="n"/>
+      <c r="G85" s="5" t="inlineStr">
         <is>
           <t>Electronics, Manufacturing</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="H85" s="5" t="n"/>
+      <c r="I85" s="5" t="inlineStr">
         <is>
           <t>Semiconductor Manufacturing, Electronics Assembly</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="J85" s="5" t="inlineStr">
         <is>
           <t>Process Engineer, Materials Scientist, Electronics Engineer</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="K85" s="5" t="inlineStr">
         <is>
           <t>Semiconductor Devices, Microelectronics</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="L85" s="5" t="inlineStr">
         <is>
           <t>Materials Science, Electrical Engineering</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="M85" s="5" t="inlineStr">
         <is>
           <t>Bonding Techniques, Adhesive Application, Surface Interaction</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="N85" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O85" s="5" t="n"/>
+      <c r="P85" s="5" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>Bootloaders</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="5" t="inlineStr">
         <is>
           <t>SKI-000085</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
         <is>
           <t>Embedded Systems, Software Engineering</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="E86" s="5" t="n"/>
+      <c r="F86" s="5" t="n"/>
+      <c r="G86" s="5" t="inlineStr">
         <is>
           <t>Electronics, Automotive, Software Development</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="H86" s="5" t="n"/>
+      <c r="I86" s="5" t="inlineStr">
         <is>
           <t>Firmware Development, Electronics, Automotive</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="J86" s="5" t="inlineStr">
         <is>
           <t>Firmware Engineer, Embedded Systems Developer, Bootloader Engineer</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="K86" s="5" t="inlineStr">
         <is>
           <t>Bootloading Software, Embedded Systems</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="L86" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Electrical Engineering</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="M86" s="5" t="inlineStr">
         <is>
           <t>Firmware Programming, System Initialization, Low-Level Debugging</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="N86" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O86" s="5" t="n"/>
+      <c r="P86" s="5" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>Brain Networks</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>SKI-000086</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>Scientific &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>Neuroscience, Artificial Intelligence</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="5" t="n"/>
+      <c r="G87" s="5" t="inlineStr">
         <is>
           <t>Healthcare, AI, Research</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="H87" s="5" t="n"/>
+      <c r="I87" s="5" t="inlineStr">
         <is>
           <t>Healthcare, AI Research, Cognitive Science</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="J87" s="5" t="inlineStr">
         <is>
           <t>Neuroscientist, AI Researcher, Cognitive Systems Engineer</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="K87" s="5" t="inlineStr">
         <is>
           <t>Neural Networks, Brain Simulation</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="L87" s="5" t="inlineStr">
         <is>
           <t>Neuroscience, AI, Computer Science</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="M87" s="5" t="inlineStr">
         <is>
           <t>Neural Connectivity, Computational Neuroscience, Brain Mapping</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
+      <c r="N87" s="5" t="inlineStr">
         <is>
           <t>2-3 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O87" s="5" t="n"/>
+      <c r="P87" s="5" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="5" t="inlineStr">
         <is>
           <t>Brain Simulation</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="5" t="inlineStr">
         <is>
           <t>SKI-000087</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="5" t="inlineStr">
         <is>
           <t>Scientific &amp; Technical Skill</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" s="5" t="inlineStr">
         <is>
           <t>Neuroscience, AI, Simulation</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="E88" s="5" t="n"/>
+      <c r="F88" s="5" t="n"/>
+      <c r="G88" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Research, AI</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="H88" s="5" t="n"/>
+      <c r="I88" s="5" t="inlineStr">
         <is>
           <t>Healthcare, Cognitive Science, AI Research</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="J88" s="5" t="inlineStr">
         <is>
           <t>Neuroscientist, Simulation Scientist, Computational Neuroscientist</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="K88" s="5" t="inlineStr">
         <is>
           <t>Brain Models, Cognitive Simulations</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="L88" s="5" t="inlineStr">
         <is>
           <t>Neuroscience, AI, Computer Science</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="M88" s="5" t="inlineStr">
         <is>
           <t>Neural Simulation, Cognitive Modeling, Brain Network Analysis</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
+      <c r="N88" s="5" t="inlineStr">
         <is>
           <t>2-3 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O88" s="5" t="n"/>
+      <c r="P88" s="5" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>Brand Building</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="5" t="inlineStr">
         <is>
           <t>SKI-000088</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
         <is>
           <t>Business &amp; Marketing Skill</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>Marketing, Branding</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="E89" s="5" t="n"/>
+      <c r="F89" s="5" t="n"/>
+      <c r="G89" s="5" t="inlineStr">
         <is>
           <t>Retail, Consumer Goods, Marketing</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="H89" s="5" t="n"/>
+      <c r="I89" s="5" t="inlineStr">
         <is>
           <t>Consumer Goods, Digital Marketing, Retail</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="J89" s="5" t="inlineStr">
         <is>
           <t>Brand Manager, Marketing Director, Digital Marketing Specialist</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="K89" s="5" t="inlineStr">
         <is>
           <t>Brand Strategy, Marketing Campaigns</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="L89" s="5" t="inlineStr">
         <is>
           <t>Marketing, Business Administration, Communications</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="M89" s="5" t="inlineStr">
         <is>
           <t>Market Research, Content Creation, Audience Engagement</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="N89" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O89" s="5" t="n"/>
+      <c r="P89" s="5" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="5" t="inlineStr">
         <is>
           <t>Brand Development</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t>SKI-000089</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
         <is>
           <t>Business &amp; Marketing Skill</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>Marketing, Branding, Strategy</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="E90" s="5" t="n"/>
+      <c r="F90" s="5" t="n"/>
+      <c r="G90" s="5" t="inlineStr">
         <is>
           <t>Retail, Advertising, Consumer Goods</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="H90" s="5" t="n"/>
+      <c r="I90" s="5" t="inlineStr">
         <is>
           <t>Advertising, Retail, Consumer Goods</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="J90" s="5" t="inlineStr">
         <is>
           <t>Brand Strategist, Marketing Manager, Product Manager</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="K90" s="5" t="inlineStr">
         <is>
           <t>Brand Positioning, Product Identity</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="L90" s="5" t="inlineStr">
         <is>
           <t>Marketing, Business Administration, Communications</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="M90" s="5" t="inlineStr">
         <is>
           <t>Brand Strategy, Customer Insights, Competitive Analysis</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="N90" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1-2 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O90" s="5" t="n"/>
+      <c r="P90" s="5" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>Burn-In Testing</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="5" t="inlineStr">
         <is>
           <t>SKI-000090</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>Quality Assurance, Testing</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="E91" s="5" t="n"/>
+      <c r="F91" s="5" t="n"/>
+      <c r="G91" s="5" t="inlineStr">
         <is>
           <t>Electronics, Automotive, Manufacturing</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="H91" s="5" t="n"/>
+      <c r="I91" s="5" t="inlineStr">
         <is>
           <t>Electronics, Manufacturing, Automotive</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="J91" s="5" t="inlineStr">
         <is>
           <t>Test Engineer, QA Engineer, Manufacturing Specialist</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="K91" s="5" t="inlineStr">
         <is>
           <t>Product Testing, Reliability Evaluation</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="L91" s="5" t="inlineStr">
         <is>
           <t>Electrical Engineering, Mechanical Engineering</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="M91" s="5" t="inlineStr">
         <is>
           <t>Stress Testing, System Testing, Failure Prediction</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="N91" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O91" s="5" t="n"/>
+      <c r="P91" s="5" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t>Bus Architectures</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>SKI-000091</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>Computer Architecture, Hardware Design</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="E92" s="5" t="n"/>
+      <c r="F92" s="5" t="n"/>
+      <c r="G92" s="5" t="inlineStr">
         <is>
           <t>Electronics, Technology, Embedded Systems</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="H92" s="5" t="n"/>
+      <c r="I92" s="5" t="inlineStr">
         <is>
           <t>Electronics, Computer Science, Embedded Systems</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="J92" s="5" t="inlineStr">
         <is>
           <t>Systems Architect, Hardware Engineer, Embedded Systems Designer</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="K92" s="5" t="inlineStr">
         <is>
           <t>Computer Systems, Microprocessor Design</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="L92" s="5" t="inlineStr">
         <is>
           <t>Computer Engineering, Electrical Engineering</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="M92" s="5" t="inlineStr">
         <is>
           <t>Data Transfer Optimization, Hardware Design, System Architecture</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
+      <c r="N92" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O92" s="5" t="n"/>
+      <c r="P92" s="5" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="5" t="inlineStr">
         <is>
           <t>Business Continuity Planning</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>SKI-000092</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="5" t="inlineStr">
         <is>
           <t>Business &amp; Organizational Skill</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>Risk Management, Business Strategy</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="E93" s="5" t="n"/>
+      <c r="F93" s="5" t="n"/>
+      <c r="G93" s="5" t="inlineStr">
         <is>
           <t>IT, Healthcare, Government, Corporate</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="H93" s="5" t="n"/>
+      <c r="I93" s="5" t="inlineStr">
         <is>
           <t>IT, Healthcare, Corporate, Government</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="J93" s="5" t="inlineStr">
         <is>
           <t>Business Continuity Planner, Risk Manager, Operations Manager</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="K93" s="5" t="inlineStr">
         <is>
           <t>Continuity Plans, Disaster Recovery</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="L93" s="5" t="inlineStr">
         <is>
           <t>Business Administration, Risk Management, IT Management</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="M93" s="5" t="inlineStr">
         <is>
           <t>Crisis Management, Risk Analysis, Strategic Planning</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
+      <c r="N93" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O93" s="5" t="n"/>
+      <c r="P93" s="5" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t>C Programming</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="5" t="inlineStr">
         <is>
           <t>SKI-000093</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>Software Development, Programming</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="E94" s="5" t="n"/>
+      <c r="F94" s="5" t="n"/>
+      <c r="G94" s="5" t="inlineStr">
         <is>
           <t>Technology, Electronics, Software Development</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="H94" s="5" t="n"/>
+      <c r="I94" s="5" t="inlineStr">
         <is>
           <t>Software Development, Embedded Systems</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="J94" s="5" t="inlineStr">
         <is>
           <t>Software Developer, Embedded Systems Engineer, Programmer</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="K94" s="5" t="inlineStr">
         <is>
           <t>Applications, Firmware, Systems Software</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="L94" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
+      <c r="M94" s="5" t="inlineStr">
         <is>
           <t>Algorithm Development, Memory Management, System-Level Programming</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
+      <c r="N94" s="5" t="inlineStr">
         <is>
           <t>6-12 months (basic proficiency), 1 year (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O94" s="5" t="n"/>
+      <c r="P94" s="5" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t>C/C++ Programming</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>SKI-000094</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>Software Development, Programming</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="E95" s="5" t="n"/>
+      <c r="F95" s="5" t="n"/>
+      <c r="G95" s="5" t="inlineStr">
         <is>
           <t>Technology, Gaming, Electronics, Software</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="H95" s="5" t="n"/>
+      <c r="I95" s="5" t="inlineStr">
         <is>
           <t>Software Development, Embedded Systems, Game Development</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="J95" s="5" t="inlineStr">
         <is>
           <t>Software Developer, Game Developer, Systems Programmer</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="K95" s="5" t="inlineStr">
         <is>
           <t>Applications, Game Engines, Systems Software</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="L95" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr">
+      <c r="M95" s="5" t="inlineStr">
         <is>
           <t>Memory Management, Object-Oriented Programming, Multi-threading</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr">
+      <c r="N95" s="5" t="inlineStr">
         <is>
           <t>1 year (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O95" s="5" t="n"/>
+      <c r="P95" s="5" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t>C/C++/Fortran Programming</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="5" t="inlineStr">
         <is>
           <t>SKI-000095</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>Software Development, Programming</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="5" t="n"/>
+      <c r="G96" s="5" t="inlineStr">
         <is>
           <t>Technology, Science, Research</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="H96" s="5" t="n"/>
+      <c r="I96" s="5" t="inlineStr">
         <is>
           <t>High-Performance Computing, Embedded Systems</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="J96" s="5" t="inlineStr">
         <is>
           <t>HPC Developer, Embedded Systems Engineer, Programmer</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="K96" s="5" t="inlineStr">
         <is>
           <t>Simulation Software, Scientific Applications</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="L96" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Engineering, Computational Science</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr">
+      <c r="M96" s="5" t="inlineStr">
         <is>
           <t>Numerical Methods, Performance Optimization, Parallel Programming</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr">
+      <c r="N96" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O96" s="5" t="n"/>
+      <c r="P96" s="5" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>C/C++/Python Programming</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>SKI-000096</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>Software Development, Programming</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="E97" s="5" t="n"/>
+      <c r="F97" s="5" t="n"/>
+      <c r="G97" s="5" t="inlineStr">
         <is>
           <t>Technology, Data Science, Gaming, Software</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="H97" s="5" t="n"/>
+      <c r="I97" s="5" t="inlineStr">
         <is>
           <t>Software Development, Data Science, Game Development</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="J97" s="5" t="inlineStr">
         <is>
           <t>Software Developer, Data Scientist, Game Programmer</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="K97" s="5" t="inlineStr">
         <is>
           <t>Applications, Data Analysis, Game Development</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="L97" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering, Data Science</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
+      <c r="M97" s="5" t="inlineStr">
         <is>
           <t>Object-Oriented Programming, Algorithm Design, Data Structures</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr">
+      <c r="N97" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O97" s="5" t="n"/>
+      <c r="P97" s="5" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>C++/Java Programming</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="5" t="inlineStr">
         <is>
           <t>SKI-000097</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>Software Development, Programming</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="E98" s="5" t="n"/>
+      <c r="F98" s="5" t="n"/>
+      <c r="G98" s="5" t="inlineStr">
         <is>
           <t>Technology, Software, Mobile Development</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="H98" s="5" t="n"/>
+      <c r="I98" s="5" t="inlineStr">
         <is>
           <t>Software Development, Web Development, Mobile Apps</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="J98" s="5" t="inlineStr">
         <is>
           <t>Software Developer, Mobile App Developer, Web Developer</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="K98" s="5" t="inlineStr">
         <is>
           <t>Applications, Web Apps, Mobile Apps</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="L98" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
+      <c r="M98" s="5" t="inlineStr">
         <is>
           <t>Object-Oriented Programming, Cross-platform Development, Web Development</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
+      <c r="N98" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate expertise)</t>
         </is>
       </c>
+      <c r="O98" s="5" t="n"/>
+      <c r="P98" s="5" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>C++/Java/Python Programming</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>SKI-000098</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>Software Development, Programming</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="E99" s="5" t="n"/>
+      <c r="F99" s="5" t="n"/>
+      <c r="G99" s="5" t="inlineStr">
         <is>
           <t>Technology, Data Science, Software Development</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="H99" s="5" t="n"/>
+      <c r="I99" s="5" t="inlineStr">
         <is>
           <t>Software Development, Data Science, Web Development</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="J99" s="5" t="inlineStr">
         <is>
           <t>Software Developer, Data Scientist, Web Developer</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="K99" s="5" t="inlineStr">
         <is>
           <t>Applications, Data Analysis, Web Development</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="L99" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering, Data Science</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="M99" s="5" t="inlineStr">
         <is>
           <t>Object-Oriented Programming, Full-stack Development, Data Structures</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
+      <c r="N99" s="5" t="inlineStr">
         <is>
           <t>2-3 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O99" s="5" t="n"/>
+      <c r="P99" s="5" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>C++/Python Programming</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="5" t="inlineStr">
         <is>
           <t>SKI-000099</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>Software Development, Programming</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="E100" s="5" t="n"/>
+      <c r="F100" s="5" t="n"/>
+      <c r="G100" s="5" t="inlineStr">
         <is>
           <t>Technology, Software, Data Science</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="H100" s="5" t="n"/>
+      <c r="I100" s="5" t="inlineStr">
         <is>
           <t>Software Development, Data Science, Embedded Systems</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="J100" s="5" t="inlineStr">
         <is>
           <t>Software Developer, Data Scientist, Embedded Systems Engineer</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="K100" s="5" t="inlineStr">
         <is>
           <t>Applications, Machine Learning, Embedded Systems</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="L100" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering, Data Science</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr">
+      <c r="M100" s="5" t="inlineStr">
         <is>
           <t>Data Structures, Algorithm Optimization, Embedded Programming</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr">
+      <c r="N100" s="5" t="inlineStr">
         <is>
           <t>1-2 years (intermediate to advanced expertise)</t>
         </is>
       </c>
+      <c r="O100" s="5" t="n"/>
+      <c r="P100" s="5" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>C++/Python/Java Programming</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>SKI-000100</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Technical Skill</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Technical Skill</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>Software Development, Programming</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="E101" s="5" t="n"/>
+      <c r="F101" s="5" t="n"/>
+      <c r="G101" s="5" t="inlineStr">
         <is>
           <t>Technology, Software, Data Science</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="H101" s="5" t="n"/>
+      <c r="I101" s="5" t="inlineStr">
         <is>
           <t>Software Development, Data Science, AI</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="J101" s="5" t="inlineStr">
         <is>
           <t>Software Developer, Data Scientist, AI Engineer</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="K101" s="5" t="inlineStr">
         <is>
           <t>Applications, Data Analysis, AI Development</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="L101" s="5" t="inlineStr">
         <is>
           <t>Computer Science, Software Engineering, Data Science</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="M101" s="5" t="inlineStr">
         <is>
           <t>Object-Oriented Programming, Full-stack Development, Machine Learning</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr">
+      <c r="N101" s="5" t="inlineStr">
         <is>
           <t>2-3 years (advanced expertise)</t>
         </is>
       </c>
+      <c r="O101" s="5" t="n"/>
+      <c r="P101" s="5" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>

--- a/apps/api/data/excel_templates/skills.xlsx
+++ b/apps/api/data/excel_templates/skills.xlsx
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FinTech, Software Development, Supply Chain, Gaming</t>
+          <t>FinTech;Software Development;Supply Chain;Gaming</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Blockchain Developer, Software Engineer, Smart Contract Developer</t>
+          <t>Blockchain Developer;Software Engineer;Smart Contract Developer</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Cryptocurrencies, Decentralized Applications, Smart Contracts</t>
+          <t>Cryptocurrencies;Decentralized Applications;Smart Contracts</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Computer Science, Engineering, Cryptography</t>
+          <t>Computer Science;Engineering;Cryptography</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Cryptography, Distributed Systems, Smart Contracts, Security</t>
+          <t>Cryptography;Distributed Systems;Smart Contracts;Security</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -620,27 +620,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Game Design, Film Production, Architecture, VR/AR</t>
+          <t>Game Design;Film Production;Architecture;VR/AR</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3D Modeler, Character Artist, Industrial Designer</t>
+          <t>3D Modeler;Character Artist;Industrial Designer</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Video Games, Films, Virtual Environments</t>
+          <t>Video Games;Films;Virtual Environments</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Digital Arts, Fine Arts, Game Design</t>
+          <t>Digital Arts;Fine Arts;Game Design</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Creativity, Texturing, Lighting, Attention to Detail, Software Proficiency (e.g., Blender, Maya, ZBrush)</t>
+          <t>Creativity;Texturing;Lighting;Attention to Detail;Software Proficiency (e.g.;Blender;Maya;ZBrush)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -677,27 +677,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Robotics, Engineering, Game Design, Simulation</t>
+          <t>Robotics;Engineering;Game Design;Simulation</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Computational Geometer, Robotics Engineer, Simulation Developer</t>
+          <t>Computational Geometer;Robotics Engineer;Simulation Developer</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Robotics, Engineering Software, Games</t>
+          <t>Robotics;Engineering Software;Games</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Mathematics, Computer Science, Engineering</t>
+          <t>Mathematics;Computer Science;Engineering</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Geometry Algorithms, Spatial Data Structures, Programming (e.g., C++, Python)</t>
+          <t>Geometry Algorithms;Spatial Data Structures;Programming (e.g.;C++;Python)</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -734,27 +734,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Semiconductor Industry, Electronics Manufacturing</t>
+          <t>Semiconductor Industry;Electronics Manufacturing</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>IC Design Engineer, Circuit Designer, Electronics Engineer</t>
+          <t>IC Design Engineer;Circuit Designer;Electronics Engineer</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Semiconductors, Consumer Electronics</t>
+          <t>Semiconductors;Consumer Electronics</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Electrical Engineering, Computer Engineering</t>
+          <t>Electrical Engineering;Computer Engineering</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Circuit Design, CAD Tools, Signal Processing, Physical Design</t>
+          <t>Circuit Design;CAD Tools;Signal Processing;Physical Design</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -791,27 +791,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Medical Imaging, Computer Vision, Virtual Reality</t>
+          <t>Medical Imaging;Computer Vision;Virtual Reality</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Imaging Specialist, Data Scientist, Research Scientist</t>
+          <t>Imaging Specialist;Data Scientist;Research Scientist</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Medical Scans, 3D Models, Virtual Reality</t>
+          <t>Medical Scans;3D Models;Virtual Reality</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Computer Science, Biomedical Engineering, Mathematics</t>
+          <t>Computer Science;Biomedical Engineering;Mathematics</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Image Processing, Algorithms, Software Proficiency (e.g., MATLAB, OpenCV)</t>
+          <t>Image Processing;Algorithms;Software Proficiency (e.g.;MATLAB;OpenCV)</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -848,27 +848,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Biotechnology, Healthcare, Pharmaceuticals</t>
+          <t>Biotechnology;Healthcare;Pharmaceuticals</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Bioinformatics Specialist, Research Scientist, Computational Biologist</t>
+          <t>Bioinformatics Specialist;Research Scientist;Computational Biologist</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Drug Development, Molecular Modeling</t>
+          <t>Drug Development;Molecular Modeling</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Biochemistry, Bioinformatics, Computer Science</t>
+          <t>Biochemistry;Bioinformatics;Computer Science</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Molecular Modeling, Visualization Tools (e.g., PyMOL, Chimera)</t>
+          <t>Molecular Modeling;Visualization Tools (e.g.;PyMOL;Chimera)</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -905,27 +905,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Electronics, Consumer Goods, Packaging Industry</t>
+          <t>Electronics;Consumer Goods;Packaging Industry</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Packaging Engineer, Industrial Designer, Product Designer</t>
+          <t>Packaging Engineer;Industrial Designer;Product Designer</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Product Packaging, Electronics, Consumer Goods</t>
+          <t>Product Packaging;Electronics;Consumer Goods</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Engineering, Industrial Design, Materials Science</t>
+          <t>Engineering;Industrial Design;Materials Science</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3D Printing, CAD Tools, Structural Design, Materials Selection</t>
+          <t>3D Printing;CAD Tools;Structural Design;Materials Selection</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -962,27 +962,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Manufacturing, Electronics, Aerospace</t>
+          <t>Manufacturing;Electronics;Aerospace</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Reliability Engineer, Test Engineer, QA Engineer</t>
+          <t>Reliability Engineer;Test Engineer;QA Engineer</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Product Testing, Quality Assurance</t>
+          <t>Product Testing;Quality Assurance</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Electrical Engineering</t>
+          <t>Mechanical Engineering;Electrical Engineering</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Failure Analysis, Statistical Modeling, Stress Testing</t>
+          <t>Failure Analysis;Statistical Modeling;Stress Testing</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Consumer Electronics, Automotive, Aerospace</t>
+          <t>Consumer Electronics;Automotive;Aerospace</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Sensor Design Engineer, Electronics Engineer, Mechatronics Engineer</t>
+          <t>Sensor Design Engineer;Electronics Engineer;Mechatronics Engineer</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Wearables, Automotive Systems, Drones</t>
+          <t>Wearables;Automotive Systems;Drones</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Electrical Engineering, Mechanical Engineering, Physics</t>
+          <t>Electrical Engineering;Mechanical Engineering;Physics</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Sensor Design, Signal Processing, MEMS Technology</t>
+          <t>Sensor Design;Signal Processing;MEMS Technology</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1076,27 +1076,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SaaS, B2B Sales, Marketing, Business Development</t>
+          <t>SaaS;B2B Sales;Marketing;Business Development</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Account Manager, Sales Representative, Business Development Manager</t>
+          <t>Account Manager;Sales Representative;Business Development Manager</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Enterprise Solutions, CRM Systems</t>
+          <t>Enterprise Solutions;CRM Systems</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Business, Marketing, Sales</t>
+          <t>Business;Marketing;Sales</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Relationship Management, Negotiation, Communication, Data Analysis</t>
+          <t>Relationship Management;Negotiation;Communication;Data Analysis</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1133,27 +1133,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Banking, Healthcare, Telecom, Finance</t>
+          <t>Banking;Healthcare;Telecom;Finance</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>IT Specialist, Account Information Manager, Data Analyst</t>
+          <t>IT Specialist;Account Information Manager;Data Analyst</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Data Security, Information Management</t>
+          <t>Data Security;Information Management</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Information Technology, Computer Science</t>
+          <t>Information Technology;Computer Science</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Data Management, Security Protocols, Database Design</t>
+          <t>Data Management;Security Protocols;Database Design</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1190,27 +1190,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Telecommunications, Audio/Video, Consumer Electronics</t>
+          <t>Telecommunications;Audio/Video;Consumer Electronics</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Electronics Engineer, Signal Processing Engineer</t>
+          <t>Electronics Engineer;Signal Processing Engineer</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Audio Devices, Communication Systems</t>
+          <t>Audio Devices;Communication Systems</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Electrical Engineering, Signal Processing</t>
+          <t>Electrical Engineering;Signal Processing</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Analog to Digital Conversion, Signal Processing, Circuit Design</t>
+          <t>Analog to Digital Conversion;Signal Processing;Circuit Design</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1247,27 +1247,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Electronics, Semiconductor, Consumer Goods</t>
+          <t>Electronics;Semiconductor;Consumer Goods</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Packaging Engineer, Process Engineer, Materials Scientist</t>
+          <t>Packaging Engineer;Process Engineer;Materials Scientist</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Microelectronics, Consumer Electronics</t>
+          <t>Microelectronics;Consumer Electronics</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Materials Science</t>
+          <t>Mechanical Engineering;Materials Science</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>3D Modeling, Thermal Management, Structural Integrity</t>
+          <t>3D Modeling;Thermal Management;Structural Integrity</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1304,27 +1304,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Finance, E-commerce, Banking, Cybersecurity</t>
+          <t>Finance;E-commerce;Banking;Cybersecurity</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Data Scientist, AI Engineer, Fraud Analyst</t>
+          <t>Data Scientist;AI Engineer;Fraud Analyst</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Fraud Detection Systems, Security Software</t>
+          <t>Fraud Detection Systems;Security Software</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Computer Science, Data Science, Engineering</t>
+          <t>Computer Science;Data Science;Engineering</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Machine Learning, Pattern Recognition, Data Analytics</t>
+          <t>Machine Learning;Pattern Recognition;Data Analytics</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1361,27 +1361,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Software Development, Machine Learning, Data Science</t>
+          <t>Software Development;Machine Learning;Data Science</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Scientist, Algorithm Engineer</t>
+          <t>Software Engineer;Data Scientist;Algorithm Engineer</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Software Algorithms, Data Processing, AI Models</t>
+          <t>Software Algorithms;Data Processing;AI Models</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Computer Science, Mathematics, Engineering</t>
+          <t>Computer Science;Mathematics;Engineering</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Problem Solving, Optimization, Data Structures, Programming</t>
+          <t>Problem Solving;Optimization;Data Structures;Programming</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1418,27 +1418,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AI, Machine Learning, Social Sciences</t>
+          <t>AI;Machine Learning;Social Sciences</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>AI Researcher, Data Scientist, Ethicist</t>
+          <t>AI Researcher;Data Scientist;Ethicist</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AI Models, Machine Learning Systems</t>
+          <t>AI Models;Machine Learning Systems</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Computer Science, Ethics, Social Science</t>
+          <t>Computer Science;Ethics;Social Science</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Bias Detection, Fairness in AI, Ethical Decision Making</t>
+          <t>Bias Detection;Fairness in AI;Ethical Decision Making</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1475,27 +1475,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AI, Machine Learning, Social Sciences</t>
+          <t>AI;Machine Learning;Social Sciences</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>AI Researcher, Data Scientist, Ethicist, Policy Analyst</t>
+          <t>AI Researcher;Data Scientist;Ethicist;Policy Analyst</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AI Models, Bias Detection Systems</t>
+          <t>AI Models;Bias Detection Systems</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Computer Science, Ethics, Social Science</t>
+          <t>Computer Science;Ethics;Social Science</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Fairness Audits, Algorithmic Evaluation, Bias Metrics</t>
+          <t>Fairness Audits;Algorithmic Evaluation;Bias Metrics</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1532,27 +1532,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Software Development, Research, AI</t>
+          <t>Software Development;Research;AI</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Algorithm Engineer, Data Scientist, Software Engineer</t>
+          <t>Algorithm Engineer;Data Scientist;Software Engineer</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Algorithm Optimization, Complexity Analysis</t>
+          <t>Algorithm Optimization;Complexity Analysis</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Computer Science, Mathematics</t>
+          <t>Computer Science;Mathematics</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Complexity Theory, Algorithmic Design, Data Structures</t>
+          <t>Complexity Theory;Algorithmic Design;Data Structures</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1589,27 +1589,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Software Development, Competitive Programming, AI</t>
+          <t>Software Development;Competitive Programming;AI</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Scientist, Algorithm Developer</t>
+          <t>Software Engineer;Data Scientist;Algorithm Developer</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Coding Competitions, AI Models, Optimization</t>
+          <t>Coding Competitions;AI Models;Optimization</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Computer Science, Mathematics, Engineering</t>
+          <t>Computer Science;Mathematics;Engineering</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Critical Thinking, Logical Reasoning, Programming Skills</t>
+          <t>Critical Thinking;Logical Reasoning;Programming Skills</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1646,27 +1646,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Financial Markets, Hedge Funds, Trading Platforms</t>
+          <t>Financial Markets;Hedge Funds;Trading Platforms</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Quantitative Analyst, Algorithmic Trader, Data Scientist</t>
+          <t>Quantitative Analyst;Algorithmic Trader;Data Scientist</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Trading Algorithms, Financial Models, Market Analytics</t>
+          <t>Trading Algorithms;Financial Models;Market Analytics</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Finance, Computer Science, Mathematics</t>
+          <t>Finance;Computer Science;Mathematics</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Data Analysis, Statistical Modeling, Market Knowledge</t>
+          <t>Data Analysis;Statistical Modeling;Market Knowledge</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1703,27 +1703,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Pharmaceuticals, Biotechnology, Chemical Engineering</t>
+          <t>Pharmaceuticals;Biotechnology;Chemical Engineering</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Data Scientist, Chemoinformatics Specialist, Research Scientist</t>
+          <t>Data Scientist;Chemoinformatics Specialist;Research Scientist</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Chemical Data Models, Drug Discovery Tools</t>
+          <t>Chemical Data Models;Drug Discovery Tools</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Chemistry, Computer Science, Biostatistics</t>
+          <t>Chemistry;Computer Science;Biostatistics</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Chemoinformatics, Pattern Recognition, Statistical Analysis</t>
+          <t>Chemoinformatics;Pattern Recognition;Statistical Analysis</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1760,27 +1760,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Telecommunications, Consumer Electronics, Computing</t>
+          <t>Telecommunications;Consumer Electronics;Computing</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>FPGA Engineer, Hardware Engineer, Embedded Systems Developer</t>
+          <t>FPGA Engineer;Hardware Engineer;Embedded Systems Developer</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Embedded Systems, Hardware Acceleration</t>
+          <t>Embedded Systems;Hardware Acceleration</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Electrical Engineering, Computer Engineering, Physics</t>
+          <t>Electrical Engineering;Computer Engineering;Physics</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>FPGA Programming, Hardware Design, Circuit Design</t>
+          <t>FPGA Programming;Hardware Design;Circuit Design</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1817,27 +1817,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Banking, Finance, Compliance, Security</t>
+          <t>Banking;Finance;Compliance;Security</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Compliance Officer, Risk Analyst, AML Specialist</t>
+          <t>Compliance Officer;Risk Analyst;AML Specialist</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Anti-Money Laundering Systems, Risk Management</t>
+          <t>Anti-Money Laundering Systems;Risk Management</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Finance, Law, Risk Management</t>
+          <t>Finance;Law;Risk Management</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Regulatory Knowledge, Risk Assessment, Investigation Techniques</t>
+          <t>Regulatory Knowledge;Risk Assessment;Investigation Techniques</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1874,27 +1874,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Audio Systems, Telecommunications, Consumer Electronics</t>
+          <t>Audio Systems;Telecommunications;Consumer Electronics</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Electronics Engineer, Audio Engineer, Signal Processing Engineer</t>
+          <t>Electronics Engineer;Audio Engineer;Signal Processing Engineer</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Audio Amplifiers, Communication Systems</t>
+          <t>Audio Amplifiers;Communication Systems</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Electrical Engineering, Audio Engineering</t>
+          <t>Electrical Engineering;Audio Engineering</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Signal Amplification, Circuit Design, Frequency Response</t>
+          <t>Signal Amplification;Circuit Design;Frequency Response</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1931,27 +1931,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Consumer Electronics, Automotive, Telecommunications</t>
+          <t>Consumer Electronics;Automotive;Telecommunications</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Circuit Designer, Electronics Engineer, Embedded Systems Engineer</t>
+          <t>Circuit Designer;Electronics Engineer;Embedded Systems Engineer</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Consumer Electronics, Communication Devices</t>
+          <t>Consumer Electronics;Communication Devices</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Electrical Engineering, Physics, Computer Engineering</t>
+          <t>Electrical Engineering;Physics;Computer Engineering</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Circuit Design, Signal Processing, Mixed-Signal Systems</t>
+          <t>Circuit Design;Signal Processing;Mixed-Signal Systems</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1988,27 +1988,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Consumer Electronics, Telecommunications, Automotive</t>
+          <t>Consumer Electronics;Telecommunications;Automotive</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Circuit Designer, Electronics Engineer, Embedded Systems Engineer</t>
+          <t>Circuit Designer;Electronics Engineer;Embedded Systems Engineer</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Audio Devices, Communication Systems, Consumer Electronics</t>
+          <t>Audio Devices;Communication Systems;Consumer Electronics</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Electrical Engineering, Physics, Computer Engineering</t>
+          <t>Electrical Engineering;Physics;Computer Engineering</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Circuit Design, Signal Integrity, Frequency Response</t>
+          <t>Circuit Design;Signal Integrity;Frequency Response</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2045,27 +2045,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Audio Systems, Communication Systems, Consumer Electronics</t>
+          <t>Audio Systems;Communication Systems;Consumer Electronics</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Electronics Engineer, Signal Processing Engineer, Embedded Systems Developer</t>
+          <t>Electronics Engineer;Signal Processing Engineer;Embedded Systems Developer</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>ADCs, Communication Systems, Consumer Electronics</t>
+          <t>ADCs;Communication Systems;Consumer Electronics</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Electrical Engineering, Physics, Computer Engineering</t>
+          <t>Electrical Engineering;Physics;Computer Engineering</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Analog-to-Digital Conversion, Signal Processing, Data Acquisition</t>
+          <t>Analog-to-Digital Conversion;Signal Processing;Data Acquisition</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2102,27 +2102,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Telecommunications, Aerospace, Consumer Electronics</t>
+          <t>Telecommunications;Aerospace;Consumer Electronics</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>RF Engineer, Antenna Engineer, Communications Systems Engineer</t>
+          <t>RF Engineer;Antenna Engineer;Communications Systems Engineer</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Communication Systems, Wireless Networks</t>
+          <t>Communication Systems;Wireless Networks</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Electrical Engineering, Physics, Telecommunications</t>
+          <t>Electrical Engineering;Physics;Telecommunications</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>RF Design, Antenna Modeling, Wireless Communication</t>
+          <t>RF Design;Antenna Modeling;Wireless Communication</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2159,27 +2159,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Web Development, Cloud Applications, SaaS</t>
+          <t>Web Development;Cloud Applications;SaaS</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>API Engineer, Backend Developer, Cloud Solutions Architect</t>
+          <t>API Engineer;Backend Developer;Cloud Solutions Architect</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Web Applications, Cloud Services, Microservices</t>
+          <t>Web Applications;Cloud Services;Microservices</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Computer Science, Software Engineering, Networking</t>
+          <t>Computer Science;Software Engineering;Networking</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>API Design, Authentication, Load Balancing, Service Integration</t>
+          <t>API Design;Authentication;Load Balancing;Service Integration</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2216,27 +2216,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Web Development, Cloud Computing, SaaS</t>
+          <t>Web Development;Cloud Computing;SaaS</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Security Engineer, API Security Specialist, Backend Developer</t>
+          <t>Security Engineer;API Security Specialist;Backend Developer</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Web Applications, API Security Systems</t>
+          <t>Web Applications;API Security Systems</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Computer Science, Cybersecurity</t>
+          <t>Computer Science;Cybersecurity</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Encryption, Authentication, Access Control, Security Protocols</t>
+          <t>Encryption;Authentication;Access Control;Security Protocols</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2273,27 +2273,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Mobile Apps, Web Apps, Enterprise Software</t>
+          <t>Mobile Apps;Web Apps;Enterprise Software</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Software Developer, Mobile Developer, Full Stack Developer</t>
+          <t>Software Developer;Mobile Developer;Full Stack Developer</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Mobile Applications, Web Platforms</t>
+          <t>Mobile Applications;Web Platforms</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Computer Science, Software Engineering</t>
+          <t>Computer Science;Software Engineering</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Programming, UI/UX Design, Databases, Problem Solving</t>
+          <t>Programming;UI/UX Design;Databases;Problem Solving</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2330,27 +2330,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SaaS, Embedded Systems, Consumer Electronics</t>
+          <t>SaaS;Embedded Systems;Consumer Electronics</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Application Engineer, Software Engineer, Systems Engineer</t>
+          <t>Application Engineer;Software Engineer;Systems Engineer</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Software Applications, Embedded Systems</t>
+          <t>Software Applications;Embedded Systems</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Computer Science, Engineering, Product Design</t>
+          <t>Computer Science;Engineering;Product Design</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Software Design, Debugging, System Integration, User Experience</t>
+          <t>Software Design;Debugging;System Integration;User Experience</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2387,27 +2387,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Healthcare, Business Services, Education</t>
+          <t>Healthcare;Business Services;Education</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Scheduling Software Developer, Operations Coordinator, IT Specialist</t>
+          <t>Scheduling Software Developer;Operations Coordinator;IT Specialist</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Appointment Scheduling Systems, Calendar Apps</t>
+          <t>Appointment Scheduling Systems;Calendar Apps</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Computer Science, Business Administration</t>
+          <t>Computer Science;Business Administration</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Time Management, Database Design, User Interface Design</t>
+          <t>Time Management;Database Design;User Interface Design</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2444,27 +2444,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Machine Learning, Data Science, Operations Research</t>
+          <t>Machine Learning;Data Science;Operations Research</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Algorithm Engineer, Data Scientist, Researcher</t>
+          <t>Algorithm Engineer;Data Scientist;Researcher</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Optimization Problems, Computational Models</t>
+          <t>Optimization Problems;Computational Models</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Computer Science, Mathematics, Operations Research</t>
+          <t>Computer Science;Mathematics;Operations Research</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Algorithm Design, Approximation Techniques, Computational Complexity</t>
+          <t>Algorithm Design;Approximation Techniques;Computational Complexity</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2501,27 +2501,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>AI, Operations Research, Data Science</t>
+          <t>AI;Operations Research;Data Science</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Researcher, Algorithm Developer, Data Scientist</t>
+          <t>Researcher;Algorithm Developer;Data Scientist</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Computational Models, Optimization Algorithms</t>
+          <t>Computational Models;Optimization Algorithms</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Mathematics, Computer Science, Operations Research</t>
+          <t>Mathematics;Computer Science;Operations Research</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Theoretical Analysis, Approximation Methods, Proofs of Bounds</t>
+          <t>Theoretical Analysis;Approximation Methods;Proofs of Bounds</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2558,27 +2558,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Mobile Devices, Embedded Systems, Consumer Electronics</t>
+          <t>Mobile Devices;Embedded Systems;Consumer Electronics</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Embedded Systems Engineer, Hardware Engineer, Firmware Developer</t>
+          <t>Embedded Systems Engineer;Hardware Engineer;Firmware Developer</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Mobile Devices, Embedded Systems</t>
+          <t>Mobile Devices;Embedded Systems</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Electrical Engineering, Computer Engineering</t>
+          <t>Electrical Engineering;Computer Engineering</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>ARM Assembly, Processor Design, Low-Level Programming</t>
+          <t>ARM Assembly;Processor Design;Low-Level Programming</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2615,27 +2615,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Telecommunications, Consumer Electronics, Computing</t>
+          <t>Telecommunications;Consumer Electronics;Computing</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>ASIC Engineer, Hardware Engineer, System-on-Chip (SoC) Designer</t>
+          <t>ASIC Engineer;Hardware Engineer;System-on-Chip (SoC) Designer</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Integrated Circuits, Consumer Electronics</t>
+          <t>Integrated Circuits;Consumer Electronics</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Electrical Engineering, Computer Engineering</t>
+          <t>Electrical Engineering;Computer Engineering</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Circuit Design, Hardware Description Languages, Optimization Techniques</t>
+          <t>Circuit Design;Hardware Description Languages;Optimization Techniques</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2672,27 +2672,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Embedded Systems, Semiconductor Design, Formal Verification</t>
+          <t>Embedded Systems;Semiconductor Design;Formal Verification</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Verification Engineer, Hardware Engineer, Software Tester</t>
+          <t>Verification Engineer;Hardware Engineer;Software Tester</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Design Verification, Testbenches</t>
+          <t>Design Verification;Testbenches</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Electrical Engineering, Computer Science</t>
+          <t>Electrical Engineering;Computer Science</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Formal Methods, Hardware Verification, Test Automation</t>
+          <t>Formal Methods;Hardware Verification;Test Automation</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2729,27 +2729,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Semiconductor Design, Embedded Systems, Software Development</t>
+          <t>Semiconductor Design;Embedded Systems;Software Development</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Verification Engineer, Embedded Systems Engineer, Hardware Engineer</t>
+          <t>Verification Engineer;Embedded Systems Engineer;Hardware Engineer</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Verification Tools, Testbenches, Simulation Models</t>
+          <t>Verification Tools;Testbenches;Simulation Models</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Electrical Engineering, Computer Science, Software Engineering</t>
+          <t>Electrical Engineering;Computer Science;Software Engineering</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Formal Verification, Test Automation, Debugging, Model Checking</t>
+          <t>Formal Verification;Test Automation;Debugging;Model Checking</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -2786,27 +2786,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Hedge Funds, Wealth Management, Financial Planning</t>
+          <t>Hedge Funds;Wealth Management;Financial Planning</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Portfolio Manager, Financial Analyst, Investment Advisor</t>
+          <t>Portfolio Manager;Financial Analyst;Investment Advisor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Investment Portfolios, Risk Management</t>
+          <t>Investment Portfolios;Risk Management</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Finance, Economics, Mathematics</t>
+          <t>Finance;Economics;Mathematics</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Risk Management, Portfolio Diversification, Statistical Analysis</t>
+          <t>Risk Management;Portfolio Diversification;Statistical Analysis</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -2843,27 +2843,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Real Estate, Private Equity, Public Markets</t>
+          <t>Real Estate;Private Equity;Public Markets</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Valuation Analyst, Financial Analyst, Real Estate Appraiser</t>
+          <t>Valuation Analyst;Financial Analyst;Real Estate Appraiser</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Investment Valuation, Property Valuation</t>
+          <t>Investment Valuation;Property Valuation</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Finance, Economics, Real Estate</t>
+          <t>Finance;Economics;Real Estate</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Market Analysis, Discounted Cash Flow, Comparable Analysis</t>
+          <t>Market Analysis;Discounted Cash Flow;Comparable Analysis</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -2900,27 +2900,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Research, Education, Space Exploration</t>
+          <t>Research;Education;Space Exploration</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Astronomer, Astrophysicist, Research Scientist</t>
+          <t>Astronomer;Astrophysicist;Research Scientist</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Space Research, Telescopes, Space Missions</t>
+          <t>Space Research;Telescopes;Space Missions</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Physics, Astronomy, Mathematics</t>
+          <t>Physics;Astronomy;Mathematics</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Celestial Observation, Telescope Operation, Research Methods</t>
+          <t>Celestial Observation;Telescope Operation;Research Methods</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -2957,27 +2957,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Space Research, Data Science, Astrophysics</t>
+          <t>Space Research;Data Science;Astrophysics</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Data Scientist, Researcher, Software Developer</t>
+          <t>Data Scientist;Researcher;Software Developer</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Space Observations, Data Analysis</t>
+          <t>Space Observations;Data Analysis</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Computer Science, Astronomy, Data Science</t>
+          <t>Computer Science;Astronomy;Data Science</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Data Parsing, Format Conversion, Data Storage Systems</t>
+          <t>Data Parsing;Format Conversion;Data Storage Systems</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3014,27 +3014,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Space Research, Simulation, Education</t>
+          <t>Space Research;Simulation;Education</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Astrophysicist, Computational Scientist, Researcher</t>
+          <t>Astrophysicist;Computational Scientist;Researcher</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Space Simulations, Astrophysical Models</t>
+          <t>Space Simulations;Astrophysical Models</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Physics, Mathematics, Computer Science</t>
+          <t>Physics;Mathematics;Computer Science</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Numerical Simulation, Mathematical Modeling, Computational Physics</t>
+          <t>Numerical Simulation;Mathematical Modeling;Computational Physics</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3071,27 +3071,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Research, Space Science, Simulations</t>
+          <t>Research;Space Science;Simulations</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Astrophysicist, Simulation Specialist, Research Scientist</t>
+          <t>Astrophysicist;Simulation Specialist;Research Scientist</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Computational Models, Simulation Software</t>
+          <t>Computational Models;Simulation Software</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Physics, Computer Science, Mathematics</t>
+          <t>Physics;Computer Science;Mathematics</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Simulation Software, Numerical Methods, High-Performance Computing</t>
+          <t>Simulation Software;Numerical Methods;High-Performance Computing</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3128,27 +3128,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Research, Education, Space Exploration</t>
+          <t>Research;Education;Space Exploration</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Astrophysicist, Research Scientist, Educator</t>
+          <t>Astrophysicist;Research Scientist;Educator</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Space Research, Scientific Discoveries</t>
+          <t>Space Research;Scientific Discoveries</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Physics, Mathematics, Astronomy</t>
+          <t>Physics;Mathematics;Astronomy</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Theoretical Physics, Research, Data Analysis, Observation Methods</t>
+          <t>Theoretical Physics;Research;Data Analysis;Observation Methods</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3185,27 +3185,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Electronics Manufacturing, Aerospace, Automotive</t>
+          <t>Electronics Manufacturing;Aerospace;Automotive</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Test Engineer, ATE Engineer, Electronics Engineer</t>
+          <t>Test Engineer;ATE Engineer;Electronics Engineer</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Testing Systems, Electronics Validation</t>
+          <t>Testing Systems;Electronics Validation</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Electrical Engineering, Computer Science, Physics</t>
+          <t>Electrical Engineering;Computer Science;Physics</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Test Automation, Hardware Testing, Software Integration</t>
+          <t>Test Automation;Hardware Testing;Software Integration</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3242,27 +3242,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Manufacturing, Aerospace, Electronics Repair</t>
+          <t>Manufacturing;Aerospace;Electronics Repair</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Maintenance Technician, ATE Engineer, Repair Specialist</t>
+          <t>Maintenance Technician;ATE Engineer;Repair Specialist</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Test Equipment, Circuit Boards, Diagnostic Systems</t>
+          <t>Test Equipment;Circuit Boards;Diagnostic Systems</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Electrical Engineering, Mechanical Engineering</t>
+          <t>Electrical Engineering;Mechanical Engineering</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Troubleshooting, Maintenance Protocols, Diagnostics</t>
+          <t>Troubleshooting;Maintenance Protocols;Diagnostics</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3299,27 +3299,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Meteorology, Climate Science, Aerospace</t>
+          <t>Meteorology;Climate Science;Aerospace</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Atmospheric Scientist, Meteorologist, Climate Modeler</t>
+          <t>Atmospheric Scientist;Meteorologist;Climate Modeler</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Weather Forecasting, Climate Simulations</t>
+          <t>Weather Forecasting;Climate Simulations</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Environmental Science, Atmospheric Science, Physics</t>
+          <t>Environmental Science;Atmospheric Science;Physics</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Numerical Weather Prediction, Data Assimilation, Climate Modeling</t>
+          <t>Numerical Weather Prediction;Data Assimilation;Climate Modeling</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3356,27 +3356,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Finance, Healthcare, Government, Corporate</t>
+          <t>Finance;Healthcare;Government;Corporate</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Audit Manager, Audit Coordinator, Compliance Officer</t>
+          <t>Audit Manager;Audit Coordinator;Compliance Officer</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Audit Processes, Risk Management</t>
+          <t>Audit Processes;Risk Management</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Business Administration, Finance, Accounting</t>
+          <t>Business Administration;Finance;Accounting</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Coordination, Risk Assessment, Documentation, Regulatory Knowledge</t>
+          <t>Coordination;Risk Assessment;Documentation;Regulatory Knowledge</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3413,27 +3413,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Finance, Government, Healthcare, Corporate</t>
+          <t>Finance;Government;Healthcare;Corporate</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Auditor, Risk Analyst, Compliance Specialist</t>
+          <t>Auditor;Risk Analyst;Compliance Specialist</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Audit Processes, Compliance Testing</t>
+          <t>Audit Processes;Compliance Testing</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Accounting, Finance, Business Administration</t>
+          <t>Accounting;Finance;Business Administration</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Internal Control Frameworks, Risk Assessment, Regulatory Knowledge</t>
+          <t>Internal Control Frameworks;Risk Assessment;Regulatory Knowledge</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3470,27 +3470,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Web Development, Cloud Computing, IT Security</t>
+          <t>Web Development;Cloud Computing;IT Security</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Security Engineer, Network Engineer, Cybersecurity Analyst</t>
+          <t>Security Engineer;Network Engineer;Cybersecurity Analyst</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Security Systems, Cloud Authentication</t>
+          <t>Security Systems;Cloud Authentication</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Computer Science, Network Engineering, Cybersecurity</t>
+          <t>Computer Science;Network Engineering;Cybersecurity</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Encryption, Access Control, Protocol Analysis, Identity Management</t>
+          <t>Encryption;Access Control;Protocol Analysis;Identity Management</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3527,27 +3527,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Manufacturing, Automotive, Consumer Electronics</t>
+          <t>Manufacturing;Automotive;Consumer Electronics</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Automation Engineer, Robotics Engineer, Manufacturing Engineer</t>
+          <t>Automation Engineer;Robotics Engineer;Manufacturing Engineer</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Production Lines, Robotics Systems</t>
+          <t>Production Lines;Robotics Systems</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Electrical Engineering</t>
+          <t>Mechanical Engineering;Electrical Engineering</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Robotics, Process Optimization, Mechatronics, System Integration</t>
+          <t>Robotics;Process Optimization;Mechatronics;System Integration</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -3584,27 +3584,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Electronics Manufacturing, Aerospace, Automotive</t>
+          <t>Electronics Manufacturing;Aerospace;Automotive</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Test Engineer, ATE Engineer, Electronics Engineer</t>
+          <t>Test Engineer;ATE Engineer;Electronics Engineer</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Testing Systems, Circuit Boards, Validation</t>
+          <t>Testing Systems;Circuit Boards;Validation</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Electrical Engineering, Computer Science, Physics</t>
+          <t>Electrical Engineering;Computer Science;Physics</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Test Automation, Hardware Testing, Software Integration</t>
+          <t>Test Automation;Hardware Testing;Software Integration</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -3641,27 +3641,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Manufacturing, Automotive, Energy, Aerospace</t>
+          <t>Manufacturing;Automotive;Energy;Aerospace</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Automation Engineer, Robotics Engineer, System Integrator</t>
+          <t>Automation Engineer;Robotics Engineer;System Integrator</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Automated Production Lines, Robotics, Control Systems</t>
+          <t>Automated Production Lines;Robotics;Control Systems</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Electrical Engineering</t>
+          <t>Mechanical Engineering;Electrical Engineering</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Robotics, Control Theory, System Design, Automation Technology</t>
+          <t>Robotics;Control Theory;System Design;Automation Technology</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -3698,27 +3698,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>IT, Software Development, Manufacturing</t>
+          <t>IT;Software Development;Manufacturing</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Automation Developer, Software Engineer, Tools Specialist</t>
+          <t>Automation Developer;Software Engineer;Tools Specialist</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Testing Tools, Automation Frameworks</t>
+          <t>Testing Tools;Automation Frameworks</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Computer Science, Software Engineering</t>
+          <t>Computer Science;Software Engineering</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Scripting, Process Automation, Tool Development, Integration</t>
+          <t>Scripting;Process Automation;Tool Development;Integration</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -3755,27 +3755,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Automotive Manufacturing, Automotive Design</t>
+          <t>Automotive Manufacturing;Automotive Design</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Safety Engineer, Regulatory Compliance Officer, Automotive Engineer</t>
+          <t>Safety Engineer;Regulatory Compliance Officer;Automotive Engineer</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Vehicle Safety Systems, Compliance Testing</t>
+          <t>Vehicle Safety Systems;Compliance Testing</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Automotive Engineering, Law</t>
+          <t>Mechanical Engineering;Automotive Engineering;Law</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Safety Protocols, Regulatory Standards, Vehicle Testing</t>
+          <t>Safety Protocols;Regulatory Standards;Vehicle Testing</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -3812,27 +3812,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Automotive Design, Automotive Manufacturing</t>
+          <t>Automotive Design;Automotive Manufacturing</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Automotive Engineer, Systems Engineer, Electronics Engineer</t>
+          <t>Automotive Engineer;Systems Engineer;Electronics Engineer</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Automotive Components, Infotainment Systems</t>
+          <t>Automotive Components;Infotainment Systems</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Electrical Engineering, Automotive Technology</t>
+          <t>Mechanical Engineering;Electrical Engineering;Automotive Technology</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Systems Design, Integration, Embedded Systems, Diagnostics</t>
+          <t>Systems Design;Integration;Embedded Systems;Diagnostics</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -3869,27 +3869,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Automotive Manufacturing, Research, Development</t>
+          <t>Automotive Manufacturing;Research;Development</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Test Engineer, Automotive Engineer, Quality Assurance Specialist</t>
+          <t>Test Engineer;Automotive Engineer;Quality Assurance Specialist</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Vehicle Testing, Crash Simulation, Performance Evaluation</t>
+          <t>Vehicle Testing;Crash Simulation;Performance Evaluation</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Automotive Engineering, Testing Methods</t>
+          <t>Mechanical Engineering;Automotive Engineering;Testing Methods</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Vehicle Diagnostics, Performance Testing, Safety Standards</t>
+          <t>Vehicle Diagnostics;Performance Testing;Safety Standards</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -3926,27 +3926,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Robotics, Autonomous Vehicles, Aerospace</t>
+          <t>Robotics;Autonomous Vehicles;Aerospace</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Robotics Engineer, Autonomous Vehicle Engineer, AI Specialist</t>
+          <t>Robotics Engineer;Autonomous Vehicle Engineer;AI Specialist</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Self-Driving Cars, Drones, Robotic Systems</t>
+          <t>Self-Driving Cars;Drones;Robotic Systems</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Robotics, Computer Science, Electrical Engineering</t>
+          <t>Robotics;Computer Science;Electrical Engineering</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Machine Learning, Sensor Integration, System Design, Path Planning</t>
+          <t>Machine Learning;Sensor Integration;System Design;Path Planning</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -3983,27 +3983,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Trading, Investment, Financial Planning</t>
+          <t>Trading;Investment;Financial Planning</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Quantitative Analyst, Algorithmic Trader, Data Scientist</t>
+          <t>Quantitative Analyst;Algorithmic Trader;Data Scientist</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Financial Models, Trading Strategies</t>
+          <t>Financial Models;Trading Strategies</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Finance, Economics, Data Science</t>
+          <t>Finance;Economics;Data Science</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Statistical Modeling, Risk Management, Performance Evaluation</t>
+          <t>Statistical Modeling;Risk Management;Performance Evaluation</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4040,27 +4040,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Banking, Fintech, Payment Systems</t>
+          <t>Banking;Fintech;Payment Systems</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Integration Specialist, Banking Software Engineer, IT Specialist</t>
+          <t>Integration Specialist;Banking Software Engineer;IT Specialist</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Core Banking Systems, Payment Gateways</t>
+          <t>Core Banking Systems;Payment Gateways</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Computer Science, Finance, Software Engineering</t>
+          <t>Computer Science;Finance;Software Engineering</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>API Integration, Security, System Interoperability</t>
+          <t>API Integration;Security;System Interoperability</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4097,27 +4097,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Banking, Fintech, Payment Systems</t>
+          <t>Banking;Fintech;Payment Systems</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Software Engineer, Banking Systems Architect, Fintech Developer</t>
+          <t>Software Engineer;Banking Systems Architect;Fintech Developer</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Banking Applications, Payment Systems</t>
+          <t>Banking Applications;Payment Systems</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Computer Science, Finance, Software Engineering</t>
+          <t>Computer Science;Finance;Software Engineering</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Financial Software Development, Security, UX/UI Design</t>
+          <t>Financial Software Development;Security;UX/UI Design</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4154,27 +4154,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Fintech, Digital Banking</t>
+          <t>Fintech;Digital Banking</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>SaaS Architect, Fintech Developer, Business Development Manager</t>
+          <t>SaaS Architect;Fintech Developer;Business Development Manager</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Digital Banking Platforms, Financial Services</t>
+          <t>Digital Banking Platforms;Financial Services</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Business Administration, Software Engineering, Finance</t>
+          <t>Business Administration;Software Engineering;Finance</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Cloud Solutions, API Development, Regulatory Compliance</t>
+          <t>Cloud Solutions;API Development;Regulatory Compliance</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4211,27 +4211,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Electric Vehicles, Renewable Energy, Consumer Electronics</t>
+          <t>Electric Vehicles;Renewable Energy;Consumer Electronics</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Battery Systems Engineer, Electrical Engineer, Energy Consultant</t>
+          <t>Battery Systems Engineer;Electrical Engineer;Energy Consultant</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Electric Vehicle Batteries, Solar Power Systems</t>
+          <t>Electric Vehicle Batteries;Solar Power Systems</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Electrical Engineering, Energy Systems, Computer Science</t>
+          <t>Electrical Engineering;Energy Systems;Computer Science</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Battery Charging, Energy Storage, Power Management</t>
+          <t>Battery Charging;Energy Storage;Power Management</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4268,27 +4268,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>E-commerce, Marketing, Consumer Behavior Research</t>
+          <t>E-commerce;Marketing;Consumer Behavior Research</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Data Scientist, Behavioral Analyst, Marketing Specialist</t>
+          <t>Data Scientist;Behavioral Analyst;Marketing Specialist</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Customer Insights, Behavioral Data Models</t>
+          <t>Customer Insights;Behavioral Data Models</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Data Science, Psychology, Marketing</t>
+          <t>Data Science;Psychology;Marketing</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Pattern Recognition, Customer Segmentation, Predictive Modeling</t>
+          <t>Pattern Recognition;Customer Segmentation;Predictive Modeling</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -4325,27 +4325,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Healthcare, Pharmaceuticals, Biotechnology</t>
+          <t>Healthcare;Pharmaceuticals;Biotechnology</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Bioinformatician, Computational Biologist, Research Scientist</t>
+          <t>Bioinformatician;Computational Biologist;Research Scientist</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Genomic Data Analysis, Healthcare Research</t>
+          <t>Genomic Data Analysis;Healthcare Research</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Biology, Computer Science, Data Science</t>
+          <t>Biology;Computer Science;Data Science</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Genomic Data Analysis, Statistical Methods, Molecular Biology</t>
+          <t>Genomic Data Analysis;Statistical Methods;Molecular Biology</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -4382,27 +4382,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Healthcare, Pharmaceuticals, Biotechnology</t>
+          <t>Healthcare;Pharmaceuticals;Biotechnology</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Computational Biologist, Bioinformatics Researcher, Data Scientist</t>
+          <t>Computational Biologist;Bioinformatics Researcher;Data Scientist</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Genomic Research, Drug Discovery Tools</t>
+          <t>Genomic Research;Drug Discovery Tools</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Computer Science, Biology, Mathematics</t>
+          <t>Computer Science;Biology;Mathematics</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Algorithm Development, Machine Learning, Data Analysis</t>
+          <t>Algorithm Development;Machine Learning;Data Analysis</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -4439,27 +4439,27 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Healthcare, Pharmaceuticals, Research</t>
+          <t>Healthcare;Pharmaceuticals;Research</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Bioinformatics Database Administrator, Data Scientist, Researcher</t>
+          <t>Bioinformatics Database Administrator;Data Scientist;Researcher</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Genomic Databases, Medical Data Repositories</t>
+          <t>Genomic Databases;Medical Data Repositories</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Computer Science, Biology, Data Science</t>
+          <t>Computer Science;Biology;Data Science</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Database Design, Data Mining, Genomic Data Management</t>
+          <t>Database Design;Data Mining;Genomic Data Management</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -4496,27 +4496,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Healthcare, Pharmaceuticals, Research</t>
+          <t>Healthcare;Pharmaceuticals;Research</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Bioinformatics Specialist, Data Scientist, Computational Biologist</t>
+          <t>Bioinformatics Specialist;Data Scientist;Computational Biologist</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Genomic Research, Medical Data Analysis</t>
+          <t>Genomic Research;Medical Data Analysis</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Computer Science, Biology, Data Science</t>
+          <t>Computer Science;Biology;Data Science</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Tool Development, Data Analysis, Genomic Data Processing</t>
+          <t>Tool Development;Data Analysis;Genomic Data Processing</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -4553,27 +4553,27 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Healthcare, Biotechnology, Research</t>
+          <t>Healthcare;Biotechnology;Research</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Data Integration Specialist, Bioinformatics Analyst, Researcher</t>
+          <t>Data Integration Specialist;Bioinformatics Analyst;Researcher</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Genomic Data Integration, Medical Records</t>
+          <t>Genomic Data Integration;Medical Records</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Computer Science, Biology, Data Science</t>
+          <t>Computer Science;Biology;Data Science</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Data Merging, Multi-Source Integration, Biological Data Analysis</t>
+          <t>Data Merging;Multi-Source Integration;Biological Data Analysis</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -4610,27 +4610,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Healthcare, Research, Biotechnology</t>
+          <t>Healthcare;Research;Biotechnology</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Database Administrator, Bioinformatics Data Manager, Research Scientist</t>
+          <t>Database Administrator;Bioinformatics Data Manager;Research Scientist</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Medical Data Repositories, Genomic Databases</t>
+          <t>Medical Data Repositories;Genomic Databases</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Computer Science, Biology, Data Management</t>
+          <t>Computer Science;Biology;Data Management</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Database Design, Data Storage, Genomic Data Management</t>
+          <t>Database Design;Data Storage;Genomic Data Management</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -4667,27 +4667,27 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Healthcare, Pharmaceuticals, Research</t>
+          <t>Healthcare;Pharmaceuticals;Research</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Bioinformatics Specialist, Database Administrator, Researcher</t>
+          <t>Bioinformatics Specialist;Database Administrator;Researcher</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Genomic Databases, Medical Data Repositories</t>
+          <t>Genomic Databases;Medical Data Repositories</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Computer Science, Biology, Data Science</t>
+          <t>Computer Science;Biology;Data Science</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Data Organization, Data Mining, Bioinformatics Analysis</t>
+          <t>Data Organization;Data Mining;Bioinformatics Analysis</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -4724,27 +4724,27 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Healthcare, Research, Pharmaceuticals</t>
+          <t>Healthcare;Research;Pharmaceuticals</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Bioinformatics Network Analyst, Systems Biologist, Researcher</t>
+          <t>Bioinformatics Network Analyst;Systems Biologist;Researcher</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Protein Interaction Networks, Biological Models</t>
+          <t>Protein Interaction Networks;Biological Models</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Biology, Computer Science, Data Science</t>
+          <t>Biology;Computer Science;Data Science</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Network Analysis, Systems Biology, Data Modeling</t>
+          <t>Network Analysis;Systems Biology;Data Modeling</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -4781,27 +4781,27 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Finance, Technology, Supply Chain</t>
+          <t>Finance;Technology;Supply Chain</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Blockchain Developer, Cryptography Engineer, Software Engineer</t>
+          <t>Blockchain Developer;Cryptography Engineer;Software Engineer</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Cryptocurrencies, Distributed Ledgers</t>
+          <t>Cryptocurrencies;Distributed Ledgers</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Computer Science, Cryptography, Mathematics</t>
+          <t>Computer Science;Cryptography;Mathematics</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Blockchain Development, Smart Contracts, Security Protocols</t>
+          <t>Blockchain Development;Smart Contracts;Security Protocols</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -4838,27 +4838,27 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Finance, Compliance, Legal, Technology</t>
+          <t>Finance;Compliance;Legal;Technology</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Compliance Engineer, Blockchain Consultant, Regulatory Analyst</t>
+          <t>Compliance Engineer;Blockchain Consultant;Regulatory Analyst</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Regulatory Compliance, Smart Contracts</t>
+          <t>Regulatory Compliance;Smart Contracts</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Computer Science, Law, Business Administration</t>
+          <t>Computer Science;Law;Business Administration</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Regulatory Frameworks, Smart Contract Development, Auditing</t>
+          <t>Regulatory Frameworks;Smart Contract Development;Auditing</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -4895,27 +4895,27 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Finance, Cybersecurity, Banking</t>
+          <t>Finance;Cybersecurity;Banking</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Blockchain Developer, Fraud Analyst, Security Specialist</t>
+          <t>Blockchain Developer;Fraud Analyst;Security Specialist</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Fraud Prevention, Transaction Monitoring</t>
+          <t>Fraud Prevention;Transaction Monitoring</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Computer Science, Cybersecurity, Finance</t>
+          <t>Computer Science;Cybersecurity;Finance</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Transaction Analysis, Fraud Prevention, Blockchain Security</t>
+          <t>Transaction Analysis;Fraud Prevention;Blockchain Security</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -4952,27 +4952,27 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Finance, Technology, Supply Chain</t>
+          <t>Finance;Technology;Supply Chain</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Blockchain Integration Specialist, Software Engineer</t>
+          <t>Blockchain Integration Specialist;Software Engineer</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Blockchain Solutions, Legacy System Integration</t>
+          <t>Blockchain Solutions;Legacy System Integration</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Computer Science, Engineering, Business Administration</t>
+          <t>Computer Science;Engineering;Business Administration</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>System Integration, Blockchain APIs, Software Development</t>
+          <t>System Integration;Blockchain APIs;Software Development</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5009,27 +5009,27 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Finance, Technology, Decentralized Applications</t>
+          <t>Finance;Technology;Decentralized Applications</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Blockchain Developer, Platform Engineer, Technical Architect</t>
+          <t>Blockchain Developer;Platform Engineer;Technical Architect</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Blockchain Networks, Decentralized Apps</t>
+          <t>Blockchain Networks;Decentralized Apps</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Computer Science, Engineering, Mathematics</t>
+          <t>Computer Science;Engineering;Mathematics</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Blockchain Development, Network Design, Platform Architecture</t>
+          <t>Blockchain Development;Network Design;Platform Architecture</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -5066,27 +5066,27 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Finance, Technology, Cryptocurrency</t>
+          <t>Finance;Technology;Cryptocurrency</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Blockchain Engineer, Distributed Systems Architect, Solutions Architect</t>
+          <t>Blockchain Engineer;Distributed Systems Architect;Solutions Architect</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Blockchain Networks, Cryptocurrencies</t>
+          <t>Blockchain Networks;Cryptocurrencies</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Computer Science, Cryptography, Mathematics</t>
+          <t>Computer Science;Cryptography;Mathematics</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Network Optimization, Consensus Algorithms, Scaling Solutions</t>
+          <t>Network Optimization;Consensus Algorithms;Scaling Solutions</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -5123,27 +5123,27 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Finance, Technology, Cryptocurrency</t>
+          <t>Finance;Technology;Cryptocurrency</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Blockchain Security Engineer, Security Analyst, Cryptography Expert</t>
+          <t>Blockchain Security Engineer;Security Analyst;Cryptography Expert</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Secure Transactions, Smart Contracts</t>
+          <t>Secure Transactions;Smart Contracts</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Computer Science, Cryptography, Cybersecurity</t>
+          <t>Computer Science;Cryptography;Cybersecurity</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Encryption, Threat Detection, Security Auditing, Penetration Testing</t>
+          <t>Encryption;Threat Detection;Security Auditing;Penetration Testing</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -5180,27 +5180,27 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Electronics Manufacturing, Hardware Development</t>
+          <t>Electronics Manufacturing;Hardware Development</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Hardware Engineer, Embedded Systems Engineer, Debugging Specialist</t>
+          <t>Hardware Engineer;Embedded Systems Engineer;Debugging Specialist</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Circuit Debugging, Microcontrollers</t>
+          <t>Circuit Debugging;Microcontrollers</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Electrical Engineering, Computer Science</t>
+          <t>Electrical Engineering;Computer Science</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Signal Testing, Circuit Troubleshooting, Debugging Techniques</t>
+          <t>Signal Testing;Circuit Troubleshooting;Debugging Techniques</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -5237,27 +5237,27 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Consumer Electronics, Telecommunications, Automotive</t>
+          <t>Consumer Electronics;Telecommunications;Automotive</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Hardware Engineer, PCB Designer, Electronics Designer</t>
+          <t>Hardware Engineer;PCB Designer;Electronics Designer</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>PCB Design, Embedded Systems</t>
+          <t>PCB Design;Embedded Systems</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Electrical Engineering, Computer Engineering</t>
+          <t>Electrical Engineering;Computer Engineering</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Schematic Design, Signal Integrity, PCB Layout</t>
+          <t>Schematic Design;Signal Integrity;PCB Layout</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -5294,27 +5294,27 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturing, Electronics Assembly</t>
+          <t>Semiconductor Manufacturing;Electronics Assembly</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Process Engineer, Materials Scientist, Electronics Engineer</t>
+          <t>Process Engineer;Materials Scientist;Electronics Engineer</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Semiconductor Devices, Microelectronics</t>
+          <t>Semiconductor Devices;Microelectronics</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Materials Science, Electrical Engineering</t>
+          <t>Materials Science;Electrical Engineering</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Bonding Techniques, Adhesive Application, Surface Interaction</t>
+          <t>Bonding Techniques;Adhesive Application;Surface Interaction</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -5351,27 +5351,27 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Firmware Development, Electronics, Automotive</t>
+          <t>Firmware Development;Electronics;Automotive</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Firmware Engineer, Embedded Systems Developer, Bootloader Engineer</t>
+          <t>Firmware Engineer;Embedded Systems Developer;Bootloader Engineer</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Bootloading Software, Embedded Systems</t>
+          <t>Bootloading Software;Embedded Systems</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Computer Science, Electrical Engineering</t>
+          <t>Computer Science;Electrical Engineering</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Firmware Programming, System Initialization, Low-Level Debugging</t>
+          <t>Firmware Programming;System Initialization;Low-Level Debugging</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -5408,27 +5408,27 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Healthcare, AI Research, Cognitive Science</t>
+          <t>Healthcare;AI Research;Cognitive Science</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Neuroscientist, AI Researcher, Cognitive Systems Engineer</t>
+          <t>Neuroscientist;AI Researcher;Cognitive Systems Engineer</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Neural Networks, Brain Simulation</t>
+          <t>Neural Networks;Brain Simulation</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Neuroscience, AI, Computer Science</t>
+          <t>Neuroscience;AI;Computer Science</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Neural Connectivity, Computational Neuroscience, Brain Mapping</t>
+          <t>Neural Connectivity;Computational Neuroscience;Brain Mapping</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -5465,27 +5465,27 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Healthcare, Cognitive Science, AI Research</t>
+          <t>Healthcare;Cognitive Science;AI Research</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Neuroscientist, Simulation Scientist, Computational Neuroscientist</t>
+          <t>Neuroscientist;Simulation Scientist;Computational Neuroscientist</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Brain Models, Cognitive Simulations</t>
+          <t>Brain Models;Cognitive Simulations</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Neuroscience, AI, Computer Science</t>
+          <t>Neuroscience;AI;Computer Science</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Neural Simulation, Cognitive Modeling, Brain Network Analysis</t>
+          <t>Neural Simulation;Cognitive Modeling;Brain Network Analysis</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -5522,27 +5522,27 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Consumer Goods, Digital Marketing, Retail</t>
+          <t>Consumer Goods;Digital Marketing;Retail</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Brand Manager, Marketing Director, Digital Marketing Specialist</t>
+          <t>Brand Manager;Marketing Director;Digital Marketing Specialist</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Brand Strategy, Marketing Campaigns</t>
+          <t>Brand Strategy;Marketing Campaigns</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Marketing, Business Administration, Communications</t>
+          <t>Marketing;Business Administration;Communications</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Market Research, Content Creation, Audience Engagement</t>
+          <t>Market Research;Content Creation;Audience Engagement</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -5579,27 +5579,27 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Advertising, Retail, Consumer Goods</t>
+          <t>Advertising;Retail;Consumer Goods</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Brand Strategist, Marketing Manager, Product Manager</t>
+          <t>Brand Strategist;Marketing Manager;Product Manager</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Brand Positioning, Product Identity</t>
+          <t>Brand Positioning;Product Identity</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Marketing, Business Administration, Communications</t>
+          <t>Marketing;Business Administration;Communications</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Brand Strategy, Customer Insights, Competitive Analysis</t>
+          <t>Brand Strategy;Customer Insights;Competitive Analysis</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -5636,27 +5636,27 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Electronics, Manufacturing, Automotive</t>
+          <t>Electronics;Manufacturing;Automotive</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Test Engineer, QA Engineer, Manufacturing Specialist</t>
+          <t>Test Engineer;QA Engineer;Manufacturing Specialist</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Product Testing, Reliability Evaluation</t>
+          <t>Product Testing;Reliability Evaluation</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Electrical Engineering, Mechanical Engineering</t>
+          <t>Electrical Engineering;Mechanical Engineering</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Stress Testing, System Testing, Failure Prediction</t>
+          <t>Stress Testing;System Testing;Failure Prediction</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -5693,27 +5693,27 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Electronics, Computer Science, Embedded Systems</t>
+          <t>Electronics;Computer Science;Embedded Systems</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Systems Architect, Hardware Engineer, Embedded Systems Designer</t>
+          <t>Systems Architect;Hardware Engineer;Embedded Systems Designer</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Computer Systems, Microprocessor Design</t>
+          <t>Computer Systems;Microprocessor Design</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Computer Engineering, Electrical Engineering</t>
+          <t>Computer Engineering;Electrical Engineering</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Data Transfer Optimization, Hardware Design, System Architecture</t>
+          <t>Data Transfer Optimization;Hardware Design;System Architecture</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -5750,27 +5750,27 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>IT, Healthcare, Corporate, Government</t>
+          <t>IT;Healthcare;Corporate;Government</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Business Continuity Planner, Risk Manager, Operations Manager</t>
+          <t>Business Continuity Planner;Risk Manager;Operations Manager</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Continuity Plans, Disaster Recovery</t>
+          <t>Continuity Plans;Disaster Recovery</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Business Administration, Risk Management, IT Management</t>
+          <t>Business Administration;Risk Management;IT Management</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Crisis Management, Risk Analysis, Strategic Planning</t>
+          <t>Crisis Management;Risk Analysis;Strategic Planning</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -5807,27 +5807,27 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Software Development, Embedded Systems</t>
+          <t>Software Development;Embedded Systems</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Software Developer, Embedded Systems Engineer, Programmer</t>
+          <t>Software Developer;Embedded Systems Engineer;Programmer</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Applications, Firmware, Systems Software</t>
+          <t>Applications;Firmware;Systems Software</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Computer Science, Software Engineering</t>
+          <t>Computer Science;Software Engineering</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Algorithm Development, Memory Management, System-Level Programming</t>
+          <t>Algorithm Development;Memory Management;System-Level Programming</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -5864,27 +5864,27 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Software Development, Embedded Systems, Game Development</t>
+          <t>Software Development;Embedded Systems;Game Development</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Software Developer, Game Developer, Systems Programmer</t>
+          <t>Software Developer;Game Developer;Systems Programmer</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Applications, Game Engines, Systems Software</t>
+          <t>Applications;Game Engines;Systems Software</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Computer Science, Software Engineering</t>
+          <t>Computer Science;Software Engineering</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Memory Management, Object-Oriented Programming, Multi-threading</t>
+          <t>Memory Management;Object-Oriented Programming;Multi-threading</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -5921,27 +5921,27 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>High-Performance Computing, Embedded Systems</t>
+          <t>High-Performance Computing;Embedded Systems</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>HPC Developer, Embedded Systems Engineer, Programmer</t>
+          <t>HPC Developer;Embedded Systems Engineer;Programmer</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Simulation Software, Scientific Applications</t>
+          <t>Simulation Software;Scientific Applications</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Computer Science, Engineering, Computational Science</t>
+          <t>Computer Science;Engineering;Computational Science</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Numerical Methods, Performance Optimization, Parallel Programming</t>
+          <t>Numerical Methods;Performance Optimization;Parallel Programming</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -5978,27 +5978,27 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Software Development, Data Science, Game Development</t>
+          <t>Software Development;Data Science;Game Development</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Software Developer, Data Scientist, Game Programmer</t>
+          <t>Software Developer;Data Scientist;Game Programmer</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Applications, Data Analysis, Game Development</t>
+          <t>Applications;Data Analysis;Game Development</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Computer Science, Software Engineering, Data Science</t>
+          <t>Computer Science;Software Engineering;Data Science</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Object-Oriented Programming, Algorithm Design, Data Structures</t>
+          <t>Object-Oriented Programming;Algorithm Design;Data Structures</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -6035,27 +6035,27 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Software Development, Web Development, Mobile Apps</t>
+          <t>Software Development;Web Development;Mobile Apps</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Software Developer, Mobile App Developer, Web Developer</t>
+          <t>Software Developer;Mobile App Developer;Web Developer</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Applications, Web Apps, Mobile Apps</t>
+          <t>Applications;Web Apps;Mobile Apps</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Computer Science, Software Engineering</t>
+          <t>Computer Science;Software Engineering</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Object-Oriented Programming, Cross-platform Development, Web Development</t>
+          <t>Object-Oriented Programming;Cross-platform Development;Web Development</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -6092,27 +6092,27 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Software Development, Data Science, Web Development</t>
+          <t>Software Development;Data Science;Web Development</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Software Developer, Data Scientist, Web Developer</t>
+          <t>Software Developer;Data Scientist;Web Developer</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Applications, Data Analysis, Web Development</t>
+          <t>Applications;Data Analysis;Web Development</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Computer Science, Software Engineering, Data Science</t>
+          <t>Computer Science;Software Engineering;Data Science</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Object-Oriented Programming, Full-stack Development, Data Structures</t>
+          <t>Object-Oriented Programming;Full-stack Development;Data Structures</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -6149,27 +6149,27 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Software Development, Data Science, Embedded Systems</t>
+          <t>Software Development;Data Science;Embedded Systems</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Software Developer, Data Scientist, Embedded Systems Engineer</t>
+          <t>Software Developer;Data Scientist;Embedded Systems Engineer</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Applications, Machine Learning, Embedded Systems</t>
+          <t>Applications;Machine Learning;Embedded Systems</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Computer Science, Software Engineering, Data Science</t>
+          <t>Computer Science;Software Engineering;Data Science</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Data Structures, Algorithm Optimization, Embedded Programming</t>
+          <t>Data Structures;Algorithm Optimization;Embedded Programming</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -6206,27 +6206,27 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Software Development, Data Science, AI</t>
+          <t>Software Development;Data Science;AI</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Software Developer, Data Scientist, AI Engineer</t>
+          <t>Software Developer;Data Scientist;AI Engineer</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Applications, Data Analysis, AI Development</t>
+          <t>Applications;Data Analysis;AI Development</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Computer Science, Software Engineering, Data Science</t>
+          <t>Computer Science;Software Engineering;Data Science</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Object-Oriented Programming, Full-stack Development, Machine Learning</t>
+          <t>Object-Oriented Programming;Full-stack Development;Machine Learning</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
